--- a/VT_EE_UPS_V01.xlsx
+++ b/VT_EE_UPS_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67818AE0-98CB-49AB-9A13-5891C522BC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C06CE32-0FDD-4B0C-B379-F906750CAE57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="901" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -1883,6 +1883,8 @@
     <author>Gary Goldstein</author>
     <author>Amit Kanudia</author>
     <author>Maurizio Gargiulo</author>
+    <author>tc={74C5EBC3-3855-49CC-8D22-3D22C507954E}</author>
+    <author>tc={E7A732B9-0C2E-4BF2-B78D-5BF686EADA9E}</author>
   </authors>
   <commentList>
     <comment ref="I3" authorId="0" shapeId="0" xr:uid="{6E5AAF16-2CE6-41AB-BA3C-4DE6B7722EEA}">
@@ -2653,6 +2655,22 @@
           </rPr>
           <t xml:space="preserve"> (Heating Plant)</t>
         </r>
+      </text>
+    </comment>
+    <comment ref="W10" authorId="3" shapeId="0" xr:uid="{74C5EBC3-3855-49CC-8D22-3D22C507954E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://news.err.ee/1609986120/vkg-overtakes-enefit-as-estonia-s-largest-oil-shale-miner</t>
+      </text>
+    </comment>
+    <comment ref="Y10" authorId="4" shapeId="0" xr:uid="{E7A732B9-0C2E-4BF2-B78D-5BF686EADA9E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Approx</t>
       </text>
     </comment>
   </commentList>
@@ -7359,7 +7377,7 @@
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000001000000}">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000001000000}">
       <text>
         <r>
           <rPr>
@@ -7473,7 +7491,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0800-000002000000}">
+    <comment ref="O3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0800-000002000000}">
       <text>
         <r>
           <rPr>
@@ -7499,7 +7517,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0800-000003000000}">
+    <comment ref="P3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0800-000003000000}">
       <text>
         <r>
           <rPr>
@@ -7572,7 +7590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0800-000004000000}">
+    <comment ref="Q3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0800-000004000000}">
       <text>
         <r>
           <rPr>
@@ -7625,7 +7643,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0800-000005000000}">
+    <comment ref="R3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0800-000005000000}">
       <text>
         <r>
           <rPr>
@@ -7705,7 +7723,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N12" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0800-000007000000}">
+    <comment ref="P12" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0800-000007000000}">
       <text>
         <r>
           <rPr>
@@ -7798,7 +7816,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O12" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0800-000008000000}">
+    <comment ref="Q12" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0800-000008000000}">
       <text>
         <r>
           <rPr>
@@ -7823,7 +7841,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P12" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0800-000009000000}">
+    <comment ref="R12" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0800-000009000000}">
       <text>
         <r>
           <rPr>
@@ -7886,7 +7904,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H13" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0800-00000A000000}">
+    <comment ref="J13" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0800-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -8134,7 +8152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="172">
   <si>
     <t>CommName</t>
   </si>
@@ -8588,17 +8606,81 @@
   <si>
     <t>Oil shale</t>
   </si>
+  <si>
+    <t>ktoe2PJ</t>
+  </si>
+  <si>
+    <t>total mined (t)</t>
+  </si>
+  <si>
+    <t>Energy density of oil shale (MJ/kg)</t>
+  </si>
+  <si>
+    <t>Production (PJ)</t>
+  </si>
+  <si>
+    <t>Cost (€/t)</t>
+  </si>
+  <si>
+    <t>Energy density of oil shale (tons/PJ)</t>
+  </si>
+  <si>
+    <t>Cost (M€/PJ)</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>Cap2ACT</t>
+  </si>
+  <si>
+    <t>Import of Electricity from Finland</t>
+  </si>
+  <si>
+    <t>IMPELCFIN</t>
+  </si>
+  <si>
+    <t>IMPELCLV</t>
+  </si>
+  <si>
+    <t>Import of Electricity from Latvia</t>
+  </si>
+  <si>
+    <t>EXPELCFIN</t>
+  </si>
+  <si>
+    <t>Export of Electricity to Finland</t>
+  </si>
+  <si>
+    <t>EXPELCLV</t>
+  </si>
+  <si>
+    <t>Export of Electricity to Latvia</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>NCAP_PASTI</t>
+  </si>
+  <si>
+    <t>FLO_COST</t>
+  </si>
+  <si>
+    <t>NCAP_AF</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="General_)"/>
     <numFmt numFmtId="165" formatCode="\Te\x\t"/>
+    <numFmt numFmtId="171" formatCode="0.000"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -8761,6 +8843,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="16">
@@ -9125,7 +9213,7 @@
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -9315,6 +9403,12 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="4" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="22">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
@@ -9441,15 +9535,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>809625</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>2486057</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>2247932</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9464,7 +9558,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7200900" y="6076950"/>
+          <a:off x="6838950" y="7362825"/>
           <a:ext cx="4514882" cy="1047750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -9549,13 +9643,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>428625</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
@@ -9938,13 +10032,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>2299252</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -10304,13 +10398,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -11131,6 +11225,12 @@
 </externalLink>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Kristopher Raik" id="{618EE9E7-879B-4C97-88A2-981A8E483D41}" userId="S::krraik@taltech.ee::b956339b-354b-46f9-8dd3-3584d8dbf762" providerId="AD"/>
+</personList>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -11477,6 +11577,23 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="W10" dT="2026-09-21T06:53:58.90" personId="{618EE9E7-879B-4C97-88A2-981A8E483D41}" id="{74C5EBC3-3855-49CC-8D22-3D22C507954E}">
+    <text>https://news.err.ee/1609986120/vkg-overtakes-enefit-as-estonia-s-largest-oil-shale-miner</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>4246205987</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="88" url="https://news.err.ee/1609986120/vkg-overtakes-enefit-as-estonia-s-largest-oil-shale-miner"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+  <threadedComment ref="Y10" dT="2026-09-21T06:56:12.74" personId="{618EE9E7-879B-4C97-88A2-981A8E483D41}" id="{E7A732B9-0C2E-4BF2-B78D-5BF686EADA9E}">
+    <text>Approx</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
@@ -12393,28 +12510,28 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="B1:S22"/>
+  <dimension ref="B1:U22"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" customWidth="1"/>
-    <col min="7" max="7" width="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.140625" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="8" width="13.7109375" customWidth="1"/>
+    <col min="9" max="9" width="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
+    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:21" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="24" t="s">
         <v>66</v>
       </c>
@@ -12430,8 +12547,10 @@
       <c r="F1" s="24" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="2" spans="2:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+    </row>
+    <row r="2" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>112</v>
       </c>
@@ -12443,130 +12562,131 @@
         <f>'EB1'!U$3</f>
         <v>Electricity</v>
       </c>
-      <c r="E2" s="9" t="str">
-        <f>'EB1'!$Z$2</f>
-        <v>PJ</v>
+      <c r="E2" s="9" t="s">
+        <v>158</v>
       </c>
       <c r="F2" s="9" t="str">
         <f>'EB1'!Y2</f>
         <v>M€2025</v>
       </c>
-      <c r="H2" s="91" t="s">
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="J2" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="91"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
+      <c r="K2" s="91"/>
       <c r="L2" s="92"/>
       <c r="M2" s="92"/>
       <c r="N2" s="92"/>
       <c r="O2" s="92"/>
       <c r="P2" s="92"/>
-    </row>
-    <row r="3" spans="2:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q2" s="92"/>
+      <c r="R2" s="92"/>
+    </row>
+    <row r="3" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
-      <c r="H3" s="93" t="s">
+      <c r="J3" s="93" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="94" t="s">
+      <c r="K3" s="94" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="93" t="s">
+      <c r="L3" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="93" t="s">
+      <c r="M3" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="93" t="s">
+      <c r="N3" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="93" t="s">
+      <c r="O3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="N3" s="93" t="s">
+      <c r="P3" s="93" t="s">
         <v>9</v>
       </c>
-      <c r="O3" s="93" t="s">
+      <c r="Q3" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="93" t="s">
+      <c r="R3" s="93" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:19" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:21" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
-      <c r="H4" s="95" t="s">
+      <c r="J4" s="95" t="s">
         <v>37</v>
       </c>
-      <c r="I4" s="95" t="s">
+      <c r="K4" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="95" t="s">
+      <c r="L4" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="95" t="s">
+      <c r="M4" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="L4" s="95" t="s">
+      <c r="N4" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="95" t="s">
+      <c r="O4" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="N4" s="95" t="s">
+      <c r="P4" s="95" t="s">
         <v>41</v>
       </c>
-      <c r="O4" s="95" t="s">
+      <c r="Q4" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="P4" s="95" t="s">
+      <c r="R4" s="95" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
-      <c r="H5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
-    </row>
-    <row r="6" spans="2:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+    </row>
+    <row r="6" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
-      <c r="H6" s="1"/>
       <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-    </row>
-    <row r="11" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+    </row>
+    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
       <c r="D11" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="4"/>
-      <c r="H11" s="91" t="s">
+      <c r="J11" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="91"/>
-      <c r="J11" s="96"/>
-      <c r="K11" s="96"/>
+      <c r="K11" s="91"/>
       <c r="L11" s="96"/>
       <c r="M11" s="96"/>
       <c r="N11" s="96"/>
       <c r="O11" s="96"/>
       <c r="P11" s="96"/>
-    </row>
-    <row r="12" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="Q11" s="96"/>
+      <c r="R11" s="96"/>
+    </row>
+    <row r="12" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
         <v>1</v>
       </c>
@@ -12577,40 +12697,46 @@
         <v>6</v>
       </c>
       <c r="E12" s="53" t="s">
-        <v>35</v>
+        <v>170</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12" s="93" t="s">
+        <v>169</v>
+      </c>
+      <c r="G12" s="99" t="s">
+        <v>159</v>
+      </c>
+      <c r="H12" s="99" t="s">
+        <v>171</v>
+      </c>
+      <c r="J12" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="94" t="s">
+      <c r="K12" s="94" t="s">
         <v>30</v>
       </c>
-      <c r="J12" s="93" t="s">
+      <c r="L12" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="K12" s="93" t="s">
+      <c r="M12" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="L12" s="93" t="s">
+      <c r="N12" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="M12" s="93" t="s">
+      <c r="O12" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="N12" s="93" t="s">
+      <c r="P12" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="O12" s="93" t="s">
+      <c r="Q12" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="P12" s="93" t="s">
+      <c r="R12" s="93" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="2:19" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:21" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="12" t="s">
         <v>39</v>
       </c>
@@ -12626,35 +12752,37 @@
       <c r="F13" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="H13" s="95" t="s">
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="J13" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="I13" s="95" t="s">
+      <c r="K13" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="95" t="s">
+      <c r="L13" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="K13" s="95" t="s">
+      <c r="M13" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="L13" s="95" t="s">
+      <c r="N13" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="M13" s="95" t="s">
+      <c r="O13" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="N13" s="95" t="s">
+      <c r="P13" s="95" t="s">
         <v>43</v>
       </c>
-      <c r="O13" s="95" t="s">
+      <c r="Q13" s="95" t="s">
         <v>42</v>
       </c>
-      <c r="P13" s="95" t="s">
+      <c r="R13" s="95" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="2:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="12" t="s">
         <v>77</v>
       </c>
@@ -12662,28 +12790,30 @@
       <c r="D14" s="11"/>
       <c r="E14" s="11" t="str">
         <f>$F$2&amp;"/"&amp;$E$2</f>
-        <v>M€2025/PJ</v>
-      </c>
-      <c r="F14" s="11" t="str">
-        <f>$E$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="H14" s="95" t="s">
+        <v>M€2025/TWh</v>
+      </c>
+      <c r="F14" s="97" t="str">
+        <f>O15</f>
+        <v>GW</v>
+      </c>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="J14" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="I14" s="95"/>
-      <c r="J14" s="95"/>
       <c r="K14" s="95"/>
       <c r="L14" s="95"/>
       <c r="M14" s="95"/>
       <c r="N14" s="95"/>
       <c r="O14" s="95"/>
       <c r="P14" s="95"/>
-    </row>
-    <row r="15" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="Q14" s="95"/>
+      <c r="R14" s="95"/>
+    </row>
+    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="str">
-        <f>J15</f>
-        <v>IMPELC1</v>
+        <f>L15</f>
+        <v>IMPELCFIN</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="str">
@@ -12691,86 +12821,168 @@
         <v>ELC</v>
       </c>
       <c r="E15" s="49">
-        <f>Pri_GAS!F12*1.3</f>
-        <v>5.3819999999999997</v>
-      </c>
-      <c r="F15" s="44">
-        <f>'EB1'!U6</f>
-        <v>583.76</v>
-      </c>
-      <c r="H15" s="96" t="str">
+        <v>80.39</v>
+      </c>
+      <c r="F15" s="101">
+        <v>1.016</v>
+      </c>
+      <c r="G15" s="100">
+        <v>8.76</v>
+      </c>
+      <c r="H15" s="100">
+        <v>0.9</v>
+      </c>
+      <c r="J15" s="96" t="str">
         <f>'EB1'!$B$6</f>
         <v>IMP</v>
       </c>
-      <c r="I15" s="96"/>
-      <c r="J15" s="96" t="str">
-        <f>$H$15&amp;C2&amp;1</f>
-        <v>IMPELC1</v>
-      </c>
-      <c r="K15" s="98" t="str">
-        <f>"Import of "&amp;D2&amp; " Step "&amp;RIGHT(J15,1)</f>
-        <v>Import of Electricity Step 1</v>
-      </c>
-      <c r="L15" s="96" t="str">
+      <c r="K15" s="96"/>
+      <c r="L15" s="96" t="s">
+        <v>161</v>
+      </c>
+      <c r="M15" s="98" t="s">
+        <v>160</v>
+      </c>
+      <c r="N15" s="96" t="str">
         <f>$E$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="M15" s="96"/>
-      <c r="N15" s="92" t="s">
+        <v>TWh</v>
+      </c>
+      <c r="O15" s="96" t="s">
+        <v>168</v>
+      </c>
+      <c r="P15" s="92" t="s">
         <v>92</v>
       </c>
-      <c r="O15" s="96"/>
-      <c r="P15" s="96"/>
-    </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="Q15" s="96"/>
+      <c r="R15" s="96"/>
+    </row>
+    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="str">
-        <f>J16</f>
-        <v>EXPELC1</v>
-      </c>
-      <c r="C16" s="1" t="str">
+        <f>L16</f>
+        <v>IMPELCLV</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1" t="str">
         <f>C2</f>
         <v>ELC</v>
       </c>
-      <c r="D16" s="1"/>
       <c r="E16" s="49">
-        <v>6</v>
-      </c>
-      <c r="F16" s="44">
-        <f>-'EB1'!U$7</f>
-        <v>563.40200000000004</v>
-      </c>
-      <c r="H16" s="96" t="str">
+        <v>85.31</v>
+      </c>
+      <c r="F16" s="101">
+        <v>1.149</v>
+      </c>
+      <c r="G16" s="100">
+        <v>8.76</v>
+      </c>
+      <c r="H16" s="100"/>
+      <c r="J16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L16" t="s">
+        <v>162</v>
+      </c>
+      <c r="M16" t="s">
+        <v>163</v>
+      </c>
+      <c r="N16" s="96" t="str">
+        <f t="shared" ref="N16:N18" si="0">$E$2</f>
+        <v>TWh</v>
+      </c>
+      <c r="O16" s="96" t="s">
+        <v>168</v>
+      </c>
+      <c r="P16" s="92" t="s">
+        <v>92</v>
+      </c>
+      <c r="U16" s="1"/>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B17" s="1" t="str">
+        <f>L17</f>
+        <v>EXPELCFIN</v>
+      </c>
+      <c r="C17" t="str">
+        <f>C2</f>
+        <v>ELC</v>
+      </c>
+      <c r="E17">
+        <v>40.49</v>
+      </c>
+      <c r="F17" s="102">
+        <v>1.016</v>
+      </c>
+      <c r="H17" s="51"/>
+      <c r="J17" s="96" t="str">
         <f>'EB1'!B7</f>
         <v>EXP</v>
       </c>
-      <c r="I16" s="96"/>
-      <c r="J16" s="96" t="str">
-        <f>$H$16&amp;C2&amp;1</f>
-        <v>EXPELC1</v>
-      </c>
-      <c r="K16" s="98" t="str">
-        <f>"Export of "&amp;D2&amp; " Step "&amp;RIGHT(J16,1)</f>
-        <v>Export of Electricity Step 1</v>
-      </c>
-      <c r="L16" s="96" t="str">
-        <f>$E$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="M16" s="96"/>
-      <c r="N16" s="92" t="s">
+      <c r="K17" s="96"/>
+      <c r="L17" s="96" t="s">
+        <v>164</v>
+      </c>
+      <c r="M17" s="98" t="s">
+        <v>165</v>
+      </c>
+      <c r="N17" s="96" t="str">
+        <f t="shared" si="0"/>
+        <v>TWh</v>
+      </c>
+      <c r="O17" s="96" t="s">
+        <v>168</v>
+      </c>
+      <c r="P17" s="92" t="s">
         <v>92</v>
       </c>
-      <c r="O16" s="96"/>
-      <c r="P16" s="96"/>
-      <c r="S16" s="1"/>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="Q17" s="96"/>
+      <c r="R17" s="96"/>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B18" s="1" t="str">
+        <f>L18</f>
+        <v>EXPELCLV</v>
+      </c>
+      <c r="C18" t="str">
+        <f>C2</f>
+        <v>ELC</v>
+      </c>
+      <c r="E18">
+        <v>85.31</v>
+      </c>
+      <c r="F18" s="102">
+        <v>0.85</v>
+      </c>
+      <c r="H18" s="51"/>
+      <c r="J18" t="s">
+        <v>62</v>
+      </c>
+      <c r="L18" t="s">
+        <v>166</v>
+      </c>
+      <c r="M18" t="s">
+        <v>167</v>
+      </c>
+      <c r="N18" s="96" t="str">
+        <f t="shared" si="0"/>
+        <v>TWh</v>
+      </c>
+      <c r="O18" s="96" t="s">
+        <v>168</v>
+      </c>
+      <c r="P18" s="92" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="H19" s="51"/>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B21" s="38"/>
       <c r="C21" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B22" s="46"/>
       <c r="C22" s="1" t="s">
         <v>115</v>
@@ -13107,10 +13319,7 @@
         <f>-SUM('EB1'!F13)/SUM('EB1'!G13:M13)</f>
         <v>1.0128203720739584</v>
       </c>
-      <c r="G12" s="45">
-        <f>SUM('EB1'!G13:M13)</f>
-        <v>15667.368999999999</v>
-      </c>
+      <c r="G12" s="45"/>
       <c r="H12" s="5"/>
       <c r="J12" s="92" t="s">
         <v>87</v>
@@ -13417,7 +13626,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:R26"/>
+  <dimension ref="B1:R23"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
@@ -13711,35 +13920,28 @@
     <row r="11" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="str">
         <f>K11</f>
-        <v>MINCOA1</v>
+        <v>IMPCOA1</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="str">
         <f>$K$5</f>
         <v>COA</v>
       </c>
-      <c r="E11" s="48">
-        <v>80000</v>
-      </c>
-      <c r="F11" s="50">
-        <v>2</v>
-      </c>
-      <c r="G11" s="44">
-        <f>'EB1'!$D$5*'EB1'!D21</f>
-        <v>3947.949525</v>
-      </c>
-      <c r="I11" s="92" t="str">
-        <f>'EB1'!$B$5</f>
-        <v>MIN</v>
+      <c r="E11" s="1"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="5"/>
+      <c r="I11" s="96" t="str">
+        <f>'EB1'!$B$6</f>
+        <v>IMP</v>
       </c>
       <c r="J11" s="96"/>
       <c r="K11" s="96" t="str">
         <f>$I$11&amp;$C$2&amp;1</f>
-        <v>MINCOA1</v>
+        <v>IMPCOA1</v>
       </c>
       <c r="L11" s="98" t="str">
-        <f>"Domestic Supply of "&amp;$D$2&amp; " Step "&amp;RIGHT(K11,1)</f>
-        <v>Domestic Supply of Solid Fuels Step 1</v>
+        <f>"Import of "&amp;$D$2&amp; " Step "&amp;RIGHT(K11,1)</f>
+        <v>Import of Solid Fuels Step 1</v>
       </c>
       <c r="M11" s="96" t="str">
         <f>$E$2</f>
@@ -13756,32 +13958,27 @@
     <row r="12" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="str">
         <f>K12</f>
-        <v>MINCOA2</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1" t="str">
+        <v>EXPCOA1</v>
+      </c>
+      <c r="C12" s="1" t="str">
         <f>$K$5</f>
         <v>COA</v>
       </c>
-      <c r="E12" s="48">
-        <v>160000</v>
-      </c>
-      <c r="F12" s="50">
-        <v>2.5</v>
-      </c>
-      <c r="G12" s="44">
-        <f>'EB1'!$D$5*'EB1'!D22</f>
-        <v>1315.9831750000001</v>
-      </c>
-      <c r="I12" s="96"/>
+      <c r="D12" s="1"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="45"/>
+      <c r="I12" s="96" t="str">
+        <f>'EB1'!B7</f>
+        <v>EXP</v>
+      </c>
       <c r="J12" s="96"/>
       <c r="K12" s="96" t="str">
-        <f>$I$11&amp;$C$2&amp;2</f>
-        <v>MINCOA2</v>
+        <f>$I$12&amp;$C$2&amp;1</f>
+        <v>EXPCOA1</v>
       </c>
       <c r="L12" s="98" t="str">
-        <f>"Domestic Supply of "&amp;$D$2&amp; " Step "&amp;RIGHT(K12,1)</f>
-        <v>Domestic Supply of Solid Fuels Step 2</v>
+        <f>"Export of "&amp;$D$2&amp; " Step "&amp;RIGHT(K12,1)</f>
+        <v>Export of Solid Fuels Step 1</v>
       </c>
       <c r="M12" s="96" t="str">
         <f>$E$2</f>
@@ -13796,165 +13993,44 @@
       <c r="Q12" s="96"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B13" s="1" t="str">
-        <f>K13</f>
-        <v>MINCOA3</v>
-      </c>
+      <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="1" t="str">
-        <f>$K$5</f>
-        <v>COA</v>
-      </c>
-      <c r="E13" s="48">
-        <v>3000000</v>
-      </c>
-      <c r="F13" s="50">
-        <v>3</v>
-      </c>
+      <c r="E13" s="1"/>
       <c r="G13" s="10"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="96"/>
-      <c r="K13" s="96" t="str">
-        <f>$I$11&amp;$C$2&amp;3</f>
-        <v>MINCOA3</v>
-      </c>
-      <c r="L13" s="98" t="str">
-        <f>"Domestic Supply of "&amp;$D$2&amp; " Step "&amp;RIGHT(K13,1)</f>
-        <v>Domestic Supply of Solid Fuels Step 3</v>
-      </c>
-      <c r="M13" s="96" t="str">
-        <f>$E$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="N13" s="96" t="str">
-        <f>$E$2&amp;"a"</f>
-        <v>PJa</v>
-      </c>
-      <c r="O13" s="96"/>
-      <c r="P13" s="96"/>
-      <c r="Q13" s="96"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B14" s="1" t="str">
-        <f>K14</f>
-        <v>IMPCOA1</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1" t="str">
-        <f>$K$5</f>
-        <v>COA</v>
-      </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="50">
-        <v>2.75</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="I14" s="96" t="str">
-        <f>'EB1'!$B$6</f>
-        <v>IMP</v>
-      </c>
-      <c r="J14" s="96"/>
-      <c r="K14" s="96" t="str">
-        <f>$I$14&amp;$C$2&amp;1</f>
-        <v>IMPCOA1</v>
-      </c>
-      <c r="L14" s="98" t="str">
-        <f>"Import of "&amp;$D$2&amp; " Step "&amp;RIGHT(K14,1)</f>
-        <v>Import of Solid Fuels Step 1</v>
-      </c>
-      <c r="M14" s="96" t="str">
-        <f>$E$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="N14" s="96" t="str">
-        <f>$E$2&amp;"a"</f>
-        <v>PJa</v>
-      </c>
-      <c r="O14" s="96"/>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="96"/>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B15" s="1" t="str">
-        <f>K15</f>
-        <v>EXPCOA1</v>
-      </c>
-      <c r="C15" s="1" t="str">
-        <f>$K$5</f>
-        <v>COA</v>
-      </c>
-      <c r="D15" s="1"/>
-      <c r="F15" s="50">
-        <v>2.75</v>
-      </c>
-      <c r="G15" s="45">
-        <f>-'EB1'!D7</f>
-        <v>745.59484999999995</v>
-      </c>
-      <c r="I15" s="96" t="str">
-        <f>'EB1'!B7</f>
-        <v>EXP</v>
-      </c>
-      <c r="J15" s="96"/>
-      <c r="K15" s="96" t="str">
-        <f>$I$15&amp;$C$2&amp;1</f>
-        <v>EXPCOA1</v>
-      </c>
-      <c r="L15" s="98" t="str">
-        <f>"Export of "&amp;$D$2&amp; " Step "&amp;RIGHT(K15,1)</f>
-        <v>Export of Solid Fuels Step 1</v>
-      </c>
-      <c r="M15" s="96" t="str">
-        <f>$E$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="N15" s="96" t="str">
-        <f>$E$2&amp;"a"</f>
-        <v>PJa</v>
-      </c>
-      <c r="O15" s="96"/>
-      <c r="P15" s="96"/>
-      <c r="Q15" s="96"/>
-    </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="G16" s="10"/>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B17" s="1"/>
-    </row>
-    <row r="22" spans="2:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C22"/>
-      <c r="D22"/>
-      <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22"/>
-      <c r="H22"/>
-      <c r="I22"/>
-      <c r="J22"/>
-      <c r="K22"/>
-      <c r="L22"/>
-      <c r="M22"/>
-      <c r="N22"/>
-      <c r="O22"/>
-      <c r="P22"/>
-      <c r="Q22"/>
-      <c r="R22"/>
+      <c r="B14" s="1"/>
+    </row>
+    <row r="19" spans="2:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19"/>
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19"/>
+      <c r="N19"/>
+      <c r="O19"/>
+      <c r="P19"/>
+      <c r="Q19"/>
+      <c r="R19"/>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="1"/>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B22" s="48"/>
+      <c r="C22" s="1" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="R23" s="1"/>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B25" s="48"/>
-      <c r="C25" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B26" s="46"/>
-      <c r="C26" s="1" t="s">
+      <c r="B23" s="46"/>
+      <c r="C23" s="1" t="s">
         <v>115</v>
       </c>
     </row>
@@ -13969,7 +14045,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CE3D601-8357-4014-BBD5-DE38AC19BE99}">
-  <dimension ref="B1:R26"/>
+  <dimension ref="B1:Z26"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
@@ -13989,9 +14065,13 @@
     <col min="15" max="15" width="13" customWidth="1"/>
     <col min="16" max="16" width="15.140625" customWidth="1"/>
     <col min="17" max="17" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:26" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="24" t="s">
         <v>66</v>
       </c>
@@ -14008,7 +14088,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="9"/>
       <c r="C2" s="9" t="s">
         <v>149</v>
@@ -14036,7 +14116,7 @@
       <c r="P2" s="92"/>
       <c r="Q2" s="92"/>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:26" x14ac:dyDescent="0.2">
       <c r="I3" s="93" t="s">
         <v>7</v>
       </c>
@@ -14065,8 +14145,13 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="1"/>
+    <row r="4" spans="2:26" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4">
+        <v>4.1868000000000002E-2</v>
+      </c>
       <c r="I4" s="95" t="s">
         <v>37</v>
       </c>
@@ -14095,7 +14180,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:26" x14ac:dyDescent="0.2">
       <c r="I5" s="92" t="s">
         <v>65</v>
       </c>
@@ -14117,7 +14202,15 @@
       <c r="P5" s="92"/>
       <c r="Q5" s="92"/>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="V6" t="s">
+        <v>153</v>
+      </c>
+      <c r="W6">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:26" x14ac:dyDescent="0.2">
       <c r="D7" s="4" t="s">
         <v>13</v>
       </c>
@@ -14133,8 +14226,15 @@
       <c r="O7" s="96"/>
       <c r="P7" s="96"/>
       <c r="Q7" s="96"/>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="V7" t="s">
+        <v>156</v>
+      </c>
+      <c r="W7">
+        <f>1000000000/(W6*1000)</f>
+        <v>105263.15789473684</v>
+      </c>
+    </row>
+    <row r="8" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
         <v>1</v>
       </c>
@@ -14181,7 +14281,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:26" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
         <v>39</v>
       </c>
@@ -14227,8 +14327,20 @@
       <c r="Q9" s="95" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="W9" t="s">
+        <v>152</v>
+      </c>
+      <c r="X9" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>155</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10" spans="2:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="12" t="s">
         <v>77</v>
       </c>
@@ -14257,8 +14369,25 @@
       <c r="O10" s="97"/>
       <c r="P10" s="97"/>
       <c r="Q10" s="97"/>
-    </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="V10">
+        <v>2025</v>
+      </c>
+      <c r="W10">
+        <v>8021108</v>
+      </c>
+      <c r="X10">
+        <f>W10*1000*W6/1000000000</f>
+        <v>76.200525999999996</v>
+      </c>
+      <c r="Y10">
+        <v>30</v>
+      </c>
+      <c r="Z10">
+        <f>W7*Y10/1000000</f>
+        <v>3.1578947368421053</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="str">
         <f>K11</f>
         <v>MINSHL1</v>
@@ -14268,15 +14397,14 @@
         <f>$K$5</f>
         <v>SHL</v>
       </c>
-      <c r="E11" s="48">
-        <v>80000</v>
-      </c>
+      <c r="E11" s="48"/>
       <c r="F11" s="50">
-        <v>2</v>
+        <f>Z10</f>
+        <v>3.1578947368421053</v>
       </c>
       <c r="G11" s="44">
-        <f>'EB1'!$D$5*'EB1'!D21</f>
-        <v>3947.949525</v>
+        <f>X10</f>
+        <v>76.200525999999996</v>
       </c>
       <c r="I11" s="92" t="str">
         <f>'EB1'!$B$5</f>
@@ -14303,7 +14431,7 @@
       <c r="P11" s="96"/>
       <c r="Q11" s="96"/>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -14320,7 +14448,7 @@
       <c r="P12" s="96"/>
       <c r="Q12" s="96"/>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -14337,7 +14465,7 @@
       <c r="P13" s="96"/>
       <c r="Q13" s="96"/>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -14354,7 +14482,7 @@
       <c r="P14" s="96"/>
       <c r="Q14" s="96"/>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -14370,7 +14498,7 @@
       <c r="P15" s="96"/>
       <c r="Q15" s="96"/>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="E16" s="1"/>
@@ -14722,16 +14850,11 @@
         <f>$K$5</f>
         <v>GAS</v>
       </c>
-      <c r="E11" s="43">
-        <v>15000</v>
-      </c>
+      <c r="E11" s="43"/>
       <c r="F11" s="49">
         <v>3.6</v>
       </c>
-      <c r="G11" s="45">
-        <f>'EB1'!$E$5*'EB1'!E21</f>
-        <v>1579.8994000000002</v>
-      </c>
+      <c r="G11" s="45"/>
       <c r="I11" s="92" t="str">
         <f>'EB1'!$B$5</f>
         <v>MIN</v>
@@ -14767,16 +14890,11 @@
         <f>$K$5</f>
         <v>GAS</v>
       </c>
-      <c r="E12" s="43">
-        <v>20000</v>
-      </c>
+      <c r="E12" s="43"/>
       <c r="F12" s="49">
         <v>4.1399999999999997</v>
       </c>
-      <c r="G12" s="45">
-        <f>'EB1'!$E$5*'EB1'!E22</f>
-        <v>1579.8994000000002</v>
-      </c>
+      <c r="G12" s="45"/>
       <c r="I12" s="96"/>
       <c r="J12" s="96"/>
       <c r="K12" s="96" t="str">
@@ -14809,15 +14927,11 @@
         <f>$K$5</f>
         <v>GAS</v>
       </c>
-      <c r="E13" s="49">
-        <v>0</v>
-      </c>
+      <c r="E13" s="49"/>
       <c r="F13" s="49">
         <v>5.4</v>
       </c>
-      <c r="G13" s="43">
-        <v>0</v>
-      </c>
+      <c r="G13" s="43"/>
       <c r="I13" s="96"/>
       <c r="J13" s="96"/>
       <c r="K13" s="96" t="str">
@@ -14853,10 +14967,7 @@
       <c r="F14" s="49">
         <v>4.5</v>
       </c>
-      <c r="G14" s="45">
-        <f>'EB1'!E6</f>
-        <v>5316.6916000000001</v>
-      </c>
+      <c r="G14" s="45"/>
       <c r="I14" s="96" t="str">
         <f>'EB1'!$B$6</f>
         <v>IMP</v>
@@ -14894,10 +15005,7 @@
       <c r="F15" s="49">
         <v>4.5</v>
       </c>
-      <c r="G15" s="45">
-        <f>-'EB1'!E7</f>
-        <v>1006.5324000000001</v>
-      </c>
+      <c r="G15" s="45"/>
       <c r="I15" s="96" t="str">
         <f>'EB1'!B7</f>
         <v>EXP</v>
@@ -14969,7 +15077,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="B1:W24"/>
+  <dimension ref="B1:W21"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
@@ -14991,7 +15099,7 @@
     <col min="17" max="17" width="7.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:23" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="24" t="s">
         <v>66</v>
       </c>
@@ -15008,7 +15116,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="9"/>
       <c r="C2" s="9" t="str">
         <f>'EB1'!F2</f>
@@ -15038,7 +15146,7 @@
       <c r="P2" s="92"/>
       <c r="Q2" s="92"/>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:23" x14ac:dyDescent="0.2">
       <c r="I3" s="93" t="s">
         <v>7</v>
       </c>
@@ -15067,7 +15175,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:23" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C4" s="1"/>
       <c r="I4" s="95" t="s">
         <v>37</v>
@@ -15097,7 +15205,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:23" x14ac:dyDescent="0.2">
       <c r="I5" s="92" t="s">
         <v>65</v>
       </c>
@@ -15119,7 +15227,7 @@
       <c r="P5" s="92"/>
       <c r="Q5" s="92"/>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:23" x14ac:dyDescent="0.2">
       <c r="D7" s="4" t="s">
         <v>13</v>
       </c>
@@ -15136,7 +15244,7 @@
       <c r="P7" s="96"/>
       <c r="Q7" s="96"/>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
         <v>1</v>
       </c>
@@ -15183,7 +15291,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:23" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
         <v>39</v>
       </c>
@@ -15230,7 +15338,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="12" t="s">
         <v>77</v>
       </c>
@@ -15260,38 +15368,33 @@
       <c r="P10" s="97"/>
       <c r="Q10" s="97"/>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="str">
         <f>K11</f>
-        <v>MINOIL1</v>
+        <v>IMPOIL1</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="str">
         <f>$K$5</f>
         <v>OIL</v>
       </c>
-      <c r="E11" s="38">
-        <v>7200</v>
-      </c>
+      <c r="E11" s="38"/>
       <c r="F11" s="49">
-        <v>6.4</v>
-      </c>
-      <c r="G11" s="45">
-        <f>'EB1'!$F$5*'EB1'!F21</f>
-        <v>2149.0016000000001</v>
-      </c>
-      <c r="I11" s="92" t="str">
-        <f>'EB1'!$B$5</f>
-        <v>MIN</v>
+        <v>8</v>
+      </c>
+      <c r="G11" s="10"/>
+      <c r="I11" s="96" t="str">
+        <f>'EB1'!$B$6</f>
+        <v>IMP</v>
       </c>
       <c r="J11" s="96"/>
       <c r="K11" s="96" t="str">
         <f>$I$11&amp;$C$2&amp;1</f>
-        <v>MINOIL1</v>
+        <v>IMPOIL1</v>
       </c>
       <c r="L11" s="98" t="str">
-        <f>"Domestic Supply of "&amp;$D$2&amp; " Step "&amp;RIGHT(K11,1)</f>
-        <v>Domestic Supply of Crude Oil Step 1</v>
+        <f>"Import of "&amp;$D$2&amp; " Step "&amp;RIGHT(K11,1)</f>
+        <v>Import of Crude Oil Step 1</v>
       </c>
       <c r="M11" s="96" t="str">
         <f>$E$2</f>
@@ -15305,35 +15408,33 @@
       <c r="P11" s="96"/>
       <c r="Q11" s="96"/>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="str">
         <f>K12</f>
-        <v>MINOIL2</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1" t="str">
+        <v>EXPOIL1</v>
+      </c>
+      <c r="C12" s="1" t="str">
         <f>$K$5</f>
         <v>OIL</v>
       </c>
-      <c r="E12" s="38">
-        <v>1800</v>
-      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="38"/>
       <c r="F12" s="49">
-        <v>7.3599999999999994</v>
-      </c>
-      <c r="G12" s="45">
-        <f>'EB1'!$F$5*'EB1'!F22</f>
-        <v>537.25040000000001</v>
-      </c>
-      <c r="I12" s="96"/>
+        <v>8</v>
+      </c>
+      <c r="G12" s="44"/>
+      <c r="I12" s="96" t="str">
+        <f>'EB1'!B7</f>
+        <v>EXP</v>
+      </c>
       <c r="J12" s="96"/>
       <c r="K12" s="96" t="str">
-        <f>$I$11&amp;$C$2&amp;2</f>
-        <v>MINOIL2</v>
+        <f>$I$12&amp;$C$2&amp;1</f>
+        <v>EXPOIL1</v>
       </c>
       <c r="L12" s="98" t="str">
-        <f>"Domestic Supply of "&amp;$D$2&amp; " Step "&amp;RIGHT(K12,1)</f>
-        <v>Domestic Supply of Crude Oil Step 2</v>
+        <f>"Export of "&amp;$D$2&amp; " Step "&amp;RIGHT(K12,1)</f>
+        <v>Export of Crude Oil Step 1</v>
       </c>
       <c r="M12" s="96" t="str">
         <f>$E$2</f>
@@ -15347,158 +15448,36 @@
       <c r="P12" s="96"/>
       <c r="Q12" s="96"/>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B13" s="1" t="str">
-        <f>K13</f>
-        <v>MINOIL3</v>
-      </c>
+    <row r="13" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="1" t="str">
-        <f>$K$5</f>
-        <v>OIL</v>
-      </c>
-      <c r="E13" s="38">
-        <v>1200000</v>
-      </c>
-      <c r="F13" s="49">
-        <v>9.6000000000000014</v>
-      </c>
-      <c r="G13" s="10"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="96"/>
-      <c r="K13" s="96" t="str">
-        <f>$I$11&amp;$C$2&amp;3</f>
-        <v>MINOIL3</v>
-      </c>
-      <c r="L13" s="98" t="str">
-        <f>"Domestic Supply of "&amp;$D$2&amp; " Step "&amp;RIGHT(K13,1)</f>
-        <v>Domestic Supply of Crude Oil Step 3</v>
-      </c>
-      <c r="M13" s="96" t="str">
-        <f>$E$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="N13" s="96" t="str">
-        <f>$E$2&amp;"a"</f>
-        <v>PJa</v>
-      </c>
-      <c r="O13" s="96"/>
-      <c r="P13" s="96"/>
-      <c r="Q13" s="96"/>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B14" s="1" t="str">
-        <f>K14</f>
-        <v>IMPOIL1</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1" t="str">
-        <f>$K$5</f>
-        <v>OIL</v>
-      </c>
-      <c r="E14" s="38"/>
-      <c r="F14" s="49">
-        <v>8</v>
-      </c>
-      <c r="G14" s="10"/>
-      <c r="I14" s="96" t="str">
-        <f>'EB1'!$B$6</f>
-        <v>IMP</v>
-      </c>
-      <c r="J14" s="96"/>
-      <c r="K14" s="96" t="str">
-        <f>$I$14&amp;$C$2&amp;1</f>
-        <v>IMPOIL1</v>
-      </c>
-      <c r="L14" s="98" t="str">
-        <f>"Import of "&amp;$D$2&amp; " Step "&amp;RIGHT(K14,1)</f>
-        <v>Import of Crude Oil Step 1</v>
-      </c>
-      <c r="M14" s="96" t="str">
-        <f>$E$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="N14" s="96" t="str">
-        <f>$E$2&amp;"a"</f>
-        <v>PJa</v>
-      </c>
-      <c r="O14" s="96"/>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="96"/>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B15" s="1" t="str">
-        <f>K15</f>
-        <v>EXPOIL1</v>
-      </c>
-      <c r="C15" s="1" t="str">
-        <f>$K$5</f>
-        <v>OIL</v>
-      </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="49">
-        <v>8</v>
-      </c>
-      <c r="G15" s="44">
-        <f>-'EB1'!F7</f>
-        <v>1648.4854999999998</v>
-      </c>
-      <c r="I15" s="96" t="str">
-        <f>'EB1'!B7</f>
-        <v>EXP</v>
-      </c>
-      <c r="J15" s="96"/>
-      <c r="K15" s="96" t="str">
-        <f>$I$15&amp;$C$2&amp;1</f>
-        <v>EXPOIL1</v>
-      </c>
-      <c r="L15" s="98" t="str">
-        <f>"Export of "&amp;$D$2&amp; " Step "&amp;RIGHT(K15,1)</f>
-        <v>Export of Crude Oil Step 1</v>
-      </c>
-      <c r="M15" s="96" t="str">
-        <f>$E$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="N15" s="96" t="str">
-        <f>$E$2&amp;"a"</f>
-        <v>PJa</v>
-      </c>
-      <c r="O15" s="96"/>
-      <c r="P15" s="96"/>
-      <c r="Q15" s="96"/>
-    </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="F16" s="51"/>
-    </row>
-    <row r="17" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B17" s="1"/>
-      <c r="F17" s="51"/>
-    </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-    </row>
-    <row r="19" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="S19" s="1"/>
-      <c r="V19" s="1"/>
-      <c r="W19" s="1"/>
-    </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B23" s="48"/>
-      <c r="C23" s="1" t="s">
+      <c r="F13" s="51"/>
+    </row>
+    <row r="14" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B14" s="1"/>
+      <c r="F14" s="51"/>
+    </row>
+    <row r="15" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+    </row>
+    <row r="16" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="S16" s="1"/>
+      <c r="V16" s="1"/>
+      <c r="W16" s="1"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B20" s="48"/>
+      <c r="C20" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="24" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B24" s="46"/>
-      <c r="C24" s="1" t="s">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B21" s="46"/>
+      <c r="C21" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H24" s="1"/>
+      <c r="H21" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17393,7 +17372,7 @@
         <v>DSL</v>
       </c>
       <c r="E17" s="49">
-        <f>Pri_OIL!$F$14*1.3</f>
+        <f>Pri_OIL!$F$11*1.3</f>
         <v>10.4</v>
       </c>
       <c r="F17" s="44"/>
@@ -17430,7 +17409,7 @@
         <v>KER</v>
       </c>
       <c r="E18" s="49">
-        <f>Pri_OIL!$F$14*1.4</f>
+        <f>Pri_OIL!$F$11*1.4</f>
         <v>11.2</v>
       </c>
       <c r="F18" s="44"/>
@@ -17465,7 +17444,7 @@
         <v>LPG</v>
       </c>
       <c r="E19" s="49">
-        <f>Pri_OIL!$F$14*1.1</f>
+        <f>Pri_OIL!$F$11*1.1</f>
         <v>8.8000000000000007</v>
       </c>
       <c r="F19" s="44"/>
@@ -17501,7 +17480,7 @@
         <v>GSL</v>
       </c>
       <c r="E20" s="49">
-        <f>Pri_OIL!$F$14*1.4</f>
+        <f>Pri_OIL!$F$11*1.4</f>
         <v>11.2</v>
       </c>
       <c r="F20" s="44"/>
@@ -17535,7 +17514,7 @@
         <v>NAP</v>
       </c>
       <c r="E21" s="49">
-        <f>Pri_OIL!$F$14*1.05</f>
+        <f>Pri_OIL!$F$11*1.05</f>
         <v>8.4</v>
       </c>
       <c r="F21" s="44"/>
@@ -17569,7 +17548,7 @@
         <v>HFO</v>
       </c>
       <c r="E22" s="49">
-        <f>Pri_OIL!$F$14*1.05</f>
+        <f>Pri_OIL!$F$11*1.05</f>
         <v>8.4</v>
       </c>
       <c r="F22" s="44"/>
@@ -17603,7 +17582,7 @@
         <v>OPP</v>
       </c>
       <c r="E23" s="49">
-        <f>Pri_OIL!$F$14*1.05</f>
+        <f>Pri_OIL!$F$11*1.05</f>
         <v>8.4</v>
       </c>
       <c r="F23" s="44"/>
@@ -17640,10 +17619,7 @@
         <f>E17*0.99</f>
         <v>10.295999999999999</v>
       </c>
-      <c r="F24" s="44">
-        <f>-'EB1'!G$7</f>
-        <v>1683.1424999999999</v>
-      </c>
+      <c r="F24" s="44"/>
       <c r="H24" s="96" t="str">
         <f>'EB1'!B7</f>
         <v>EXP</v>
@@ -17681,10 +17657,7 @@
         <f t="shared" ref="E25:E30" si="10">E18*0.99</f>
         <v>11.087999999999999</v>
       </c>
-      <c r="F25" s="44">
-        <f>-'EB1'!H$7</f>
-        <v>295.38850000000002</v>
-      </c>
+      <c r="F25" s="44"/>
       <c r="H25" s="96"/>
       <c r="I25" s="96"/>
       <c r="J25" s="96" t="str">
@@ -17719,10 +17692,7 @@
         <f t="shared" si="10"/>
         <v>8.7119999999999997</v>
       </c>
-      <c r="F26" s="44">
-        <f>-'EB1'!I$7</f>
-        <v>194.51650000000001</v>
-      </c>
+      <c r="F26" s="44"/>
       <c r="H26" s="96"/>
       <c r="I26" s="96"/>
       <c r="J26" s="96" t="str">
@@ -17756,10 +17726,7 @@
         <f t="shared" si="10"/>
         <v>11.087999999999999</v>
       </c>
-      <c r="F27" s="44">
-        <f>-'EB1'!J$7</f>
-        <v>1500.6420000000001</v>
-      </c>
+      <c r="F27" s="44"/>
       <c r="H27" s="96"/>
       <c r="I27" s="96"/>
       <c r="J27" s="96" t="str">
@@ -17793,10 +17760,7 @@
         <f t="shared" si="10"/>
         <v>8.3160000000000007</v>
       </c>
-      <c r="F28" s="44">
-        <f>-'EB1'!K$7</f>
-        <v>400.84</v>
-      </c>
+      <c r="F28" s="44"/>
       <c r="H28" s="96"/>
       <c r="I28" s="96"/>
       <c r="J28" s="96" t="str">
@@ -17830,14 +17794,11 @@
         <f t="shared" si="10"/>
         <v>8.3160000000000007</v>
       </c>
-      <c r="F29" s="44">
-        <f>-'EB1'!L$7</f>
-        <v>1239.28</v>
-      </c>
+      <c r="F29" s="44"/>
       <c r="H29" s="96"/>
       <c r="I29" s="96"/>
       <c r="J29" s="96" t="str">
-        <f t="shared" si="8"/>
+        <f>$H$24&amp;C7&amp;1</f>
         <v>EXPHFO1</v>
       </c>
       <c r="K29" s="98" t="str">
@@ -17867,10 +17828,7 @@
         <f t="shared" si="10"/>
         <v>8.3160000000000007</v>
       </c>
-      <c r="F30" s="44">
-        <f>-'EB1'!M$7</f>
-        <v>453.036</v>
-      </c>
+      <c r="F30" s="44"/>
       <c r="H30" s="96"/>
       <c r="I30" s="96"/>
       <c r="J30" s="96" t="str">

--- a/VT_EE_UPS_V01.xlsx
+++ b/VT_EE_UPS_V01.xlsx
@@ -8,26 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C06CE32-0FDD-4B0C-B379-F906750CAE57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CE95D7-95B4-48CB-8162-2C6C133C6762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
-    <sheet name="Pri_COA" sheetId="132" r:id="rId2"/>
-    <sheet name="Pri_SHL" sheetId="155" r:id="rId3"/>
-    <sheet name="Pri_GAS" sheetId="136" r:id="rId4"/>
-    <sheet name="Pri_OIL" sheetId="137" r:id="rId5"/>
-    <sheet name="Pri_NUC" sheetId="144" r:id="rId6"/>
-    <sheet name="Pri_RNW" sheetId="142" r:id="rId7"/>
-    <sheet name="Pri_WST" sheetId="154" r:id="rId8"/>
-    <sheet name="Pri_PP" sheetId="148" r:id="rId9"/>
-    <sheet name="Pri_ELC" sheetId="152" r:id="rId10"/>
-    <sheet name="Con_REF" sheetId="147" r:id="rId11"/>
-    <sheet name="TOTCO2" sheetId="153" r:id="rId12"/>
+    <sheet name="JRC-IDEES2023" sheetId="156" r:id="rId2"/>
+    <sheet name="Pri_COA" sheetId="132" r:id="rId3"/>
+    <sheet name="Pri_SHL" sheetId="155" r:id="rId4"/>
+    <sheet name="Pri_GAS" sheetId="136" r:id="rId5"/>
+    <sheet name="Pri_OIL" sheetId="137" r:id="rId6"/>
+    <sheet name="Pri_NUC" sheetId="144" r:id="rId7"/>
+    <sheet name="Pri_RNW" sheetId="142" r:id="rId8"/>
+    <sheet name="Pri_WST" sheetId="154" r:id="rId9"/>
+    <sheet name="Pri_PP" sheetId="148" r:id="rId10"/>
+    <sheet name="Pri_ELC" sheetId="152" r:id="rId11"/>
+    <sheet name="Con_REF" sheetId="147" r:id="rId12"/>
+    <sheet name="TOTCO2" sheetId="153" r:id="rId13"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId13"/>
+    <externalReference r:id="rId14"/>
   </externalReferences>
   <definedNames>
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
@@ -2685,7 +2686,7 @@
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -2799,7 +2800,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
+    <comment ref="Q3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -2825,7 +2826,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
+    <comment ref="R3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -2898,7 +2899,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
+    <comment ref="S3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -2951,7 +2952,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
+    <comment ref="T3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -3031,7 +3032,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O8" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
+    <comment ref="R8" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
       <text>
         <r>
           <rPr>
@@ -3124,7 +3125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P8" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
+    <comment ref="S8" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
       <text>
         <r>
           <rPr>
@@ -3149,7 +3150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q8" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
+    <comment ref="T8" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
       <text>
         <r>
           <rPr>
@@ -3212,7 +3213,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I9" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000A000000}">
+    <comment ref="L9" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -8152,7 +8153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="182">
   <si>
     <t>CommName</t>
   </si>
@@ -8668,6 +8669,36 @@
   </si>
   <si>
     <t>NCAP_AF</t>
+  </si>
+  <si>
+    <t>ACT_BND~2020</t>
+  </si>
+  <si>
+    <t>ACT_BND~2021</t>
+  </si>
+  <si>
+    <t>ACT_BND~2022</t>
+  </si>
+  <si>
+    <t>ACT_BND~2023</t>
+  </si>
+  <si>
+    <t>ktoe</t>
+  </si>
+  <si>
+    <t>supply</t>
+  </si>
+  <si>
+    <t>import</t>
+  </si>
+  <si>
+    <t>export</t>
+  </si>
+  <si>
+    <t>Natural gas</t>
+  </si>
+  <si>
+    <t>mwh2PJ</t>
   </si>
 </sst>
 </file>
@@ -8680,7 +8711,7 @@
     <numFmt numFmtId="165" formatCode="\Te\x\t"/>
     <numFmt numFmtId="171" formatCode="0.000"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -8850,8 +8881,16 @@
       <name val="Tahoma"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF050505"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8934,6 +8973,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0F5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -9213,7 +9258,7 @@
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -9409,6 +9454,10 @@
     <xf numFmtId="2" fontId="4" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="171" fontId="4" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="22">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
@@ -10282,15 +10331,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>2325972</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>150514</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -12509,6 +12558,989 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="B1:V36"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.140625" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="B1" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" s="9" t="str">
+        <f>'EB1'!G$2</f>
+        <v>DSL</v>
+      </c>
+      <c r="D2" s="9" t="str">
+        <f>'EB1'!G$3</f>
+        <v>Diesel oil</v>
+      </c>
+      <c r="E2" s="9" t="str">
+        <f>'EB1'!$Z$2</f>
+        <v>PJ</v>
+      </c>
+      <c r="F2" s="9" t="str">
+        <f>'EB1'!Y2</f>
+        <v>M€2025</v>
+      </c>
+      <c r="H2" s="91" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="91"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="92"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="92"/>
+    </row>
+    <row r="3" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C3" s="9" t="str">
+        <f>'EB1'!H$2</f>
+        <v>KER</v>
+      </c>
+      <c r="D3" s="9" t="str">
+        <f>'EB1'!H$3</f>
+        <v>Kerosenes</v>
+      </c>
+      <c r="E3" s="9" t="str">
+        <f>'EB1'!$Z$2</f>
+        <v>PJ</v>
+      </c>
+      <c r="H3" s="93" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="94" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="93" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="93" t="s">
+        <v>3</v>
+      </c>
+      <c r="L3" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="M3" s="93" t="s">
+        <v>8</v>
+      </c>
+      <c r="N3" s="93" t="s">
+        <v>9</v>
+      </c>
+      <c r="O3" s="93" t="s">
+        <v>10</v>
+      </c>
+      <c r="P3" s="93" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="9" t="str">
+        <f>'EB1'!I$2</f>
+        <v>LPG</v>
+      </c>
+      <c r="D4" s="9" t="str">
+        <f>'EB1'!I$3</f>
+        <v>LPG</v>
+      </c>
+      <c r="E4" s="9" t="str">
+        <f>'EB1'!$Z$2</f>
+        <v>PJ</v>
+      </c>
+      <c r="H4" s="95" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="95" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="95" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="95" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="95" t="s">
+        <v>4</v>
+      </c>
+      <c r="M4" s="95" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4" s="95" t="s">
+        <v>41</v>
+      </c>
+      <c r="O4" s="95" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" s="95" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C5" s="9" t="str">
+        <f>'EB1'!J$2</f>
+        <v>GSL</v>
+      </c>
+      <c r="D5" s="9" t="str">
+        <f>'EB1'!J$3</f>
+        <v>Motor spirit</v>
+      </c>
+      <c r="E5" s="9" t="str">
+        <f>'EB1'!$Z$2</f>
+        <v>PJ</v>
+      </c>
+      <c r="H5" s="92" t="s">
+        <v>65</v>
+      </c>
+      <c r="I5" s="96"/>
+      <c r="J5" s="92" t="str">
+        <f t="shared" ref="J5:K11" si="0">C2</f>
+        <v>DSL</v>
+      </c>
+      <c r="K5" s="92" t="str">
+        <f t="shared" si="0"/>
+        <v>Diesel oil</v>
+      </c>
+      <c r="L5" s="92" t="str">
+        <f t="shared" ref="L5:L11" si="1">$E$2</f>
+        <v>PJ</v>
+      </c>
+      <c r="M5" s="92"/>
+      <c r="N5" s="92"/>
+      <c r="O5" s="92"/>
+      <c r="P5" s="92"/>
+    </row>
+    <row r="6" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C6" s="9" t="str">
+        <f>'EB1'!K$2</f>
+        <v>NAP</v>
+      </c>
+      <c r="D6" s="9" t="str">
+        <f>'EB1'!K$3</f>
+        <v>Naphtha</v>
+      </c>
+      <c r="E6" s="9" t="str">
+        <f>'EB1'!$Z$2</f>
+        <v>PJ</v>
+      </c>
+      <c r="H6" s="92"/>
+      <c r="I6" s="96"/>
+      <c r="J6" s="92" t="str">
+        <f t="shared" si="0"/>
+        <v>KER</v>
+      </c>
+      <c r="K6" s="92" t="str">
+        <f t="shared" si="0"/>
+        <v>Kerosenes</v>
+      </c>
+      <c r="L6" s="92" t="str">
+        <f t="shared" si="1"/>
+        <v>PJ</v>
+      </c>
+      <c r="M6" s="92"/>
+      <c r="N6" s="92"/>
+      <c r="O6" s="92"/>
+      <c r="P6" s="92"/>
+    </row>
+    <row r="7" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C7" s="9" t="str">
+        <f>'EB1'!L$2</f>
+        <v>HFO</v>
+      </c>
+      <c r="D7" s="9" t="str">
+        <f>'EB1'!L$3</f>
+        <v>Heavy Fuel Oil</v>
+      </c>
+      <c r="E7" s="9" t="str">
+        <f>'EB1'!$Z$2</f>
+        <v>PJ</v>
+      </c>
+      <c r="H7" s="92"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="92" t="str">
+        <f t="shared" si="0"/>
+        <v>LPG</v>
+      </c>
+      <c r="K7" s="92" t="str">
+        <f t="shared" si="0"/>
+        <v>LPG</v>
+      </c>
+      <c r="L7" s="92" t="str">
+        <f t="shared" si="1"/>
+        <v>PJ</v>
+      </c>
+      <c r="M7" s="92"/>
+      <c r="N7" s="92"/>
+      <c r="O7" s="92"/>
+      <c r="P7" s="92"/>
+    </row>
+    <row r="8" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C8" s="9" t="str">
+        <f>'EB1'!M$2</f>
+        <v>OPP</v>
+      </c>
+      <c r="D8" s="9" t="str">
+        <f>'EB1'!M$3</f>
+        <v>Other Petroleum Products</v>
+      </c>
+      <c r="E8" s="9" t="str">
+        <f>'EB1'!$Z$2</f>
+        <v>PJ</v>
+      </c>
+      <c r="H8" s="92"/>
+      <c r="I8" s="96"/>
+      <c r="J8" s="92" t="str">
+        <f t="shared" si="0"/>
+        <v>GSL</v>
+      </c>
+      <c r="K8" s="92" t="str">
+        <f t="shared" si="0"/>
+        <v>Motor spirit</v>
+      </c>
+      <c r="L8" s="92" t="str">
+        <f t="shared" si="1"/>
+        <v>PJ</v>
+      </c>
+      <c r="M8" s="92"/>
+      <c r="N8" s="92"/>
+      <c r="O8" s="92"/>
+      <c r="P8" s="92"/>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="H9" s="92"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="92" t="str">
+        <f t="shared" si="0"/>
+        <v>NAP</v>
+      </c>
+      <c r="K9" s="92" t="str">
+        <f t="shared" si="0"/>
+        <v>Naphtha</v>
+      </c>
+      <c r="L9" s="92" t="str">
+        <f t="shared" si="1"/>
+        <v>PJ</v>
+      </c>
+      <c r="M9" s="92"/>
+      <c r="N9" s="92"/>
+      <c r="O9" s="92"/>
+      <c r="P9" s="92"/>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="H10" s="92"/>
+      <c r="I10" s="96"/>
+      <c r="J10" s="92" t="str">
+        <f t="shared" si="0"/>
+        <v>HFO</v>
+      </c>
+      <c r="K10" s="92" t="str">
+        <f t="shared" si="0"/>
+        <v>Heavy Fuel Oil</v>
+      </c>
+      <c r="L10" s="92" t="str">
+        <f t="shared" si="1"/>
+        <v>PJ</v>
+      </c>
+      <c r="M10" s="92"/>
+      <c r="N10" s="92"/>
+      <c r="O10" s="92"/>
+      <c r="P10" s="92"/>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="H11" s="92"/>
+      <c r="I11" s="96"/>
+      <c r="J11" s="92" t="str">
+        <f t="shared" si="0"/>
+        <v>OPP</v>
+      </c>
+      <c r="K11" s="92" t="str">
+        <f t="shared" si="0"/>
+        <v>Other Petroleum Products</v>
+      </c>
+      <c r="L11" s="92" t="str">
+        <f t="shared" si="1"/>
+        <v>PJ</v>
+      </c>
+      <c r="M11" s="92"/>
+      <c r="N11" s="92"/>
+      <c r="O11" s="92"/>
+      <c r="P11" s="92"/>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="D13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="H13" s="91" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="91"/>
+      <c r="J13" s="96"/>
+      <c r="K13" s="96"/>
+      <c r="L13" s="96"/>
+      <c r="M13" s="96"/>
+      <c r="N13" s="96"/>
+      <c r="O13" s="96"/>
+      <c r="P13" s="96"/>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="H14" s="93" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="94" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14" s="93" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="L14" s="93" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="93" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" s="93" t="s">
+        <v>18</v>
+      </c>
+      <c r="O14" s="93" t="s">
+        <v>19</v>
+      </c>
+      <c r="P14" s="93" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" s="95" t="s">
+        <v>38</v>
+      </c>
+      <c r="I15" s="95" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" s="95" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="95" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" s="95" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15" s="95" t="s">
+        <v>24</v>
+      </c>
+      <c r="N15" s="95" t="s">
+        <v>43</v>
+      </c>
+      <c r="O15" s="95" t="s">
+        <v>42</v>
+      </c>
+      <c r="P15" s="95" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11" t="str">
+        <f>$F$2&amp;"/"&amp;$E$2</f>
+        <v>M€2025/PJ</v>
+      </c>
+      <c r="F16" s="11" t="str">
+        <f>$E$2</f>
+        <v>PJ</v>
+      </c>
+      <c r="H16" s="95" t="s">
+        <v>73</v>
+      </c>
+      <c r="I16" s="95"/>
+      <c r="J16" s="95"/>
+      <c r="K16" s="95"/>
+      <c r="L16" s="95"/>
+      <c r="M16" s="95"/>
+      <c r="N16" s="95"/>
+      <c r="O16" s="95"/>
+      <c r="P16" s="95"/>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B17" s="1" t="str">
+        <f t="shared" ref="B17:B30" si="2">J17</f>
+        <v>IMPDSL1</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1" t="str">
+        <f t="shared" ref="D17:D23" si="3">C2</f>
+        <v>DSL</v>
+      </c>
+      <c r="E17" s="49">
+        <f>Pri_OIL!$F$11*1.3</f>
+        <v>10.4</v>
+      </c>
+      <c r="F17" s="44"/>
+      <c r="H17" s="96" t="str">
+        <f>'EB1'!$B$6</f>
+        <v>IMP</v>
+      </c>
+      <c r="I17" s="96"/>
+      <c r="J17" s="96" t="str">
+        <f t="shared" ref="J17:J23" si="4">$H$17&amp;C2&amp;1</f>
+        <v>IMPDSL1</v>
+      </c>
+      <c r="K17" s="98" t="str">
+        <f t="shared" ref="K17:K23" si="5">"Import of "&amp;D2&amp; " Step "&amp;RIGHT(J17,1)</f>
+        <v>Import of Diesel oil Step 1</v>
+      </c>
+      <c r="L17" s="96" t="str">
+        <f t="shared" ref="L17:L30" si="6">$E$2</f>
+        <v>PJ</v>
+      </c>
+      <c r="M17" s="96"/>
+      <c r="N17" s="96"/>
+      <c r="O17" s="96"/>
+      <c r="P17" s="96"/>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B18" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>IMPKER1</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>KER</v>
+      </c>
+      <c r="E18" s="49">
+        <f>Pri_OIL!$F$11*1.4</f>
+        <v>11.2</v>
+      </c>
+      <c r="F18" s="44"/>
+      <c r="H18" s="96"/>
+      <c r="I18" s="96"/>
+      <c r="J18" s="96" t="str">
+        <f t="shared" si="4"/>
+        <v>IMPKER1</v>
+      </c>
+      <c r="K18" s="98" t="str">
+        <f t="shared" si="5"/>
+        <v>Import of Kerosenes Step 1</v>
+      </c>
+      <c r="L18" s="96" t="str">
+        <f t="shared" si="6"/>
+        <v>PJ</v>
+      </c>
+      <c r="M18" s="96"/>
+      <c r="N18" s="96"/>
+      <c r="O18" s="96"/>
+      <c r="P18" s="96"/>
+      <c r="T18" s="1"/>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B19" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>IMPLPG1</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>LPG</v>
+      </c>
+      <c r="E19" s="49">
+        <f>Pri_OIL!$F$11*1.1</f>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="F19" s="44"/>
+      <c r="H19" s="96"/>
+      <c r="I19" s="96"/>
+      <c r="J19" s="96" t="str">
+        <f t="shared" si="4"/>
+        <v>IMPLPG1</v>
+      </c>
+      <c r="K19" s="98" t="str">
+        <f t="shared" si="5"/>
+        <v>Import of LPG Step 1</v>
+      </c>
+      <c r="L19" s="96" t="str">
+        <f t="shared" si="6"/>
+        <v>PJ</v>
+      </c>
+      <c r="M19" s="96"/>
+      <c r="N19" s="96"/>
+      <c r="O19" s="96"/>
+      <c r="P19" s="96"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B20" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>IMPGSL1</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>GSL</v>
+      </c>
+      <c r="E20" s="49">
+        <f>Pri_OIL!$F$11*1.4</f>
+        <v>11.2</v>
+      </c>
+      <c r="F20" s="44"/>
+      <c r="H20" s="96"/>
+      <c r="I20" s="96"/>
+      <c r="J20" s="96" t="str">
+        <f t="shared" si="4"/>
+        <v>IMPGSL1</v>
+      </c>
+      <c r="K20" s="98" t="str">
+        <f t="shared" si="5"/>
+        <v>Import of Motor spirit Step 1</v>
+      </c>
+      <c r="L20" s="96" t="str">
+        <f t="shared" si="6"/>
+        <v>PJ</v>
+      </c>
+      <c r="M20" s="96"/>
+      <c r="N20" s="96"/>
+      <c r="O20" s="96"/>
+      <c r="P20" s="96"/>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B21" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>IMPNAP1</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>NAP</v>
+      </c>
+      <c r="E21" s="49">
+        <f>Pri_OIL!$F$11*1.05</f>
+        <v>8.4</v>
+      </c>
+      <c r="F21" s="44"/>
+      <c r="H21" s="96"/>
+      <c r="I21" s="96"/>
+      <c r="J21" s="96" t="str">
+        <f t="shared" si="4"/>
+        <v>IMPNAP1</v>
+      </c>
+      <c r="K21" s="98" t="str">
+        <f t="shared" si="5"/>
+        <v>Import of Naphtha Step 1</v>
+      </c>
+      <c r="L21" s="96" t="str">
+        <f t="shared" si="6"/>
+        <v>PJ</v>
+      </c>
+      <c r="M21" s="96"/>
+      <c r="N21" s="96"/>
+      <c r="O21" s="96"/>
+      <c r="P21" s="96"/>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B22" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>IMPHFO1</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>HFO</v>
+      </c>
+      <c r="E22" s="49">
+        <f>Pri_OIL!$F$11*1.05</f>
+        <v>8.4</v>
+      </c>
+      <c r="F22" s="44"/>
+      <c r="H22" s="96"/>
+      <c r="I22" s="96"/>
+      <c r="J22" s="96" t="str">
+        <f t="shared" si="4"/>
+        <v>IMPHFO1</v>
+      </c>
+      <c r="K22" s="98" t="str">
+        <f t="shared" si="5"/>
+        <v>Import of Heavy Fuel Oil Step 1</v>
+      </c>
+      <c r="L22" s="96" t="str">
+        <f t="shared" si="6"/>
+        <v>PJ</v>
+      </c>
+      <c r="M22" s="96"/>
+      <c r="N22" s="96"/>
+      <c r="O22" s="96"/>
+      <c r="P22" s="96"/>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B23" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>IMPOPP1</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>OPP</v>
+      </c>
+      <c r="E23" s="49">
+        <f>Pri_OIL!$F$11*1.05</f>
+        <v>8.4</v>
+      </c>
+      <c r="F23" s="44"/>
+      <c r="H23" s="96"/>
+      <c r="I23" s="96"/>
+      <c r="J23" s="96" t="str">
+        <f t="shared" si="4"/>
+        <v>IMPOPP1</v>
+      </c>
+      <c r="K23" s="98" t="str">
+        <f t="shared" si="5"/>
+        <v>Import of Other Petroleum Products Step 1</v>
+      </c>
+      <c r="L23" s="96" t="str">
+        <f t="shared" si="6"/>
+        <v>PJ</v>
+      </c>
+      <c r="M23" s="96"/>
+      <c r="N23" s="96"/>
+      <c r="O23" s="96"/>
+      <c r="P23" s="96"/>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B24" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>EXPDSL1</v>
+      </c>
+      <c r="C24" s="1" t="str">
+        <f t="shared" ref="C24:C30" si="7">C2</f>
+        <v>DSL</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="49">
+        <f>E17*0.99</f>
+        <v>10.295999999999999</v>
+      </c>
+      <c r="F24" s="44"/>
+      <c r="H24" s="96" t="str">
+        <f>'EB1'!B7</f>
+        <v>EXP</v>
+      </c>
+      <c r="I24" s="96"/>
+      <c r="J24" s="96" t="str">
+        <f t="shared" ref="J24:J30" si="8">$H$24&amp;C2&amp;1</f>
+        <v>EXPDSL1</v>
+      </c>
+      <c r="K24" s="98" t="str">
+        <f t="shared" ref="K24:K30" si="9">"Export of "&amp;D2&amp; " Step "&amp;RIGHT(J24,1)</f>
+        <v>Export of Diesel oil Step 1</v>
+      </c>
+      <c r="L24" s="96" t="str">
+        <f t="shared" si="6"/>
+        <v>PJ</v>
+      </c>
+      <c r="M24" s="96"/>
+      <c r="N24" s="96"/>
+      <c r="O24" s="96"/>
+      <c r="P24" s="96"/>
+      <c r="S24" s="1"/>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B25" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>EXPKER1</v>
+      </c>
+      <c r="C25" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>KER</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="49">
+        <f t="shared" ref="E25:E30" si="10">E18*0.99</f>
+        <v>11.087999999999999</v>
+      </c>
+      <c r="F25" s="44"/>
+      <c r="H25" s="96"/>
+      <c r="I25" s="96"/>
+      <c r="J25" s="96" t="str">
+        <f t="shared" si="8"/>
+        <v>EXPKER1</v>
+      </c>
+      <c r="K25" s="98" t="str">
+        <f t="shared" si="9"/>
+        <v>Export of Kerosenes Step 1</v>
+      </c>
+      <c r="L25" s="96" t="str">
+        <f t="shared" si="6"/>
+        <v>PJ</v>
+      </c>
+      <c r="M25" s="96"/>
+      <c r="N25" s="96"/>
+      <c r="O25" s="96"/>
+      <c r="P25" s="96"/>
+      <c r="R25" s="1"/>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B26" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>EXPLPG1</v>
+      </c>
+      <c r="C26" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>LPG</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="49">
+        <f t="shared" si="10"/>
+        <v>8.7119999999999997</v>
+      </c>
+      <c r="F26" s="44"/>
+      <c r="H26" s="96"/>
+      <c r="I26" s="96"/>
+      <c r="J26" s="96" t="str">
+        <f t="shared" si="8"/>
+        <v>EXPLPG1</v>
+      </c>
+      <c r="K26" s="98" t="str">
+        <f t="shared" si="9"/>
+        <v>Export of LPG Step 1</v>
+      </c>
+      <c r="L26" s="96" t="str">
+        <f t="shared" si="6"/>
+        <v>PJ</v>
+      </c>
+      <c r="M26" s="96"/>
+      <c r="N26" s="96"/>
+      <c r="O26" s="96"/>
+      <c r="P26" s="96"/>
+    </row>
+    <row r="27" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B27" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>EXPGSL1</v>
+      </c>
+      <c r="C27" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>GSL</v>
+      </c>
+      <c r="D27" s="1"/>
+      <c r="E27" s="49">
+        <f t="shared" si="10"/>
+        <v>11.087999999999999</v>
+      </c>
+      <c r="F27" s="44"/>
+      <c r="H27" s="96"/>
+      <c r="I27" s="96"/>
+      <c r="J27" s="96" t="str">
+        <f t="shared" si="8"/>
+        <v>EXPGSL1</v>
+      </c>
+      <c r="K27" s="98" t="str">
+        <f t="shared" si="9"/>
+        <v>Export of Motor spirit Step 1</v>
+      </c>
+      <c r="L27" s="96" t="str">
+        <f t="shared" si="6"/>
+        <v>PJ</v>
+      </c>
+      <c r="M27" s="96"/>
+      <c r="N27" s="96"/>
+      <c r="O27" s="96"/>
+      <c r="P27" s="96"/>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B28" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>EXPNAP1</v>
+      </c>
+      <c r="C28" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>NAP</v>
+      </c>
+      <c r="D28" s="1"/>
+      <c r="E28" s="49">
+        <f t="shared" si="10"/>
+        <v>8.3160000000000007</v>
+      </c>
+      <c r="F28" s="44"/>
+      <c r="H28" s="96"/>
+      <c r="I28" s="96"/>
+      <c r="J28" s="96" t="str">
+        <f t="shared" si="8"/>
+        <v>EXPNAP1</v>
+      </c>
+      <c r="K28" s="98" t="str">
+        <f t="shared" si="9"/>
+        <v>Export of Naphtha Step 1</v>
+      </c>
+      <c r="L28" s="96" t="str">
+        <f t="shared" si="6"/>
+        <v>PJ</v>
+      </c>
+      <c r="M28" s="96"/>
+      <c r="N28" s="96"/>
+      <c r="O28" s="96"/>
+      <c r="P28" s="96"/>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B29" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>EXPHFO1</v>
+      </c>
+      <c r="C29" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>HFO</v>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="E29" s="49">
+        <f t="shared" si="10"/>
+        <v>8.3160000000000007</v>
+      </c>
+      <c r="F29" s="44"/>
+      <c r="H29" s="96"/>
+      <c r="I29" s="96"/>
+      <c r="J29" s="96" t="str">
+        <f>$H$24&amp;C7&amp;1</f>
+        <v>EXPHFO1</v>
+      </c>
+      <c r="K29" s="98" t="str">
+        <f t="shared" si="9"/>
+        <v>Export of Heavy Fuel Oil Step 1</v>
+      </c>
+      <c r="L29" s="96" t="str">
+        <f t="shared" si="6"/>
+        <v>PJ</v>
+      </c>
+      <c r="M29" s="96"/>
+      <c r="N29" s="96"/>
+      <c r="O29" s="96"/>
+      <c r="P29" s="96"/>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B30" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>EXPOPP1</v>
+      </c>
+      <c r="C30" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>OPP</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="E30" s="49">
+        <f t="shared" si="10"/>
+        <v>8.3160000000000007</v>
+      </c>
+      <c r="F30" s="44"/>
+      <c r="H30" s="96"/>
+      <c r="I30" s="96"/>
+      <c r="J30" s="96" t="str">
+        <f t="shared" si="8"/>
+        <v>EXPOPP1</v>
+      </c>
+      <c r="K30" s="98" t="str">
+        <f t="shared" si="9"/>
+        <v>Export of Other Petroleum Products Step 1</v>
+      </c>
+      <c r="L30" s="96" t="str">
+        <f t="shared" si="6"/>
+        <v>PJ</v>
+      </c>
+      <c r="M30" s="96"/>
+      <c r="N30" s="96"/>
+      <c r="O30" s="96"/>
+      <c r="P30" s="96"/>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B35" s="38"/>
+      <c r="C35" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B36" s="46"/>
+      <c r="C36" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B1:U22"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -12997,7 +14029,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B1:R24"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -13446,7 +14478,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="B4:S12"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -13625,6 +14657,71 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D56D8D7-E1A6-4544-9E5E-4BF2900A3B3E}">
+  <dimension ref="B3:G6"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D3" s="103">
+        <v>2020</v>
+      </c>
+      <c r="E3" s="103">
+        <v>2021</v>
+      </c>
+      <c r="F3" s="103">
+        <v>2022</v>
+      </c>
+      <c r="G3" s="103">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B4" s="104" t="s">
+        <v>180</v>
+      </c>
+      <c r="C4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B5" s="104"/>
+      <c r="C5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D5">
+        <v>369.77644024075659</v>
+      </c>
+      <c r="E5">
+        <v>418.15907136715379</v>
+      </c>
+      <c r="F5">
+        <v>347.09088564058459</v>
+      </c>
+      <c r="G5">
+        <v>269.10361134995702</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B6" s="104"/>
+      <c r="C6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B4:B6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:R23"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -14043,7 +15140,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CE3D601-8357-4014-BBD5-DE38AC19BE99}">
   <dimension ref="B1:Z26"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -14547,9 +15644,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:R24"/>
+  <dimension ref="B1:U21"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
@@ -14558,20 +15655,21 @@
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
     <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.7109375" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" customWidth="1"/>
-    <col min="8" max="8" width="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" customWidth="1"/>
-    <col min="10" max="10" width="7.140625" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.5703125" customWidth="1"/>
-    <col min="15" max="15" width="13" customWidth="1"/>
-    <col min="16" max="16" width="15.140625" customWidth="1"/>
-    <col min="17" max="17" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="10" width="15.28515625" customWidth="1"/>
+    <col min="11" max="11" width="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" customWidth="1"/>
+    <col min="13" max="13" width="7.140625" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="35" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.7109375" customWidth="1"/>
+    <col min="17" max="17" width="11.5703125" customWidth="1"/>
+    <col min="18" max="18" width="13" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" customWidth="1"/>
+    <col min="20" max="20" width="7.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:20" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="24" t="s">
         <v>66</v>
       </c>
@@ -14588,7 +15686,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="9"/>
       <c r="C2" s="9" t="str">
         <f>'EB1'!E2</f>
@@ -14606,117 +15704,128 @@
         <f>'EB1'!Y2</f>
         <v>M€2025</v>
       </c>
-      <c r="I2" s="91" t="s">
+      <c r="L2" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="91"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
+      <c r="M2" s="91"/>
       <c r="N2" s="92"/>
       <c r="O2" s="92"/>
       <c r="P2" s="92"/>
       <c r="Q2" s="92"/>
-    </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="I3" s="93" t="s">
+      <c r="R2" s="92"/>
+      <c r="S2" s="92"/>
+      <c r="T2" s="92"/>
+    </row>
+    <row r="3" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="L3" s="93" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="94" t="s">
+      <c r="M3" s="94" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="93" t="s">
+      <c r="N3" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="93" t="s">
+      <c r="O3" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="93" t="s">
+      <c r="P3" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="93" t="s">
+      <c r="Q3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="O3" s="93" t="s">
+      <c r="R3" s="93" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="93" t="s">
+      <c r="S3" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="Q3" s="93" t="s">
+      <c r="T3" s="93" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="1"/>
-      <c r="I4" s="95" t="s">
+    <row r="4" spans="2:20" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4">
+        <v>4.1868000000000002E-2</v>
+      </c>
+      <c r="L4" s="95" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="95" t="s">
+      <c r="M4" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="95" t="s">
+      <c r="N4" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="95" t="s">
+      <c r="O4" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="95" t="s">
+      <c r="P4" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="95" t="s">
+      <c r="Q4" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="O4" s="95" t="s">
+      <c r="R4" s="95" t="s">
         <v>41</v>
       </c>
-      <c r="P4" s="95" t="s">
+      <c r="S4" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="Q4" s="95" t="s">
+      <c r="T4" s="95" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="I5" s="92" t="s">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5">
+        <v>3.5999999999999998E-6</v>
+      </c>
+      <c r="L5" s="92" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="96"/>
-      <c r="K5" s="92" t="str">
+      <c r="M5" s="96"/>
+      <c r="N5" s="92" t="str">
         <f>C2</f>
         <v>GAS</v>
       </c>
-      <c r="L5" s="92" t="str">
+      <c r="O5" s="92" t="str">
         <f>D2</f>
         <v>Natural Gas</v>
       </c>
-      <c r="M5" s="92" t="str">
+      <c r="P5" s="92" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="N5" s="92"/>
-      <c r="O5" s="92"/>
-      <c r="P5" s="92"/>
       <c r="Q5" s="92"/>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R5" s="92"/>
+      <c r="S5" s="92"/>
+      <c r="T5" s="92"/>
+    </row>
+    <row r="7" spans="2:20" x14ac:dyDescent="0.2">
       <c r="D7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="4"/>
-      <c r="I7" s="91" t="s">
+      <c r="L7" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="91"/>
-      <c r="K7" s="96"/>
-      <c r="L7" s="96"/>
-      <c r="M7" s="96"/>
+      <c r="M7" s="91"/>
       <c r="N7" s="96"/>
       <c r="O7" s="96"/>
       <c r="P7" s="96"/>
       <c r="Q7" s="96"/>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="96"/>
+      <c r="S7" s="96"/>
+      <c r="T7" s="96"/>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
         <v>1</v>
       </c>
@@ -14733,37 +15842,46 @@
         <v>35</v>
       </c>
       <c r="G8" s="53" t="s">
-        <v>72</v>
-      </c>
-      <c r="I8" s="93" t="s">
+        <v>172</v>
+      </c>
+      <c r="H8" s="53" t="s">
+        <v>173</v>
+      </c>
+      <c r="I8" s="53" t="s">
+        <v>174</v>
+      </c>
+      <c r="J8" s="53" t="s">
+        <v>175</v>
+      </c>
+      <c r="L8" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="J8" s="94" t="s">
+      <c r="M8" s="94" t="s">
         <v>30</v>
       </c>
-      <c r="K8" s="93" t="s">
+      <c r="N8" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="L8" s="93" t="s">
+      <c r="O8" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="M8" s="93" t="s">
+      <c r="P8" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="93" t="s">
+      <c r="Q8" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="O8" s="93" t="s">
+      <c r="R8" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="P8" s="93" t="s">
+      <c r="S8" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Q8" s="93" t="s">
+      <c r="T8" s="93" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:20" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
         <v>39</v>
       </c>
@@ -14782,35 +15900,44 @@
       <c r="G9" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I9" s="95" t="s">
+      <c r="H9" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="L9" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="J9" s="95" t="s">
+      <c r="M9" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="K9" s="95" t="s">
+      <c r="N9" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="95" t="s">
+      <c r="O9" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="M9" s="95" t="s">
+      <c r="P9" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="N9" s="95" t="s">
+      <c r="Q9" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="O9" s="95" t="s">
+      <c r="R9" s="95" t="s">
         <v>43</v>
       </c>
-      <c r="P9" s="95" t="s">
+      <c r="S9" s="95" t="s">
         <v>42</v>
       </c>
-      <c r="Q9" s="95" t="s">
+      <c r="T9" s="95" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:20" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="12" t="s">
         <v>77</v>
       </c>
@@ -14828,243 +15955,164 @@
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="I10" s="95" t="s">
+      <c r="H10" s="11" t="str">
+        <f t="shared" ref="H10:J10" si="0">$E$2</f>
+        <v>PJ</v>
+      </c>
+      <c r="I10" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PJ</v>
+      </c>
+      <c r="J10" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PJ</v>
+      </c>
+      <c r="L10" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="J10" s="97"/>
-      <c r="K10" s="97"/>
-      <c r="L10" s="97"/>
       <c r="M10" s="97"/>
       <c r="N10" s="97"/>
       <c r="O10" s="97"/>
       <c r="P10" s="97"/>
       <c r="Q10" s="97"/>
-    </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="97"/>
+      <c r="S10" s="97"/>
+      <c r="T10" s="97"/>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="str">
-        <f>K11</f>
-        <v>MINGAS1</v>
+        <f>N11</f>
+        <v>IMPGAS1</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="str">
-        <f>$K$5</f>
+        <f>$N$5</f>
         <v>GAS</v>
       </c>
-      <c r="E11" s="43"/>
       <c r="F11" s="49">
-        <v>3.6</v>
-      </c>
-      <c r="G11" s="45"/>
-      <c r="I11" s="92" t="str">
-        <f>'EB1'!$B$5</f>
-        <v>MIN</v>
-      </c>
-      <c r="J11" s="96"/>
-      <c r="K11" s="96" t="str">
-        <f>$I$11&amp;$C$2&amp;1</f>
-        <v>MINGAS1</v>
-      </c>
-      <c r="L11" s="98" t="str">
-        <f>"Domestic Supply of "&amp;$D$2&amp; " Step "&amp;RIGHT(K11,1)</f>
-        <v>Domestic Supply of Natural Gas Step 1</v>
-      </c>
-      <c r="M11" s="96" t="str">
+        <f>36/C5/1000000</f>
+        <v>10</v>
+      </c>
+      <c r="G11" s="45">
+        <f>'JRC-IDEES2023'!D5</f>
+        <v>369.77644024075659</v>
+      </c>
+      <c r="H11" s="45">
+        <f>'JRC-IDEES2023'!E5</f>
+        <v>418.15907136715379</v>
+      </c>
+      <c r="I11" s="45">
+        <f>'JRC-IDEES2023'!F5</f>
+        <v>347.09088564058459</v>
+      </c>
+      <c r="J11" s="45">
+        <f>'JRC-IDEES2023'!G5</f>
+        <v>269.10361134995702</v>
+      </c>
+      <c r="L11" s="96" t="str">
+        <f>'EB1'!$B$6</f>
+        <v>IMP</v>
+      </c>
+      <c r="M11" s="96"/>
+      <c r="N11" s="96" t="str">
+        <f>$L$11&amp;$C$2&amp;1</f>
+        <v>IMPGAS1</v>
+      </c>
+      <c r="O11" s="98" t="str">
+        <f>"Import of "&amp;$D$2&amp; " Step "&amp;RIGHT(N11,1)</f>
+        <v>Import of Natural Gas Step 1</v>
+      </c>
+      <c r="P11" s="96" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="N11" s="96" t="str">
+      <c r="Q11" s="96" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="O11" s="96"/>
-      <c r="P11" s="96"/>
-      <c r="Q11" s="96"/>
-    </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="96"/>
+      <c r="S11" s="96"/>
+      <c r="T11" s="96"/>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="str">
-        <f>K12</f>
-        <v>MINGAS2</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1" t="str">
-        <f>$K$5</f>
+        <f>N12</f>
+        <v>EXPGAS1</v>
+      </c>
+      <c r="C12" s="1" t="str">
+        <f>$N$5</f>
         <v>GAS</v>
       </c>
-      <c r="E12" s="43"/>
       <c r="F12" s="49">
-        <v>4.1399999999999997</v>
+        <f>36/C5/1000000</f>
+        <v>10</v>
       </c>
       <c r="G12" s="45"/>
-      <c r="I12" s="96"/>
-      <c r="J12" s="96"/>
-      <c r="K12" s="96" t="str">
-        <f>$I$11&amp;$C$2&amp;2</f>
-        <v>MINGAS2</v>
-      </c>
-      <c r="L12" s="98" t="str">
-        <f>"Domestic Supply of "&amp;$D$2&amp; " Step "&amp;RIGHT(K12,1)</f>
-        <v>Domestic Supply of Natural Gas Step 2</v>
-      </c>
-      <c r="M12" s="96" t="str">
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="L12" s="96" t="str">
+        <f>'EB1'!B7</f>
+        <v>EXP</v>
+      </c>
+      <c r="M12" s="96"/>
+      <c r="N12" s="96" t="str">
+        <f>$L$12&amp;$C$2&amp;1</f>
+        <v>EXPGAS1</v>
+      </c>
+      <c r="O12" s="98" t="str">
+        <f>"Export of "&amp;$D$2&amp; " Step "&amp;RIGHT(N12,1)</f>
+        <v>Export of Natural Gas Step 1</v>
+      </c>
+      <c r="P12" s="96" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="N12" s="96" t="str">
+      <c r="Q12" s="96" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="O12" s="96"/>
-      <c r="P12" s="96"/>
-      <c r="Q12" s="96"/>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B13" s="1" t="str">
-        <f>K13</f>
-        <v>MINGAS3</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1" t="str">
-        <f>$K$5</f>
-        <v>GAS</v>
-      </c>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49">
-        <v>5.4</v>
-      </c>
-      <c r="G13" s="43"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="96"/>
-      <c r="K13" s="96" t="str">
-        <f>$I$11&amp;$C$2&amp;3</f>
-        <v>MINGAS3</v>
-      </c>
-      <c r="L13" s="98" t="str">
-        <f>"Domestic Supply of "&amp;$D$2&amp; " Step "&amp;RIGHT(K13,1)</f>
-        <v>Domestic Supply of Natural Gas Step 3</v>
-      </c>
-      <c r="M13" s="96" t="str">
-        <f>$E$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="N13" s="96" t="str">
-        <f>$E$2&amp;"a"</f>
-        <v>PJa</v>
-      </c>
-      <c r="O13" s="96"/>
-      <c r="P13" s="96"/>
-      <c r="Q13" s="96"/>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B14" s="1" t="str">
-        <f>K14</f>
-        <v>IMPGAS1</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1" t="str">
-        <f>$K$5</f>
-        <v>GAS</v>
-      </c>
-      <c r="F14" s="49">
-        <v>4.5</v>
-      </c>
-      <c r="G14" s="45"/>
-      <c r="I14" s="96" t="str">
-        <f>'EB1'!$B$6</f>
-        <v>IMP</v>
-      </c>
-      <c r="J14" s="96"/>
-      <c r="K14" s="96" t="str">
-        <f>$I$14&amp;$C$2&amp;1</f>
-        <v>IMPGAS1</v>
-      </c>
-      <c r="L14" s="98" t="str">
-        <f>"Import of "&amp;$D$2&amp; " Step "&amp;RIGHT(K14,1)</f>
-        <v>Import of Natural Gas Step 1</v>
-      </c>
-      <c r="M14" s="96" t="str">
-        <f>$E$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="N14" s="96" t="str">
-        <f>$E$2&amp;"a"</f>
-        <v>PJa</v>
-      </c>
-      <c r="O14" s="96"/>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="96"/>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B15" s="1" t="str">
-        <f>K15</f>
-        <v>EXPGAS1</v>
-      </c>
-      <c r="C15" s="1" t="str">
-        <f>$K$5</f>
-        <v>GAS</v>
-      </c>
-      <c r="F15" s="49">
-        <v>4.5</v>
-      </c>
-      <c r="G15" s="45"/>
-      <c r="I15" s="96" t="str">
-        <f>'EB1'!B7</f>
-        <v>EXP</v>
-      </c>
-      <c r="J15" s="96"/>
-      <c r="K15" s="96" t="str">
-        <f>$I$15&amp;$C$2&amp;1</f>
-        <v>EXPGAS1</v>
-      </c>
-      <c r="L15" s="98" t="str">
-        <f>"Export of "&amp;$D$2&amp; " Step "&amp;RIGHT(K15,1)</f>
-        <v>Export of Natural Gas Step 1</v>
-      </c>
-      <c r="M15" s="96" t="str">
-        <f>$E$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="N15" s="96" t="str">
-        <f>$E$2&amp;"a"</f>
-        <v>PJa</v>
-      </c>
-      <c r="O15" s="96"/>
-      <c r="P15" s="96"/>
-      <c r="Q15" s="96"/>
-    </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B16" s="1"/>
-      <c r="F16" s="51"/>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B22" s="48"/>
-      <c r="C22" s="1" t="s">
+      <c r="R12" s="96"/>
+      <c r="S12" s="96"/>
+      <c r="T12" s="96"/>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B13" s="1"/>
+      <c r="F13" s="51"/>
+    </row>
+    <row r="19" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B19" s="48"/>
+      <c r="C19" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="23" spans="2:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="46"/>
-      <c r="C23" s="1" t="s">
+    <row r="20" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="46"/>
+      <c r="C20" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D23"/>
-      <c r="E23"/>
-      <c r="F23"/>
-      <c r="G23"/>
-      <c r="H23"/>
-      <c r="I23"/>
-      <c r="J23"/>
-      <c r="K23"/>
-      <c r="L23"/>
-      <c r="M23"/>
-      <c r="N23"/>
-      <c r="O23"/>
-      <c r="P23"/>
-      <c r="Q23"/>
-      <c r="R23"/>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="H24" s="1"/>
-      <c r="R24" s="1"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20"/>
+      <c r="K20"/>
+      <c r="L20"/>
+      <c r="M20"/>
+      <c r="N20"/>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+      <c r="R20"/>
+      <c r="S20"/>
+      <c r="T20"/>
+      <c r="U20"/>
+    </row>
+    <row r="21" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="K21" s="1"/>
+      <c r="U21" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15075,7 +16123,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:W21"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -15488,7 +16536,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:P24"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -15870,7 +16918,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:P26"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -16435,7 +17483,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96226FE7-BF63-468B-8CA5-904DC2B1D71B}">
   <dimension ref="B1:P26"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -16884,987 +17932,4 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="B1:V36"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" customWidth="1"/>
-    <col min="7" max="7" width="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.140625" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="B1" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="C2" s="9" t="str">
-        <f>'EB1'!G$2</f>
-        <v>DSL</v>
-      </c>
-      <c r="D2" s="9" t="str">
-        <f>'EB1'!G$3</f>
-        <v>Diesel oil</v>
-      </c>
-      <c r="E2" s="9" t="str">
-        <f>'EB1'!$Z$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="F2" s="9" t="str">
-        <f>'EB1'!Y2</f>
-        <v>M€2025</v>
-      </c>
-      <c r="H2" s="91" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="91"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
-      <c r="P2" s="92"/>
-    </row>
-    <row r="3" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C3" s="9" t="str">
-        <f>'EB1'!H$2</f>
-        <v>KER</v>
-      </c>
-      <c r="D3" s="9" t="str">
-        <f>'EB1'!H$3</f>
-        <v>Kerosenes</v>
-      </c>
-      <c r="E3" s="9" t="str">
-        <f>'EB1'!$Z$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="H3" s="93" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="94" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" s="93" t="s">
-        <v>0</v>
-      </c>
-      <c r="K3" s="93" t="s">
-        <v>3</v>
-      </c>
-      <c r="L3" s="93" t="s">
-        <v>4</v>
-      </c>
-      <c r="M3" s="93" t="s">
-        <v>8</v>
-      </c>
-      <c r="N3" s="93" t="s">
-        <v>9</v>
-      </c>
-      <c r="O3" s="93" t="s">
-        <v>10</v>
-      </c>
-      <c r="P3" s="93" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="9" t="str">
-        <f>'EB1'!I$2</f>
-        <v>LPG</v>
-      </c>
-      <c r="D4" s="9" t="str">
-        <f>'EB1'!I$3</f>
-        <v>LPG</v>
-      </c>
-      <c r="E4" s="9" t="str">
-        <f>'EB1'!$Z$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="H4" s="95" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" s="95" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="95" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" s="95" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="95" t="s">
-        <v>4</v>
-      </c>
-      <c r="M4" s="95" t="s">
-        <v>40</v>
-      </c>
-      <c r="N4" s="95" t="s">
-        <v>41</v>
-      </c>
-      <c r="O4" s="95" t="s">
-        <v>28</v>
-      </c>
-      <c r="P4" s="95" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C5" s="9" t="str">
-        <f>'EB1'!J$2</f>
-        <v>GSL</v>
-      </c>
-      <c r="D5" s="9" t="str">
-        <f>'EB1'!J$3</f>
-        <v>Motor spirit</v>
-      </c>
-      <c r="E5" s="9" t="str">
-        <f>'EB1'!$Z$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="H5" s="92" t="s">
-        <v>65</v>
-      </c>
-      <c r="I5" s="96"/>
-      <c r="J5" s="92" t="str">
-        <f t="shared" ref="J5:K11" si="0">C2</f>
-        <v>DSL</v>
-      </c>
-      <c r="K5" s="92" t="str">
-        <f t="shared" si="0"/>
-        <v>Diesel oil</v>
-      </c>
-      <c r="L5" s="92" t="str">
-        <f t="shared" ref="L5:L11" si="1">$E$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="M5" s="92"/>
-      <c r="N5" s="92"/>
-      <c r="O5" s="92"/>
-      <c r="P5" s="92"/>
-    </row>
-    <row r="6" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C6" s="9" t="str">
-        <f>'EB1'!K$2</f>
-        <v>NAP</v>
-      </c>
-      <c r="D6" s="9" t="str">
-        <f>'EB1'!K$3</f>
-        <v>Naphtha</v>
-      </c>
-      <c r="E6" s="9" t="str">
-        <f>'EB1'!$Z$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="H6" s="92"/>
-      <c r="I6" s="96"/>
-      <c r="J6" s="92" t="str">
-        <f t="shared" si="0"/>
-        <v>KER</v>
-      </c>
-      <c r="K6" s="92" t="str">
-        <f t="shared" si="0"/>
-        <v>Kerosenes</v>
-      </c>
-      <c r="L6" s="92" t="str">
-        <f t="shared" si="1"/>
-        <v>PJ</v>
-      </c>
-      <c r="M6" s="92"/>
-      <c r="N6" s="92"/>
-      <c r="O6" s="92"/>
-      <c r="P6" s="92"/>
-    </row>
-    <row r="7" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C7" s="9" t="str">
-        <f>'EB1'!L$2</f>
-        <v>HFO</v>
-      </c>
-      <c r="D7" s="9" t="str">
-        <f>'EB1'!L$3</f>
-        <v>Heavy Fuel Oil</v>
-      </c>
-      <c r="E7" s="9" t="str">
-        <f>'EB1'!$Z$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="H7" s="92"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="92" t="str">
-        <f t="shared" si="0"/>
-        <v>LPG</v>
-      </c>
-      <c r="K7" s="92" t="str">
-        <f t="shared" si="0"/>
-        <v>LPG</v>
-      </c>
-      <c r="L7" s="92" t="str">
-        <f t="shared" si="1"/>
-        <v>PJ</v>
-      </c>
-      <c r="M7" s="92"/>
-      <c r="N7" s="92"/>
-      <c r="O7" s="92"/>
-      <c r="P7" s="92"/>
-    </row>
-    <row r="8" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C8" s="9" t="str">
-        <f>'EB1'!M$2</f>
-        <v>OPP</v>
-      </c>
-      <c r="D8" s="9" t="str">
-        <f>'EB1'!M$3</f>
-        <v>Other Petroleum Products</v>
-      </c>
-      <c r="E8" s="9" t="str">
-        <f>'EB1'!$Z$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="H8" s="92"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="92" t="str">
-        <f t="shared" si="0"/>
-        <v>GSL</v>
-      </c>
-      <c r="K8" s="92" t="str">
-        <f t="shared" si="0"/>
-        <v>Motor spirit</v>
-      </c>
-      <c r="L8" s="92" t="str">
-        <f t="shared" si="1"/>
-        <v>PJ</v>
-      </c>
-      <c r="M8" s="92"/>
-      <c r="N8" s="92"/>
-      <c r="O8" s="92"/>
-      <c r="P8" s="92"/>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="H9" s="92"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="92" t="str">
-        <f t="shared" si="0"/>
-        <v>NAP</v>
-      </c>
-      <c r="K9" s="92" t="str">
-        <f t="shared" si="0"/>
-        <v>Naphtha</v>
-      </c>
-      <c r="L9" s="92" t="str">
-        <f t="shared" si="1"/>
-        <v>PJ</v>
-      </c>
-      <c r="M9" s="92"/>
-      <c r="N9" s="92"/>
-      <c r="O9" s="92"/>
-      <c r="P9" s="92"/>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="H10" s="92"/>
-      <c r="I10" s="96"/>
-      <c r="J10" s="92" t="str">
-        <f t="shared" si="0"/>
-        <v>HFO</v>
-      </c>
-      <c r="K10" s="92" t="str">
-        <f t="shared" si="0"/>
-        <v>Heavy Fuel Oil</v>
-      </c>
-      <c r="L10" s="92" t="str">
-        <f t="shared" si="1"/>
-        <v>PJ</v>
-      </c>
-      <c r="M10" s="92"/>
-      <c r="N10" s="92"/>
-      <c r="O10" s="92"/>
-      <c r="P10" s="92"/>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="H11" s="92"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="92" t="str">
-        <f t="shared" si="0"/>
-        <v>OPP</v>
-      </c>
-      <c r="K11" s="92" t="str">
-        <f t="shared" si="0"/>
-        <v>Other Petroleum Products</v>
-      </c>
-      <c r="L11" s="92" t="str">
-        <f t="shared" si="1"/>
-        <v>PJ</v>
-      </c>
-      <c r="M11" s="92"/>
-      <c r="N11" s="92"/>
-      <c r="O11" s="92"/>
-      <c r="P11" s="92"/>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="D13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="H13" s="91" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="91"/>
-      <c r="J13" s="96"/>
-      <c r="K13" s="96"/>
-      <c r="L13" s="96"/>
-      <c r="M13" s="96"/>
-      <c r="N13" s="96"/>
-      <c r="O13" s="96"/>
-      <c r="P13" s="96"/>
-    </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B14" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="53" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="53" t="s">
-        <v>72</v>
-      </c>
-      <c r="H14" s="93" t="s">
-        <v>11</v>
-      </c>
-      <c r="I14" s="94" t="s">
-        <v>30</v>
-      </c>
-      <c r="J14" s="93" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" s="93" t="s">
-        <v>2</v>
-      </c>
-      <c r="L14" s="93" t="s">
-        <v>16</v>
-      </c>
-      <c r="M14" s="93" t="s">
-        <v>17</v>
-      </c>
-      <c r="N14" s="93" t="s">
-        <v>18</v>
-      </c>
-      <c r="O14" s="93" t="s">
-        <v>19</v>
-      </c>
-      <c r="P14" s="93" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="2:16" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="H15" s="95" t="s">
-        <v>38</v>
-      </c>
-      <c r="I15" s="95" t="s">
-        <v>31</v>
-      </c>
-      <c r="J15" s="95" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" s="95" t="s">
-        <v>22</v>
-      </c>
-      <c r="L15" s="95" t="s">
-        <v>23</v>
-      </c>
-      <c r="M15" s="95" t="s">
-        <v>24</v>
-      </c>
-      <c r="N15" s="95" t="s">
-        <v>43</v>
-      </c>
-      <c r="O15" s="95" t="s">
-        <v>42</v>
-      </c>
-      <c r="P15" s="95" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11" t="str">
-        <f>$F$2&amp;"/"&amp;$E$2</f>
-        <v>M€2025/PJ</v>
-      </c>
-      <c r="F16" s="11" t="str">
-        <f>$E$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="H16" s="95" t="s">
-        <v>73</v>
-      </c>
-      <c r="I16" s="95"/>
-      <c r="J16" s="95"/>
-      <c r="K16" s="95"/>
-      <c r="L16" s="95"/>
-      <c r="M16" s="95"/>
-      <c r="N16" s="95"/>
-      <c r="O16" s="95"/>
-      <c r="P16" s="95"/>
-    </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B17" s="1" t="str">
-        <f t="shared" ref="B17:B30" si="2">J17</f>
-        <v>IMPDSL1</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1" t="str">
-        <f t="shared" ref="D17:D23" si="3">C2</f>
-        <v>DSL</v>
-      </c>
-      <c r="E17" s="49">
-        <f>Pri_OIL!$F$11*1.3</f>
-        <v>10.4</v>
-      </c>
-      <c r="F17" s="44"/>
-      <c r="H17" s="96" t="str">
-        <f>'EB1'!$B$6</f>
-        <v>IMP</v>
-      </c>
-      <c r="I17" s="96"/>
-      <c r="J17" s="96" t="str">
-        <f t="shared" ref="J17:J23" si="4">$H$17&amp;C2&amp;1</f>
-        <v>IMPDSL1</v>
-      </c>
-      <c r="K17" s="98" t="str">
-        <f t="shared" ref="K17:K23" si="5">"Import of "&amp;D2&amp; " Step "&amp;RIGHT(J17,1)</f>
-        <v>Import of Diesel oil Step 1</v>
-      </c>
-      <c r="L17" s="96" t="str">
-        <f t="shared" ref="L17:L30" si="6">$E$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="M17" s="96"/>
-      <c r="N17" s="96"/>
-      <c r="O17" s="96"/>
-      <c r="P17" s="96"/>
-    </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B18" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>IMPKER1</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>KER</v>
-      </c>
-      <c r="E18" s="49">
-        <f>Pri_OIL!$F$11*1.4</f>
-        <v>11.2</v>
-      </c>
-      <c r="F18" s="44"/>
-      <c r="H18" s="96"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="96" t="str">
-        <f t="shared" si="4"/>
-        <v>IMPKER1</v>
-      </c>
-      <c r="K18" s="98" t="str">
-        <f t="shared" si="5"/>
-        <v>Import of Kerosenes Step 1</v>
-      </c>
-      <c r="L18" s="96" t="str">
-        <f t="shared" si="6"/>
-        <v>PJ</v>
-      </c>
-      <c r="M18" s="96"/>
-      <c r="N18" s="96"/>
-      <c r="O18" s="96"/>
-      <c r="P18" s="96"/>
-      <c r="T18" s="1"/>
-    </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B19" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>IMPLPG1</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>LPG</v>
-      </c>
-      <c r="E19" s="49">
-        <f>Pri_OIL!$F$11*1.1</f>
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="F19" s="44"/>
-      <c r="H19" s="96"/>
-      <c r="I19" s="96"/>
-      <c r="J19" s="96" t="str">
-        <f t="shared" si="4"/>
-        <v>IMPLPG1</v>
-      </c>
-      <c r="K19" s="98" t="str">
-        <f t="shared" si="5"/>
-        <v>Import of LPG Step 1</v>
-      </c>
-      <c r="L19" s="96" t="str">
-        <f t="shared" si="6"/>
-        <v>PJ</v>
-      </c>
-      <c r="M19" s="96"/>
-      <c r="N19" s="96"/>
-      <c r="O19" s="96"/>
-      <c r="P19" s="96"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
-    </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B20" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>IMPGSL1</v>
-      </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>GSL</v>
-      </c>
-      <c r="E20" s="49">
-        <f>Pri_OIL!$F$11*1.4</f>
-        <v>11.2</v>
-      </c>
-      <c r="F20" s="44"/>
-      <c r="H20" s="96"/>
-      <c r="I20" s="96"/>
-      <c r="J20" s="96" t="str">
-        <f t="shared" si="4"/>
-        <v>IMPGSL1</v>
-      </c>
-      <c r="K20" s="98" t="str">
-        <f t="shared" si="5"/>
-        <v>Import of Motor spirit Step 1</v>
-      </c>
-      <c r="L20" s="96" t="str">
-        <f t="shared" si="6"/>
-        <v>PJ</v>
-      </c>
-      <c r="M20" s="96"/>
-      <c r="N20" s="96"/>
-      <c r="O20" s="96"/>
-      <c r="P20" s="96"/>
-    </row>
-    <row r="21" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B21" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>IMPNAP1</v>
-      </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NAP</v>
-      </c>
-      <c r="E21" s="49">
-        <f>Pri_OIL!$F$11*1.05</f>
-        <v>8.4</v>
-      </c>
-      <c r="F21" s="44"/>
-      <c r="H21" s="96"/>
-      <c r="I21" s="96"/>
-      <c r="J21" s="96" t="str">
-        <f t="shared" si="4"/>
-        <v>IMPNAP1</v>
-      </c>
-      <c r="K21" s="98" t="str">
-        <f t="shared" si="5"/>
-        <v>Import of Naphtha Step 1</v>
-      </c>
-      <c r="L21" s="96" t="str">
-        <f t="shared" si="6"/>
-        <v>PJ</v>
-      </c>
-      <c r="M21" s="96"/>
-      <c r="N21" s="96"/>
-      <c r="O21" s="96"/>
-      <c r="P21" s="96"/>
-    </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B22" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>IMPHFO1</v>
-      </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>HFO</v>
-      </c>
-      <c r="E22" s="49">
-        <f>Pri_OIL!$F$11*1.05</f>
-        <v>8.4</v>
-      </c>
-      <c r="F22" s="44"/>
-      <c r="H22" s="96"/>
-      <c r="I22" s="96"/>
-      <c r="J22" s="96" t="str">
-        <f t="shared" si="4"/>
-        <v>IMPHFO1</v>
-      </c>
-      <c r="K22" s="98" t="str">
-        <f t="shared" si="5"/>
-        <v>Import of Heavy Fuel Oil Step 1</v>
-      </c>
-      <c r="L22" s="96" t="str">
-        <f t="shared" si="6"/>
-        <v>PJ</v>
-      </c>
-      <c r="M22" s="96"/>
-      <c r="N22" s="96"/>
-      <c r="O22" s="96"/>
-      <c r="P22" s="96"/>
-    </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B23" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>IMPOPP1</v>
-      </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>OPP</v>
-      </c>
-      <c r="E23" s="49">
-        <f>Pri_OIL!$F$11*1.05</f>
-        <v>8.4</v>
-      </c>
-      <c r="F23" s="44"/>
-      <c r="H23" s="96"/>
-      <c r="I23" s="96"/>
-      <c r="J23" s="96" t="str">
-        <f t="shared" si="4"/>
-        <v>IMPOPP1</v>
-      </c>
-      <c r="K23" s="98" t="str">
-        <f t="shared" si="5"/>
-        <v>Import of Other Petroleum Products Step 1</v>
-      </c>
-      <c r="L23" s="96" t="str">
-        <f t="shared" si="6"/>
-        <v>PJ</v>
-      </c>
-      <c r="M23" s="96"/>
-      <c r="N23" s="96"/>
-      <c r="O23" s="96"/>
-      <c r="P23" s="96"/>
-    </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B24" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>EXPDSL1</v>
-      </c>
-      <c r="C24" s="1" t="str">
-        <f t="shared" ref="C24:C30" si="7">C2</f>
-        <v>DSL</v>
-      </c>
-      <c r="D24" s="1"/>
-      <c r="E24" s="49">
-        <f>E17*0.99</f>
-        <v>10.295999999999999</v>
-      </c>
-      <c r="F24" s="44"/>
-      <c r="H24" s="96" t="str">
-        <f>'EB1'!B7</f>
-        <v>EXP</v>
-      </c>
-      <c r="I24" s="96"/>
-      <c r="J24" s="96" t="str">
-        <f t="shared" ref="J24:J30" si="8">$H$24&amp;C2&amp;1</f>
-        <v>EXPDSL1</v>
-      </c>
-      <c r="K24" s="98" t="str">
-        <f t="shared" ref="K24:K30" si="9">"Export of "&amp;D2&amp; " Step "&amp;RIGHT(J24,1)</f>
-        <v>Export of Diesel oil Step 1</v>
-      </c>
-      <c r="L24" s="96" t="str">
-        <f t="shared" si="6"/>
-        <v>PJ</v>
-      </c>
-      <c r="M24" s="96"/>
-      <c r="N24" s="96"/>
-      <c r="O24" s="96"/>
-      <c r="P24" s="96"/>
-      <c r="S24" s="1"/>
-    </row>
-    <row r="25" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B25" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>EXPKER1</v>
-      </c>
-      <c r="C25" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>KER</v>
-      </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="49">
-        <f t="shared" ref="E25:E30" si="10">E18*0.99</f>
-        <v>11.087999999999999</v>
-      </c>
-      <c r="F25" s="44"/>
-      <c r="H25" s="96"/>
-      <c r="I25" s="96"/>
-      <c r="J25" s="96" t="str">
-        <f t="shared" si="8"/>
-        <v>EXPKER1</v>
-      </c>
-      <c r="K25" s="98" t="str">
-        <f t="shared" si="9"/>
-        <v>Export of Kerosenes Step 1</v>
-      </c>
-      <c r="L25" s="96" t="str">
-        <f t="shared" si="6"/>
-        <v>PJ</v>
-      </c>
-      <c r="M25" s="96"/>
-      <c r="N25" s="96"/>
-      <c r="O25" s="96"/>
-      <c r="P25" s="96"/>
-      <c r="R25" s="1"/>
-    </row>
-    <row r="26" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B26" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>EXPLPG1</v>
-      </c>
-      <c r="C26" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>LPG</v>
-      </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="49">
-        <f t="shared" si="10"/>
-        <v>8.7119999999999997</v>
-      </c>
-      <c r="F26" s="44"/>
-      <c r="H26" s="96"/>
-      <c r="I26" s="96"/>
-      <c r="J26" s="96" t="str">
-        <f t="shared" si="8"/>
-        <v>EXPLPG1</v>
-      </c>
-      <c r="K26" s="98" t="str">
-        <f t="shared" si="9"/>
-        <v>Export of LPG Step 1</v>
-      </c>
-      <c r="L26" s="96" t="str">
-        <f t="shared" si="6"/>
-        <v>PJ</v>
-      </c>
-      <c r="M26" s="96"/>
-      <c r="N26" s="96"/>
-      <c r="O26" s="96"/>
-      <c r="P26" s="96"/>
-    </row>
-    <row r="27" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B27" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>EXPGSL1</v>
-      </c>
-      <c r="C27" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>GSL</v>
-      </c>
-      <c r="D27" s="1"/>
-      <c r="E27" s="49">
-        <f t="shared" si="10"/>
-        <v>11.087999999999999</v>
-      </c>
-      <c r="F27" s="44"/>
-      <c r="H27" s="96"/>
-      <c r="I27" s="96"/>
-      <c r="J27" s="96" t="str">
-        <f t="shared" si="8"/>
-        <v>EXPGSL1</v>
-      </c>
-      <c r="K27" s="98" t="str">
-        <f t="shared" si="9"/>
-        <v>Export of Motor spirit Step 1</v>
-      </c>
-      <c r="L27" s="96" t="str">
-        <f t="shared" si="6"/>
-        <v>PJ</v>
-      </c>
-      <c r="M27" s="96"/>
-      <c r="N27" s="96"/>
-      <c r="O27" s="96"/>
-      <c r="P27" s="96"/>
-    </row>
-    <row r="28" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B28" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>EXPNAP1</v>
-      </c>
-      <c r="C28" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>NAP</v>
-      </c>
-      <c r="D28" s="1"/>
-      <c r="E28" s="49">
-        <f t="shared" si="10"/>
-        <v>8.3160000000000007</v>
-      </c>
-      <c r="F28" s="44"/>
-      <c r="H28" s="96"/>
-      <c r="I28" s="96"/>
-      <c r="J28" s="96" t="str">
-        <f t="shared" si="8"/>
-        <v>EXPNAP1</v>
-      </c>
-      <c r="K28" s="98" t="str">
-        <f t="shared" si="9"/>
-        <v>Export of Naphtha Step 1</v>
-      </c>
-      <c r="L28" s="96" t="str">
-        <f t="shared" si="6"/>
-        <v>PJ</v>
-      </c>
-      <c r="M28" s="96"/>
-      <c r="N28" s="96"/>
-      <c r="O28" s="96"/>
-      <c r="P28" s="96"/>
-    </row>
-    <row r="29" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B29" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>EXPHFO1</v>
-      </c>
-      <c r="C29" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>HFO</v>
-      </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="49">
-        <f t="shared" si="10"/>
-        <v>8.3160000000000007</v>
-      </c>
-      <c r="F29" s="44"/>
-      <c r="H29" s="96"/>
-      <c r="I29" s="96"/>
-      <c r="J29" s="96" t="str">
-        <f>$H$24&amp;C7&amp;1</f>
-        <v>EXPHFO1</v>
-      </c>
-      <c r="K29" s="98" t="str">
-        <f t="shared" si="9"/>
-        <v>Export of Heavy Fuel Oil Step 1</v>
-      </c>
-      <c r="L29" s="96" t="str">
-        <f t="shared" si="6"/>
-        <v>PJ</v>
-      </c>
-      <c r="M29" s="96"/>
-      <c r="N29" s="96"/>
-      <c r="O29" s="96"/>
-      <c r="P29" s="96"/>
-    </row>
-    <row r="30" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B30" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>EXPOPP1</v>
-      </c>
-      <c r="C30" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>OPP</v>
-      </c>
-      <c r="D30" s="1"/>
-      <c r="E30" s="49">
-        <f t="shared" si="10"/>
-        <v>8.3160000000000007</v>
-      </c>
-      <c r="F30" s="44"/>
-      <c r="H30" s="96"/>
-      <c r="I30" s="96"/>
-      <c r="J30" s="96" t="str">
-        <f t="shared" si="8"/>
-        <v>EXPOPP1</v>
-      </c>
-      <c r="K30" s="98" t="str">
-        <f t="shared" si="9"/>
-        <v>Export of Other Petroleum Products Step 1</v>
-      </c>
-      <c r="L30" s="96" t="str">
-        <f t="shared" si="6"/>
-        <v>PJ</v>
-      </c>
-      <c r="M30" s="96"/>
-      <c r="N30" s="96"/>
-      <c r="O30" s="96"/>
-      <c r="P30" s="96"/>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B35" s="38"/>
-      <c r="C35" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B36" s="46"/>
-      <c r="C36" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
-</worksheet>
 </file>
--- a/VT_EE_UPS_V01.xlsx
+++ b/VT_EE_UPS_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CE95D7-95B4-48CB-8162-2C6C133C6762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2632341B-47B6-42A1-B447-3D3298883F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -8709,9 +8709,9 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="General_)"/>
     <numFmt numFmtId="165" formatCode="\Te\x\t"/>
-    <numFmt numFmtId="171" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -8874,12 +8874,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -9448,13 +9442,13 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="4" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -13907,7 +13901,9 @@
       <c r="G16" s="100">
         <v>8.76</v>
       </c>
-      <c r="H16" s="100"/>
+      <c r="H16" s="100">
+        <v>0.9</v>
+      </c>
       <c r="J16" t="s">
         <v>60</v>
       </c>
@@ -13944,7 +13940,12 @@
       <c r="F17" s="102">
         <v>1.016</v>
       </c>
-      <c r="H17" s="51"/>
+      <c r="G17" s="100">
+        <v>8.76</v>
+      </c>
+      <c r="H17" s="100">
+        <v>0.9</v>
+      </c>
       <c r="J17" s="96" t="str">
         <f>'EB1'!B7</f>
         <v>EXP</v>
@@ -13984,7 +13985,12 @@
       <c r="F18" s="102">
         <v>0.85</v>
       </c>
-      <c r="H18" s="51"/>
+      <c r="G18" s="100">
+        <v>8.76</v>
+      </c>
+      <c r="H18" s="100">
+        <v>0.9</v>
+      </c>
       <c r="J18" t="s">
         <v>62</v>
       </c>

--- a/VT_EE_UPS_V01.xlsx
+++ b/VT_EE_UPS_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2632341B-47B6-42A1-B447-3D3298883F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF09819-58BB-44AA-AC4E-A143ECD38405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>

--- a/VT_EE_UPS_V01.xlsx
+++ b/VT_EE_UPS_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF09819-58BB-44AA-AC4E-A143ECD38405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B110F94D-8814-433C-A8F0-D3AFBF713ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="901" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -8153,7 +8153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="181">
   <si>
     <t>CommName</t>
   </si>
@@ -8663,9 +8663,6 @@
   </si>
   <si>
     <t>NCAP_PASTI</t>
-  </si>
-  <si>
-    <t>FLO_COST</t>
   </si>
   <si>
     <t>NCAP_AF</t>
@@ -8719,6 +8716,8 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="186"/>
     </font>
     <font>
       <sz val="10"/>
@@ -13723,7 +13722,7 @@
         <v>6</v>
       </c>
       <c r="E12" s="53" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="F12" s="53" t="s">
         <v>169</v>
@@ -13732,7 +13731,7 @@
         <v>159</v>
       </c>
       <c r="H12" s="99" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J12" s="93" t="s">
         <v>11</v>
@@ -14672,7 +14671,7 @@
   <sheetData>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D3" s="103">
         <v>2020</v>
@@ -14689,16 +14688,16 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="104" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="104"/>
       <c r="C5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D5">
         <v>369.77644024075659</v>
@@ -14716,7 +14715,7 @@
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B6" s="104"/>
       <c r="C6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -15491,7 +15490,7 @@
       </c>
     </row>
     <row r="11" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="B11" s="1" t="str">
+      <c r="B11" s="92" t="str">
         <f>K11</f>
         <v>MINSHL1</v>
       </c>
@@ -15788,7 +15787,7 @@
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C5">
         <v>3.5999999999999998E-6</v>
@@ -15848,16 +15847,16 @@
         <v>35</v>
       </c>
       <c r="G8" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="H8" s="53" t="s">
         <v>172</v>
       </c>
-      <c r="H8" s="53" t="s">
+      <c r="I8" s="53" t="s">
         <v>173</v>
       </c>
-      <c r="I8" s="53" t="s">
+      <c r="J8" s="53" t="s">
         <v>174</v>
-      </c>
-      <c r="J8" s="53" t="s">
-        <v>175</v>
       </c>
       <c r="L8" s="93" t="s">
         <v>11</v>
@@ -15995,10 +15994,7 @@
         <f>$N$5</f>
         <v>GAS</v>
       </c>
-      <c r="F11" s="49">
-        <f>36/C5/1000000</f>
-        <v>10</v>
-      </c>
+      <c r="F11" s="49"/>
       <c r="G11" s="45">
         <f>'JRC-IDEES2023'!D5</f>
         <v>369.77644024075659</v>
@@ -16049,10 +16045,7 @@
         <f>$N$5</f>
         <v>GAS</v>
       </c>
-      <c r="F12" s="49">
-        <f>36/C5/1000000</f>
-        <v>10</v>
-      </c>
+      <c r="F12" s="49"/>
       <c r="G12" s="45"/>
       <c r="H12" s="45"/>
       <c r="I12" s="45"/>
@@ -17826,7 +17819,9 @@
         <f>J5</f>
         <v>MSW</v>
       </c>
-      <c r="E14" s="38"/>
+      <c r="E14" s="38">
+        <v>4.0500000000000007</v>
+      </c>
       <c r="F14" s="55"/>
       <c r="H14" s="92" t="str">
         <f>'EB1'!$B$5</f>

--- a/VT_EE_UPS_V01.xlsx
+++ b/VT_EE_UPS_V01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B110F94D-8814-433C-A8F0-D3AFBF713ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{262F1C52-D28D-482A-8B73-BC520FCE2075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="901" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8153,7 +8153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="182">
   <si>
     <t>CommName</t>
   </si>
@@ -8663,6 +8663,9 @@
   </si>
   <si>
     <t>NCAP_PASTI</t>
+  </si>
+  <si>
+    <t>FLO_COST</t>
   </si>
   <si>
     <t>NCAP_AF</t>
@@ -13722,7 +13725,7 @@
         <v>6</v>
       </c>
       <c r="E12" s="53" t="s">
-        <v>35</v>
+        <v>170</v>
       </c>
       <c r="F12" s="53" t="s">
         <v>169</v>
@@ -13731,7 +13734,7 @@
         <v>159</v>
       </c>
       <c r="H12" s="99" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J12" s="93" t="s">
         <v>11</v>
@@ -14671,7 +14674,7 @@
   <sheetData>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D3" s="103">
         <v>2020</v>
@@ -14688,16 +14691,16 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="104" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="104"/>
       <c r="C5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D5">
         <v>369.77644024075659</v>
@@ -14715,7 +14718,7 @@
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B6" s="104"/>
       <c r="C6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -15787,7 +15790,7 @@
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C5">
         <v>3.5999999999999998E-6</v>
@@ -15847,16 +15850,16 @@
         <v>35</v>
       </c>
       <c r="G8" s="53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H8" s="53" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I8" s="53" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J8" s="53" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L8" s="93" t="s">
         <v>11</v>

--- a/VT_EE_UPS_V01.xlsx
+++ b/VT_EE_UPS_V01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{262F1C52-D28D-482A-8B73-BC520FCE2075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8534A76-9D18-465B-A1CA-25D85EEDC245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="901" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="901" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -25,10 +25,9 @@
     <sheet name="Pri_PP" sheetId="148" r:id="rId10"/>
     <sheet name="Pri_ELC" sheetId="152" r:id="rId11"/>
     <sheet name="Con_REF" sheetId="147" r:id="rId12"/>
-    <sheet name="TOTCO2" sheetId="153" r:id="rId13"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId14"/>
+    <externalReference r:id="rId13"/>
   </externalReferences>
   <definedNames>
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
@@ -1560,317 +1559,6 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve"> (Heating Plant)</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Gary Goldstein</author>
-    <author>Amit Kanudia</author>
-    <author>Maurizio Gargiulo</author>
-  </authors>
-  <commentList>
-    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0A00-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Csets declarations are inherited until the next one is encountered.
-Allowed Cset:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>NRG</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Energy)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>ENV</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Emission)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>DEM</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Demand)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>MAT</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Material)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>FIN</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Financial)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G10" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0A00-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Amit Kanudia:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-LO for PRODUCTION &gt;= CONSUMPTION (Default)
-FX for PRODUCTION = CONSUMPTION
-UP for PRODUCTION &lt;= CONSUMPTION</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H10" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0A00-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Allowed CTSLvl</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-SEASON</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Seasonal level)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-WEEKLY</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Weekly level)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-DAYNITE</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (day and night level)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I10" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0A00-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Allowed PeakTS</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-ANNUAL </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(to generate Peak Equation for all the TimeSlices)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-User TS </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(to generate Peak Equation for a single TS)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J10" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0A00-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Allowed Ctype
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>ELC</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Electricity)</t>
         </r>
       </text>
     </comment>
@@ -8153,7 +7841,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="172">
   <si>
     <t>CommName</t>
   </si>
@@ -8563,36 +8251,6 @@
     <t>Crude Oil</t>
   </si>
   <si>
-    <t>~COMAGG</t>
-  </si>
-  <si>
-    <t>AGRCO2</t>
-  </si>
-  <si>
-    <t>COMCO2</t>
-  </si>
-  <si>
-    <t>RSDCO2</t>
-  </si>
-  <si>
-    <t>ELCCO2</t>
-  </si>
-  <si>
-    <t>TRACO2</t>
-  </si>
-  <si>
-    <t>INDCO2</t>
-  </si>
-  <si>
-    <t>TOTCO2</t>
-  </si>
-  <si>
-    <t>ENV</t>
-  </si>
-  <si>
-    <t>Total CO2</t>
-  </si>
-  <si>
     <t>M€2025</t>
   </si>
   <si>
@@ -8886,7 +8544,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8963,12 +8621,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -9254,7 +8906,7 @@
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -9417,15 +9069,6 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="10" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -9450,7 +9093,7 @@
     <xf numFmtId="2" fontId="4" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="4" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -9909,150 +9552,6 @@
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
             <a:t> technology to convert oil in petroleoum products.</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-GB" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>14653</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>153866</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="TextBox 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{638CCDDD-5884-4EF0-A47F-400CF431D28A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="611188" y="3309938"/>
-          <a:ext cx="5070840" cy="630116"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent6">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0" algn="l"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="1">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>~COMAGG </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>is used to define an aggregated commodity, TOTCO2</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>in this example, multiplying the sectoral</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> emissions by a coefficient 1 (cells C1:H1). It is possible to add more aggregated commodities and change multipliers.</a:t>
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
@@ -11739,7 +11238,7 @@
       </c>
       <c r="V2" s="26"/>
       <c r="Y2" s="35" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="Z2" s="9" t="s">
         <v>69</v>
@@ -12613,17 +12112,17 @@
         <f>'EB1'!Y2</f>
         <v>M€2025</v>
       </c>
-      <c r="H2" s="91" t="s">
+      <c r="H2" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="91"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
-      <c r="P2" s="92"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="87"/>
+      <c r="P2" s="87"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C3" s="9" t="str">
@@ -12638,31 +12137,31 @@
         <f>'EB1'!$Z$2</f>
         <v>PJ</v>
       </c>
-      <c r="H3" s="93" t="s">
+      <c r="H3" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="94" t="s">
+      <c r="I3" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="93" t="s">
+      <c r="J3" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="93" t="s">
+      <c r="K3" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="93" t="s">
+      <c r="L3" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="93" t="s">
+      <c r="M3" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="N3" s="93" t="s">
+      <c r="N3" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="O3" s="93" t="s">
+      <c r="O3" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="93" t="s">
+      <c r="P3" s="88" t="s">
         <v>12</v>
       </c>
     </row>
@@ -12679,31 +12178,31 @@
         <f>'EB1'!$Z$2</f>
         <v>PJ</v>
       </c>
-      <c r="H4" s="95" t="s">
+      <c r="H4" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="I4" s="95" t="s">
+      <c r="I4" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="95" t="s">
+      <c r="J4" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="95" t="s">
+      <c r="K4" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="L4" s="95" t="s">
+      <c r="L4" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="95" t="s">
+      <c r="M4" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="N4" s="95" t="s">
+      <c r="N4" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="O4" s="95" t="s">
+      <c r="O4" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="P4" s="95" t="s">
+      <c r="P4" s="90" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12720,26 +12219,26 @@
         <f>'EB1'!$Z$2</f>
         <v>PJ</v>
       </c>
-      <c r="H5" s="92" t="s">
+      <c r="H5" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="I5" s="96"/>
-      <c r="J5" s="92" t="str">
+      <c r="I5" s="91"/>
+      <c r="J5" s="87" t="str">
         <f t="shared" ref="J5:K11" si="0">C2</f>
         <v>DSL</v>
       </c>
-      <c r="K5" s="92" t="str">
+      <c r="K5" s="87" t="str">
         <f t="shared" si="0"/>
         <v>Diesel oil</v>
       </c>
-      <c r="L5" s="92" t="str">
+      <c r="L5" s="87" t="str">
         <f t="shared" ref="L5:L11" si="1">$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="M5" s="92"/>
-      <c r="N5" s="92"/>
-      <c r="O5" s="92"/>
-      <c r="P5" s="92"/>
+      <c r="M5" s="87"/>
+      <c r="N5" s="87"/>
+      <c r="O5" s="87"/>
+      <c r="P5" s="87"/>
     </row>
     <row r="6" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C6" s="9" t="str">
@@ -12754,24 +12253,24 @@
         <f>'EB1'!$Z$2</f>
         <v>PJ</v>
       </c>
-      <c r="H6" s="92"/>
-      <c r="I6" s="96"/>
-      <c r="J6" s="92" t="str">
+      <c r="H6" s="87"/>
+      <c r="I6" s="91"/>
+      <c r="J6" s="87" t="str">
         <f t="shared" si="0"/>
         <v>KER</v>
       </c>
-      <c r="K6" s="92" t="str">
+      <c r="K6" s="87" t="str">
         <f t="shared" si="0"/>
         <v>Kerosenes</v>
       </c>
-      <c r="L6" s="92" t="str">
+      <c r="L6" s="87" t="str">
         <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="M6" s="92"/>
-      <c r="N6" s="92"/>
-      <c r="O6" s="92"/>
-      <c r="P6" s="92"/>
+      <c r="M6" s="87"/>
+      <c r="N6" s="87"/>
+      <c r="O6" s="87"/>
+      <c r="P6" s="87"/>
     </row>
     <row r="7" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C7" s="9" t="str">
@@ -12786,24 +12285,24 @@
         <f>'EB1'!$Z$2</f>
         <v>PJ</v>
       </c>
-      <c r="H7" s="92"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="92" t="str">
+      <c r="H7" s="87"/>
+      <c r="I7" s="91"/>
+      <c r="J7" s="87" t="str">
         <f t="shared" si="0"/>
         <v>LPG</v>
       </c>
-      <c r="K7" s="92" t="str">
+      <c r="K7" s="87" t="str">
         <f t="shared" si="0"/>
         <v>LPG</v>
       </c>
-      <c r="L7" s="92" t="str">
+      <c r="L7" s="87" t="str">
         <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="M7" s="92"/>
-      <c r="N7" s="92"/>
-      <c r="O7" s="92"/>
-      <c r="P7" s="92"/>
+      <c r="M7" s="87"/>
+      <c r="N7" s="87"/>
+      <c r="O7" s="87"/>
+      <c r="P7" s="87"/>
     </row>
     <row r="8" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C8" s="9" t="str">
@@ -12818,101 +12317,101 @@
         <f>'EB1'!$Z$2</f>
         <v>PJ</v>
       </c>
-      <c r="H8" s="92"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="92" t="str">
+      <c r="H8" s="87"/>
+      <c r="I8" s="91"/>
+      <c r="J8" s="87" t="str">
         <f t="shared" si="0"/>
         <v>GSL</v>
       </c>
-      <c r="K8" s="92" t="str">
+      <c r="K8" s="87" t="str">
         <f t="shared" si="0"/>
         <v>Motor spirit</v>
       </c>
-      <c r="L8" s="92" t="str">
+      <c r="L8" s="87" t="str">
         <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="M8" s="92"/>
-      <c r="N8" s="92"/>
-      <c r="O8" s="92"/>
-      <c r="P8" s="92"/>
+      <c r="M8" s="87"/>
+      <c r="N8" s="87"/>
+      <c r="O8" s="87"/>
+      <c r="P8" s="87"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="H9" s="92"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="92" t="str">
+      <c r="H9" s="87"/>
+      <c r="I9" s="91"/>
+      <c r="J9" s="87" t="str">
         <f t="shared" si="0"/>
         <v>NAP</v>
       </c>
-      <c r="K9" s="92" t="str">
+      <c r="K9" s="87" t="str">
         <f t="shared" si="0"/>
         <v>Naphtha</v>
       </c>
-      <c r="L9" s="92" t="str">
+      <c r="L9" s="87" t="str">
         <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="M9" s="92"/>
-      <c r="N9" s="92"/>
-      <c r="O9" s="92"/>
-      <c r="P9" s="92"/>
+      <c r="M9" s="87"/>
+      <c r="N9" s="87"/>
+      <c r="O9" s="87"/>
+      <c r="P9" s="87"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="H10" s="92"/>
-      <c r="I10" s="96"/>
-      <c r="J10" s="92" t="str">
+      <c r="H10" s="87"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="87" t="str">
         <f t="shared" si="0"/>
         <v>HFO</v>
       </c>
-      <c r="K10" s="92" t="str">
+      <c r="K10" s="87" t="str">
         <f t="shared" si="0"/>
         <v>Heavy Fuel Oil</v>
       </c>
-      <c r="L10" s="92" t="str">
+      <c r="L10" s="87" t="str">
         <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="M10" s="92"/>
-      <c r="N10" s="92"/>
-      <c r="O10" s="92"/>
-      <c r="P10" s="92"/>
+      <c r="M10" s="87"/>
+      <c r="N10" s="87"/>
+      <c r="O10" s="87"/>
+      <c r="P10" s="87"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="H11" s="92"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="92" t="str">
+      <c r="H11" s="87"/>
+      <c r="I11" s="91"/>
+      <c r="J11" s="87" t="str">
         <f t="shared" si="0"/>
         <v>OPP</v>
       </c>
-      <c r="K11" s="92" t="str">
+      <c r="K11" s="87" t="str">
         <f t="shared" si="0"/>
         <v>Other Petroleum Products</v>
       </c>
-      <c r="L11" s="92" t="str">
+      <c r="L11" s="87" t="str">
         <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="M11" s="92"/>
-      <c r="N11" s="92"/>
-      <c r="O11" s="92"/>
-      <c r="P11" s="92"/>
+      <c r="M11" s="87"/>
+      <c r="N11" s="87"/>
+      <c r="O11" s="87"/>
+      <c r="P11" s="87"/>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.2">
       <c r="D13" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="4"/>
-      <c r="H13" s="91" t="s">
+      <c r="H13" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="91"/>
-      <c r="J13" s="96"/>
-      <c r="K13" s="96"/>
-      <c r="L13" s="96"/>
-      <c r="M13" s="96"/>
-      <c r="N13" s="96"/>
-      <c r="O13" s="96"/>
-      <c r="P13" s="96"/>
+      <c r="I13" s="86"/>
+      <c r="J13" s="91"/>
+      <c r="K13" s="91"/>
+      <c r="L13" s="91"/>
+      <c r="M13" s="91"/>
+      <c r="N13" s="91"/>
+      <c r="O13" s="91"/>
+      <c r="P13" s="91"/>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
@@ -12930,31 +12429,31 @@
       <c r="F14" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="H14" s="93" t="s">
+      <c r="H14" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="94" t="s">
+      <c r="I14" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="J14" s="93" t="s">
+      <c r="J14" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="K14" s="93" t="s">
+      <c r="K14" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="L14" s="93" t="s">
+      <c r="L14" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="M14" s="93" t="s">
+      <c r="M14" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="N14" s="93" t="s">
+      <c r="N14" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="O14" s="93" t="s">
+      <c r="O14" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="P14" s="93" t="s">
+      <c r="P14" s="88" t="s">
         <v>20</v>
       </c>
     </row>
@@ -12974,31 +12473,31 @@
       <c r="F15" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="H15" s="95" t="s">
+      <c r="H15" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="I15" s="95" t="s">
+      <c r="I15" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="J15" s="95" t="s">
+      <c r="J15" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="K15" s="95" t="s">
+      <c r="K15" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="L15" s="95" t="s">
+      <c r="L15" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="M15" s="95" t="s">
+      <c r="M15" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="N15" s="95" t="s">
+      <c r="N15" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="O15" s="95" t="s">
+      <c r="O15" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="P15" s="95" t="s">
+      <c r="P15" s="90" t="s">
         <v>25</v>
       </c>
     </row>
@@ -13016,17 +12515,17 @@
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="H16" s="95" t="s">
+      <c r="H16" s="90" t="s">
         <v>73</v>
       </c>
-      <c r="I16" s="95"/>
-      <c r="J16" s="95"/>
-      <c r="K16" s="95"/>
-      <c r="L16" s="95"/>
-      <c r="M16" s="95"/>
-      <c r="N16" s="95"/>
-      <c r="O16" s="95"/>
-      <c r="P16" s="95"/>
+      <c r="I16" s="90"/>
+      <c r="J16" s="90"/>
+      <c r="K16" s="90"/>
+      <c r="L16" s="90"/>
+      <c r="M16" s="90"/>
+      <c r="N16" s="90"/>
+      <c r="O16" s="90"/>
+      <c r="P16" s="90"/>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="str">
@@ -13043,27 +12542,27 @@
         <v>10.4</v>
       </c>
       <c r="F17" s="44"/>
-      <c r="H17" s="96" t="str">
+      <c r="H17" s="91" t="str">
         <f>'EB1'!$B$6</f>
         <v>IMP</v>
       </c>
-      <c r="I17" s="96"/>
-      <c r="J17" s="96" t="str">
+      <c r="I17" s="91"/>
+      <c r="J17" s="91" t="str">
         <f t="shared" ref="J17:J23" si="4">$H$17&amp;C2&amp;1</f>
         <v>IMPDSL1</v>
       </c>
-      <c r="K17" s="98" t="str">
+      <c r="K17" s="93" t="str">
         <f t="shared" ref="K17:K23" si="5">"Import of "&amp;D2&amp; " Step "&amp;RIGHT(J17,1)</f>
         <v>Import of Diesel oil Step 1</v>
       </c>
-      <c r="L17" s="96" t="str">
+      <c r="L17" s="91" t="str">
         <f t="shared" ref="L17:L30" si="6">$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="M17" s="96"/>
-      <c r="N17" s="96"/>
-      <c r="O17" s="96"/>
-      <c r="P17" s="96"/>
+      <c r="M17" s="91"/>
+      <c r="N17" s="91"/>
+      <c r="O17" s="91"/>
+      <c r="P17" s="91"/>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="str">
@@ -13080,24 +12579,24 @@
         <v>11.2</v>
       </c>
       <c r="F18" s="44"/>
-      <c r="H18" s="96"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="96" t="str">
+      <c r="H18" s="91"/>
+      <c r="I18" s="91"/>
+      <c r="J18" s="91" t="str">
         <f t="shared" si="4"/>
         <v>IMPKER1</v>
       </c>
-      <c r="K18" s="98" t="str">
+      <c r="K18" s="93" t="str">
         <f t="shared" si="5"/>
         <v>Import of Kerosenes Step 1</v>
       </c>
-      <c r="L18" s="96" t="str">
+      <c r="L18" s="91" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="M18" s="96"/>
-      <c r="N18" s="96"/>
-      <c r="O18" s="96"/>
-      <c r="P18" s="96"/>
+      <c r="M18" s="91"/>
+      <c r="N18" s="91"/>
+      <c r="O18" s="91"/>
+      <c r="P18" s="91"/>
       <c r="T18" s="1"/>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.2">
@@ -13115,24 +12614,24 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="F19" s="44"/>
-      <c r="H19" s="96"/>
-      <c r="I19" s="96"/>
-      <c r="J19" s="96" t="str">
+      <c r="H19" s="91"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="91" t="str">
         <f t="shared" si="4"/>
         <v>IMPLPG1</v>
       </c>
-      <c r="K19" s="98" t="str">
+      <c r="K19" s="93" t="str">
         <f t="shared" si="5"/>
         <v>Import of LPG Step 1</v>
       </c>
-      <c r="L19" s="96" t="str">
+      <c r="L19" s="91" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="M19" s="96"/>
-      <c r="N19" s="96"/>
-      <c r="O19" s="96"/>
-      <c r="P19" s="96"/>
+      <c r="M19" s="91"/>
+      <c r="N19" s="91"/>
+      <c r="O19" s="91"/>
+      <c r="P19" s="91"/>
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
     </row>
@@ -13151,24 +12650,24 @@
         <v>11.2</v>
       </c>
       <c r="F20" s="44"/>
-      <c r="H20" s="96"/>
-      <c r="I20" s="96"/>
-      <c r="J20" s="96" t="str">
+      <c r="H20" s="91"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="91" t="str">
         <f t="shared" si="4"/>
         <v>IMPGSL1</v>
       </c>
-      <c r="K20" s="98" t="str">
+      <c r="K20" s="93" t="str">
         <f t="shared" si="5"/>
         <v>Import of Motor spirit Step 1</v>
       </c>
-      <c r="L20" s="96" t="str">
+      <c r="L20" s="91" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="M20" s="96"/>
-      <c r="N20" s="96"/>
-      <c r="O20" s="96"/>
-      <c r="P20" s="96"/>
+      <c r="M20" s="91"/>
+      <c r="N20" s="91"/>
+      <c r="O20" s="91"/>
+      <c r="P20" s="91"/>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="str">
@@ -13185,24 +12684,24 @@
         <v>8.4</v>
       </c>
       <c r="F21" s="44"/>
-      <c r="H21" s="96"/>
-      <c r="I21" s="96"/>
-      <c r="J21" s="96" t="str">
+      <c r="H21" s="91"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="91" t="str">
         <f t="shared" si="4"/>
         <v>IMPNAP1</v>
       </c>
-      <c r="K21" s="98" t="str">
+      <c r="K21" s="93" t="str">
         <f t="shared" si="5"/>
         <v>Import of Naphtha Step 1</v>
       </c>
-      <c r="L21" s="96" t="str">
+      <c r="L21" s="91" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="M21" s="96"/>
-      <c r="N21" s="96"/>
-      <c r="O21" s="96"/>
-      <c r="P21" s="96"/>
+      <c r="M21" s="91"/>
+      <c r="N21" s="91"/>
+      <c r="O21" s="91"/>
+      <c r="P21" s="91"/>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="str">
@@ -13219,24 +12718,24 @@
         <v>8.4</v>
       </c>
       <c r="F22" s="44"/>
-      <c r="H22" s="96"/>
-      <c r="I22" s="96"/>
-      <c r="J22" s="96" t="str">
+      <c r="H22" s="91"/>
+      <c r="I22" s="91"/>
+      <c r="J22" s="91" t="str">
         <f t="shared" si="4"/>
         <v>IMPHFO1</v>
       </c>
-      <c r="K22" s="98" t="str">
+      <c r="K22" s="93" t="str">
         <f t="shared" si="5"/>
         <v>Import of Heavy Fuel Oil Step 1</v>
       </c>
-      <c r="L22" s="96" t="str">
+      <c r="L22" s="91" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="M22" s="96"/>
-      <c r="N22" s="96"/>
-      <c r="O22" s="96"/>
-      <c r="P22" s="96"/>
+      <c r="M22" s="91"/>
+      <c r="N22" s="91"/>
+      <c r="O22" s="91"/>
+      <c r="P22" s="91"/>
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="str">
@@ -13253,24 +12752,24 @@
         <v>8.4</v>
       </c>
       <c r="F23" s="44"/>
-      <c r="H23" s="96"/>
-      <c r="I23" s="96"/>
-      <c r="J23" s="96" t="str">
+      <c r="H23" s="91"/>
+      <c r="I23" s="91"/>
+      <c r="J23" s="91" t="str">
         <f t="shared" si="4"/>
         <v>IMPOPP1</v>
       </c>
-      <c r="K23" s="98" t="str">
+      <c r="K23" s="93" t="str">
         <f t="shared" si="5"/>
         <v>Import of Other Petroleum Products Step 1</v>
       </c>
-      <c r="L23" s="96" t="str">
+      <c r="L23" s="91" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="M23" s="96"/>
-      <c r="N23" s="96"/>
-      <c r="O23" s="96"/>
-      <c r="P23" s="96"/>
+      <c r="M23" s="91"/>
+      <c r="N23" s="91"/>
+      <c r="O23" s="91"/>
+      <c r="P23" s="91"/>
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="str">
@@ -13287,27 +12786,27 @@
         <v>10.295999999999999</v>
       </c>
       <c r="F24" s="44"/>
-      <c r="H24" s="96" t="str">
+      <c r="H24" s="91" t="str">
         <f>'EB1'!B7</f>
         <v>EXP</v>
       </c>
-      <c r="I24" s="96"/>
-      <c r="J24" s="96" t="str">
+      <c r="I24" s="91"/>
+      <c r="J24" s="91" t="str">
         <f t="shared" ref="J24:J30" si="8">$H$24&amp;C2&amp;1</f>
         <v>EXPDSL1</v>
       </c>
-      <c r="K24" s="98" t="str">
+      <c r="K24" s="93" t="str">
         <f t="shared" ref="K24:K30" si="9">"Export of "&amp;D2&amp; " Step "&amp;RIGHT(J24,1)</f>
         <v>Export of Diesel oil Step 1</v>
       </c>
-      <c r="L24" s="96" t="str">
+      <c r="L24" s="91" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="M24" s="96"/>
-      <c r="N24" s="96"/>
-      <c r="O24" s="96"/>
-      <c r="P24" s="96"/>
+      <c r="M24" s="91"/>
+      <c r="N24" s="91"/>
+      <c r="O24" s="91"/>
+      <c r="P24" s="91"/>
       <c r="S24" s="1"/>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.2">
@@ -13325,24 +12824,24 @@
         <v>11.087999999999999</v>
       </c>
       <c r="F25" s="44"/>
-      <c r="H25" s="96"/>
-      <c r="I25" s="96"/>
-      <c r="J25" s="96" t="str">
+      <c r="H25" s="91"/>
+      <c r="I25" s="91"/>
+      <c r="J25" s="91" t="str">
         <f t="shared" si="8"/>
         <v>EXPKER1</v>
       </c>
-      <c r="K25" s="98" t="str">
+      <c r="K25" s="93" t="str">
         <f t="shared" si="9"/>
         <v>Export of Kerosenes Step 1</v>
       </c>
-      <c r="L25" s="96" t="str">
+      <c r="L25" s="91" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="M25" s="96"/>
-      <c r="N25" s="96"/>
-      <c r="O25" s="96"/>
-      <c r="P25" s="96"/>
+      <c r="M25" s="91"/>
+      <c r="N25" s="91"/>
+      <c r="O25" s="91"/>
+      <c r="P25" s="91"/>
       <c r="R25" s="1"/>
     </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.2">
@@ -13360,24 +12859,24 @@
         <v>8.7119999999999997</v>
       </c>
       <c r="F26" s="44"/>
-      <c r="H26" s="96"/>
-      <c r="I26" s="96"/>
-      <c r="J26" s="96" t="str">
+      <c r="H26" s="91"/>
+      <c r="I26" s="91"/>
+      <c r="J26" s="91" t="str">
         <f t="shared" si="8"/>
         <v>EXPLPG1</v>
       </c>
-      <c r="K26" s="98" t="str">
+      <c r="K26" s="93" t="str">
         <f t="shared" si="9"/>
         <v>Export of LPG Step 1</v>
       </c>
-      <c r="L26" s="96" t="str">
+      <c r="L26" s="91" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="M26" s="96"/>
-      <c r="N26" s="96"/>
-      <c r="O26" s="96"/>
-      <c r="P26" s="96"/>
+      <c r="M26" s="91"/>
+      <c r="N26" s="91"/>
+      <c r="O26" s="91"/>
+      <c r="P26" s="91"/>
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="str">
@@ -13394,24 +12893,24 @@
         <v>11.087999999999999</v>
       </c>
       <c r="F27" s="44"/>
-      <c r="H27" s="96"/>
-      <c r="I27" s="96"/>
-      <c r="J27" s="96" t="str">
+      <c r="H27" s="91"/>
+      <c r="I27" s="91"/>
+      <c r="J27" s="91" t="str">
         <f t="shared" si="8"/>
         <v>EXPGSL1</v>
       </c>
-      <c r="K27" s="98" t="str">
+      <c r="K27" s="93" t="str">
         <f t="shared" si="9"/>
         <v>Export of Motor spirit Step 1</v>
       </c>
-      <c r="L27" s="96" t="str">
+      <c r="L27" s="91" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="M27" s="96"/>
-      <c r="N27" s="96"/>
-      <c r="O27" s="96"/>
-      <c r="P27" s="96"/>
+      <c r="M27" s="91"/>
+      <c r="N27" s="91"/>
+      <c r="O27" s="91"/>
+      <c r="P27" s="91"/>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="str">
@@ -13428,24 +12927,24 @@
         <v>8.3160000000000007</v>
       </c>
       <c r="F28" s="44"/>
-      <c r="H28" s="96"/>
-      <c r="I28" s="96"/>
-      <c r="J28" s="96" t="str">
+      <c r="H28" s="91"/>
+      <c r="I28" s="91"/>
+      <c r="J28" s="91" t="str">
         <f t="shared" si="8"/>
         <v>EXPNAP1</v>
       </c>
-      <c r="K28" s="98" t="str">
+      <c r="K28" s="93" t="str">
         <f t="shared" si="9"/>
         <v>Export of Naphtha Step 1</v>
       </c>
-      <c r="L28" s="96" t="str">
+      <c r="L28" s="91" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="M28" s="96"/>
-      <c r="N28" s="96"/>
-      <c r="O28" s="96"/>
-      <c r="P28" s="96"/>
+      <c r="M28" s="91"/>
+      <c r="N28" s="91"/>
+      <c r="O28" s="91"/>
+      <c r="P28" s="91"/>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="str">
@@ -13462,24 +12961,24 @@
         <v>8.3160000000000007</v>
       </c>
       <c r="F29" s="44"/>
-      <c r="H29" s="96"/>
-      <c r="I29" s="96"/>
-      <c r="J29" s="96" t="str">
+      <c r="H29" s="91"/>
+      <c r="I29" s="91"/>
+      <c r="J29" s="91" t="str">
         <f>$H$24&amp;C7&amp;1</f>
         <v>EXPHFO1</v>
       </c>
-      <c r="K29" s="98" t="str">
+      <c r="K29" s="93" t="str">
         <f t="shared" si="9"/>
         <v>Export of Heavy Fuel Oil Step 1</v>
       </c>
-      <c r="L29" s="96" t="str">
+      <c r="L29" s="91" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="M29" s="96"/>
-      <c r="N29" s="96"/>
-      <c r="O29" s="96"/>
-      <c r="P29" s="96"/>
+      <c r="M29" s="91"/>
+      <c r="N29" s="91"/>
+      <c r="O29" s="91"/>
+      <c r="P29" s="91"/>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="str">
@@ -13496,24 +12995,24 @@
         <v>8.3160000000000007</v>
       </c>
       <c r="F30" s="44"/>
-      <c r="H30" s="96"/>
-      <c r="I30" s="96"/>
-      <c r="J30" s="96" t="str">
+      <c r="H30" s="91"/>
+      <c r="I30" s="91"/>
+      <c r="J30" s="91" t="str">
         <f t="shared" si="8"/>
         <v>EXPOPP1</v>
       </c>
-      <c r="K30" s="98" t="str">
+      <c r="K30" s="93" t="str">
         <f t="shared" si="9"/>
         <v>Export of Other Petroleum Products Step 1</v>
       </c>
-      <c r="L30" s="96" t="str">
+      <c r="L30" s="91" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="M30" s="96"/>
-      <c r="N30" s="96"/>
-      <c r="O30" s="96"/>
-      <c r="P30" s="96"/>
+      <c r="M30" s="91"/>
+      <c r="N30" s="91"/>
+      <c r="O30" s="91"/>
+      <c r="P30" s="91"/>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B35" s="38"/>
@@ -13591,7 +13090,7 @@
         <v>Electricity</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="F2" s="9" t="str">
         <f>'EB1'!Y2</f>
@@ -13599,77 +13098,77 @@
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
-      <c r="J2" s="91" t="s">
+      <c r="J2" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="91"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
-      <c r="P2" s="92"/>
-      <c r="Q2" s="92"/>
-      <c r="R2" s="92"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="87"/>
+      <c r="P2" s="87"/>
+      <c r="Q2" s="87"/>
+      <c r="R2" s="87"/>
     </row>
     <row r="3" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
-      <c r="J3" s="93" t="s">
+      <c r="J3" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="94" t="s">
+      <c r="K3" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="93" t="s">
+      <c r="L3" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="M3" s="93" t="s">
+      <c r="M3" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="93" t="s">
+      <c r="N3" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="93" t="s">
+      <c r="O3" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="93" t="s">
+      <c r="P3" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="Q3" s="93" t="s">
+      <c r="Q3" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="R3" s="93" t="s">
+      <c r="R3" s="88" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="2:21" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
-      <c r="J4" s="95" t="s">
+      <c r="J4" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="95" t="s">
+      <c r="K4" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="95" t="s">
+      <c r="L4" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="95" t="s">
+      <c r="M4" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="95" t="s">
+      <c r="N4" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="O4" s="95" t="s">
+      <c r="O4" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="P4" s="95" t="s">
+      <c r="P4" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="Q4" s="95" t="s">
+      <c r="Q4" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="R4" s="95" t="s">
+      <c r="R4" s="90" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13702,17 +13201,17 @@
         <v>13</v>
       </c>
       <c r="E11" s="4"/>
-      <c r="J11" s="91" t="s">
+      <c r="J11" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="91"/>
-      <c r="L11" s="96"/>
-      <c r="M11" s="96"/>
-      <c r="N11" s="96"/>
-      <c r="O11" s="96"/>
-      <c r="P11" s="96"/>
-      <c r="Q11" s="96"/>
-      <c r="R11" s="96"/>
+      <c r="K11" s="86"/>
+      <c r="L11" s="91"/>
+      <c r="M11" s="91"/>
+      <c r="N11" s="91"/>
+      <c r="O11" s="91"/>
+      <c r="P11" s="91"/>
+      <c r="Q11" s="91"/>
+      <c r="R11" s="91"/>
     </row>
     <row r="12" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
@@ -13725,42 +13224,42 @@
         <v>6</v>
       </c>
       <c r="E12" s="53" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>169</v>
-      </c>
-      <c r="G12" s="99" t="s">
         <v>159</v>
       </c>
-      <c r="H12" s="99" t="s">
-        <v>171</v>
-      </c>
-      <c r="J12" s="93" t="s">
+      <c r="G12" s="94" t="s">
+        <v>149</v>
+      </c>
+      <c r="H12" s="94" t="s">
+        <v>161</v>
+      </c>
+      <c r="J12" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="K12" s="94" t="s">
+      <c r="K12" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="L12" s="93" t="s">
+      <c r="L12" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="M12" s="93" t="s">
+      <c r="M12" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="N12" s="93" t="s">
+      <c r="N12" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="O12" s="93" t="s">
+      <c r="O12" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="P12" s="93" t="s">
+      <c r="P12" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="Q12" s="93" t="s">
+      <c r="Q12" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="R12" s="93" t="s">
+      <c r="R12" s="88" t="s">
         <v>20</v>
       </c>
     </row>
@@ -13782,31 +13281,31 @@
       </c>
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
-      <c r="J13" s="95" t="s">
+      <c r="J13" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="K13" s="95" t="s">
+      <c r="K13" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="L13" s="95" t="s">
+      <c r="L13" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="M13" s="95" t="s">
+      <c r="M13" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="N13" s="95" t="s">
+      <c r="N13" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="O13" s="95" t="s">
+      <c r="O13" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="P13" s="95" t="s">
+      <c r="P13" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="Q13" s="95" t="s">
+      <c r="Q13" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="R13" s="95" t="s">
+      <c r="R13" s="90" t="s">
         <v>25</v>
       </c>
     </row>
@@ -13820,23 +13319,23 @@
         <f>$F$2&amp;"/"&amp;$E$2</f>
         <v>M€2025/TWh</v>
       </c>
-      <c r="F14" s="97" t="str">
+      <c r="F14" s="92" t="str">
         <f>O15</f>
         <v>GW</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
-      <c r="J14" s="95" t="s">
+      <c r="J14" s="90" t="s">
         <v>73</v>
       </c>
-      <c r="K14" s="95"/>
-      <c r="L14" s="95"/>
-      <c r="M14" s="95"/>
-      <c r="N14" s="95"/>
-      <c r="O14" s="95"/>
-      <c r="P14" s="95"/>
-      <c r="Q14" s="95"/>
-      <c r="R14" s="95"/>
+      <c r="K14" s="90"/>
+      <c r="L14" s="90"/>
+      <c r="M14" s="90"/>
+      <c r="N14" s="90"/>
+      <c r="O14" s="90"/>
+      <c r="P14" s="90"/>
+      <c r="Q14" s="90"/>
+      <c r="R14" s="90"/>
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="str">
@@ -13851,38 +13350,38 @@
       <c r="E15" s="49">
         <v>80.39</v>
       </c>
-      <c r="F15" s="101">
+      <c r="F15" s="96">
         <v>1.016</v>
       </c>
-      <c r="G15" s="100">
+      <c r="G15" s="95">
         <v>8.76</v>
       </c>
-      <c r="H15" s="100">
+      <c r="H15" s="95">
         <v>0.9</v>
       </c>
-      <c r="J15" s="96" t="str">
+      <c r="J15" s="91" t="str">
         <f>'EB1'!$B$6</f>
         <v>IMP</v>
       </c>
-      <c r="K15" s="96"/>
-      <c r="L15" s="96" t="s">
-        <v>161</v>
-      </c>
-      <c r="M15" s="98" t="s">
-        <v>160</v>
-      </c>
-      <c r="N15" s="96" t="str">
+      <c r="K15" s="91"/>
+      <c r="L15" s="91" t="s">
+        <v>151</v>
+      </c>
+      <c r="M15" s="93" t="s">
+        <v>150</v>
+      </c>
+      <c r="N15" s="91" t="str">
         <f>$E$2</f>
         <v>TWh</v>
       </c>
-      <c r="O15" s="96" t="s">
-        <v>168</v>
-      </c>
-      <c r="P15" s="92" t="s">
+      <c r="O15" s="91" t="s">
+        <v>158</v>
+      </c>
+      <c r="P15" s="87" t="s">
         <v>92</v>
       </c>
-      <c r="Q15" s="96"/>
-      <c r="R15" s="96"/>
+      <c r="Q15" s="91"/>
+      <c r="R15" s="91"/>
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="str">
@@ -13897,32 +13396,32 @@
       <c r="E16" s="49">
         <v>85.31</v>
       </c>
-      <c r="F16" s="101">
+      <c r="F16" s="96">
         <v>1.149</v>
       </c>
-      <c r="G16" s="100">
+      <c r="G16" s="95">
         <v>8.76</v>
       </c>
-      <c r="H16" s="100">
+      <c r="H16" s="95">
         <v>0.9</v>
       </c>
       <c r="J16" t="s">
         <v>60</v>
       </c>
       <c r="L16" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="M16" t="s">
-        <v>163</v>
-      </c>
-      <c r="N16" s="96" t="str">
+        <v>153</v>
+      </c>
+      <c r="N16" s="91" t="str">
         <f t="shared" ref="N16:N18" si="0">$E$2</f>
         <v>TWh</v>
       </c>
-      <c r="O16" s="96" t="s">
-        <v>168</v>
-      </c>
-      <c r="P16" s="92" t="s">
+      <c r="O16" s="91" t="s">
+        <v>158</v>
+      </c>
+      <c r="P16" s="87" t="s">
         <v>92</v>
       </c>
       <c r="U16" s="1"/>
@@ -13939,38 +13438,38 @@
       <c r="E17">
         <v>40.49</v>
       </c>
-      <c r="F17" s="102">
+      <c r="F17" s="97">
         <v>1.016</v>
       </c>
-      <c r="G17" s="100">
+      <c r="G17" s="95">
         <v>8.76</v>
       </c>
-      <c r="H17" s="100">
+      <c r="H17" s="95">
         <v>0.9</v>
       </c>
-      <c r="J17" s="96" t="str">
+      <c r="J17" s="91" t="str">
         <f>'EB1'!B7</f>
         <v>EXP</v>
       </c>
-      <c r="K17" s="96"/>
-      <c r="L17" s="96" t="s">
-        <v>164</v>
-      </c>
-      <c r="M17" s="98" t="s">
-        <v>165</v>
-      </c>
-      <c r="N17" s="96" t="str">
+      <c r="K17" s="91"/>
+      <c r="L17" s="91" t="s">
+        <v>154</v>
+      </c>
+      <c r="M17" s="93" t="s">
+        <v>155</v>
+      </c>
+      <c r="N17" s="91" t="str">
         <f t="shared" si="0"/>
         <v>TWh</v>
       </c>
-      <c r="O17" s="96" t="s">
-        <v>168</v>
-      </c>
-      <c r="P17" s="92" t="s">
+      <c r="O17" s="91" t="s">
+        <v>158</v>
+      </c>
+      <c r="P17" s="87" t="s">
         <v>92</v>
       </c>
-      <c r="Q17" s="96"/>
-      <c r="R17" s="96"/>
+      <c r="Q17" s="91"/>
+      <c r="R17" s="91"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="str">
@@ -13984,32 +13483,32 @@
       <c r="E18">
         <v>85.31</v>
       </c>
-      <c r="F18" s="102">
+      <c r="F18" s="97">
         <v>0.85</v>
       </c>
-      <c r="G18" s="100">
+      <c r="G18" s="95">
         <v>8.76</v>
       </c>
-      <c r="H18" s="100">
+      <c r="H18" s="95">
         <v>0.9</v>
       </c>
       <c r="J18" t="s">
         <v>62</v>
       </c>
       <c r="L18" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="M18" t="s">
-        <v>167</v>
-      </c>
-      <c r="N18" s="96" t="str">
+        <v>157</v>
+      </c>
+      <c r="N18" s="91" t="str">
         <f t="shared" si="0"/>
         <v>TWh</v>
       </c>
-      <c r="O18" s="96" t="s">
-        <v>168</v>
-      </c>
-      <c r="P18" s="92" t="s">
+      <c r="O18" s="91" t="s">
+        <v>158</v>
+      </c>
+      <c r="P18" s="87" t="s">
         <v>92</v>
       </c>
     </row>
@@ -14110,44 +13609,44 @@
       <c r="H2" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="J2" s="91" t="s">
+      <c r="J2" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="91"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
-      <c r="P2" s="92"/>
-      <c r="Q2" s="92"/>
-      <c r="R2" s="92"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="87"/>
+      <c r="P2" s="87"/>
+      <c r="Q2" s="87"/>
+      <c r="R2" s="87"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="J3" s="93" t="s">
+      <c r="J3" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="94" t="s">
+      <c r="K3" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="93" t="s">
+      <c r="L3" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="M3" s="93" t="s">
+      <c r="M3" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="93" t="s">
+      <c r="N3" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="93" t="s">
+      <c r="O3" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="93" t="s">
+      <c r="P3" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="Q3" s="93" t="s">
+      <c r="Q3" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="R3" s="93" t="s">
+      <c r="R3" s="88" t="s">
         <v>12</v>
       </c>
     </row>
@@ -14157,31 +13656,31 @@
       <c r="D4" s="32"/>
       <c r="E4" s="32"/>
       <c r="H4" s="82"/>
-      <c r="J4" s="95" t="s">
+      <c r="J4" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="95" t="s">
+      <c r="K4" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="95" t="s">
+      <c r="L4" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="95" t="s">
+      <c r="M4" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="95" t="s">
+      <c r="N4" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="O4" s="95" t="s">
+      <c r="O4" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="P4" s="95" t="s">
+      <c r="P4" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="Q4" s="95" t="s">
+      <c r="Q4" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="R4" s="95" t="s">
+      <c r="R4" s="90" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14204,17 +13703,17 @@
       <c r="F8" s="4"/>
       <c r="G8" s="81"/>
       <c r="H8" s="81"/>
-      <c r="J8" s="91" t="s">
+      <c r="J8" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="K8" s="91"/>
-      <c r="L8" s="92"/>
-      <c r="M8" s="92"/>
-      <c r="N8" s="92"/>
-      <c r="O8" s="92"/>
-      <c r="P8" s="92"/>
-      <c r="Q8" s="92"/>
-      <c r="R8" s="92"/>
+      <c r="K8" s="86"/>
+      <c r="L8" s="87"/>
+      <c r="M8" s="87"/>
+      <c r="N8" s="87"/>
+      <c r="O8" s="87"/>
+      <c r="P8" s="87"/>
+      <c r="Q8" s="87"/>
+      <c r="R8" s="87"/>
     </row>
     <row r="9" spans="2:18" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="14" t="s">
@@ -14237,31 +13736,31 @@
       </c>
       <c r="H9" s="83"/>
       <c r="I9" s="28"/>
-      <c r="J9" s="93" t="s">
+      <c r="J9" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="K9" s="94" t="s">
+      <c r="K9" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="L9" s="93" t="s">
+      <c r="L9" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="M9" s="93" t="s">
+      <c r="M9" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="N9" s="93" t="s">
+      <c r="N9" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="93" t="s">
+      <c r="O9" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="P9" s="93" t="s">
+      <c r="P9" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="Q9" s="93" t="s">
+      <c r="Q9" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="R9" s="93" t="s">
+      <c r="R9" s="88" t="s">
         <v>20</v>
       </c>
     </row>
@@ -14285,31 +13784,31 @@
         <v>107</v>
       </c>
       <c r="H10" s="84"/>
-      <c r="J10" s="95" t="s">
+      <c r="J10" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="K10" s="95" t="s">
+      <c r="K10" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="L10" s="95" t="s">
+      <c r="L10" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="M10" s="95" t="s">
+      <c r="M10" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="N10" s="95" t="s">
+      <c r="N10" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="O10" s="95" t="s">
+      <c r="O10" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="P10" s="95" t="s">
+      <c r="P10" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="Q10" s="95" t="s">
+      <c r="Q10" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="R10" s="95" t="s">
+      <c r="R10" s="90" t="s">
         <v>25</v>
       </c>
     </row>
@@ -14326,17 +13825,17 @@
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="85"/>
-      <c r="J11" s="95" t="s">
+      <c r="J11" s="90" t="s">
         <v>73</v>
       </c>
-      <c r="K11" s="95"/>
-      <c r="L11" s="95"/>
-      <c r="M11" s="95"/>
-      <c r="N11" s="95"/>
-      <c r="O11" s="95"/>
-      <c r="P11" s="95"/>
-      <c r="Q11" s="95"/>
-      <c r="R11" s="95"/>
+      <c r="K11" s="90"/>
+      <c r="L11" s="90"/>
+      <c r="M11" s="90"/>
+      <c r="N11" s="90"/>
+      <c r="O11" s="90"/>
+      <c r="P11" s="90"/>
+      <c r="Q11" s="90"/>
+      <c r="R11" s="90"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B12" s="27" t="str">
@@ -14361,31 +13860,31 @@
       </c>
       <c r="G12" s="45"/>
       <c r="H12" s="5"/>
-      <c r="J12" s="92" t="s">
+      <c r="J12" s="87" t="s">
         <v>87</v>
       </c>
-      <c r="K12" s="96"/>
-      <c r="L12" s="96" t="str">
+      <c r="K12" s="91"/>
+      <c r="L12" s="91" t="str">
         <f>$B$2&amp;$H$2&amp;'EB1'!F2&amp;"00"</f>
         <v>REFEOIL00</v>
       </c>
-      <c r="M12" s="98" t="str">
+      <c r="M12" s="93" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(L12,2)</f>
         <v>Refinery Existing00</v>
       </c>
-      <c r="N12" s="96" t="str">
+      <c r="N12" s="91" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O12" s="96" t="str">
+      <c r="O12" s="91" t="str">
         <f>$F$2</f>
         <v>Pja</v>
       </c>
-      <c r="P12" s="92"/>
-      <c r="Q12" s="92" t="s">
+      <c r="P12" s="87"/>
+      <c r="Q12" s="87" t="s">
         <v>110</v>
       </c>
-      <c r="R12" s="96"/>
+      <c r="R12" s="91"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.2">
       <c r="D13" s="27" t="str">
@@ -14478,184 +13977,6 @@
       <c r="C24" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="B4:S12"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="4" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B4" s="87" t="s">
-        <v>136</v>
-      </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-    </row>
-    <row r="5" spans="2:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="86" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="90" t="s">
-        <v>137</v>
-      </c>
-      <c r="D5" s="90" t="s">
-        <v>138</v>
-      </c>
-      <c r="E5" s="90" t="s">
-        <v>139</v>
-      </c>
-      <c r="F5" s="90" t="s">
-        <v>140</v>
-      </c>
-      <c r="G5" s="90" t="s">
-        <v>141</v>
-      </c>
-      <c r="H5" s="90" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B6" s="88" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" s="89">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="K7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-    </row>
-    <row r="9" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B9" s="91" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="91"/>
-      <c r="D9" s="92"/>
-      <c r="E9" s="92"/>
-      <c r="F9" s="92"/>
-      <c r="G9" s="92"/>
-      <c r="H9" s="92"/>
-      <c r="I9" s="92"/>
-      <c r="J9" s="92"/>
-    </row>
-    <row r="10" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B10" s="93" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="94" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="93" t="s">
-        <v>0</v>
-      </c>
-      <c r="E10" s="93" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="93" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="93" t="s">
-        <v>8</v>
-      </c>
-      <c r="H10" s="93" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="93" t="s">
-        <v>10</v>
-      </c>
-      <c r="J10" s="93" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="2:19" ht="34.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="95" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="95" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="95" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="95" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="95" t="s">
-        <v>4</v>
-      </c>
-      <c r="G11" s="95" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="95" t="s">
-        <v>41</v>
-      </c>
-      <c r="I11" s="95" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" s="95" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B12" s="92" t="s">
-        <v>144</v>
-      </c>
-      <c r="C12" s="96"/>
-      <c r="D12" s="92" t="str">
-        <f>B6</f>
-        <v>TOTCO2</v>
-      </c>
-      <c r="E12" s="92" t="s">
-        <v>145</v>
-      </c>
-      <c r="F12" s="92" t="str">
-        <f>'EB1'!AA2</f>
-        <v>kt</v>
-      </c>
-      <c r="G12" s="92"/>
-      <c r="H12" s="92"/>
-      <c r="I12" s="92"/>
-      <c r="J12" s="92"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14674,33 +13995,33 @@
   <sheetData>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D3" s="103">
+        <v>166</v>
+      </c>
+      <c r="D3" s="98">
         <v>2020</v>
       </c>
-      <c r="E3" s="103">
+      <c r="E3" s="98">
         <v>2021</v>
       </c>
-      <c r="F3" s="103">
+      <c r="F3" s="98">
         <v>2022</v>
       </c>
-      <c r="G3" s="103">
+      <c r="G3" s="98">
         <v>2023</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="104" t="s">
-        <v>180</v>
+      <c r="B4" s="99" t="s">
+        <v>170</v>
       </c>
       <c r="C4" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B5" s="104"/>
+      <c r="B5" s="99"/>
       <c r="C5" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="D5">
         <v>369.77644024075659</v>
@@ -14716,9 +14037,9 @@
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B6" s="104"/>
+      <c r="B6" s="99"/>
       <c r="C6" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -14788,115 +14109,115 @@
         <f>'EB1'!Y2</f>
         <v>M€2025</v>
       </c>
-      <c r="I2" s="91" t="s">
+      <c r="I2" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="91"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
-      <c r="P2" s="92"/>
-      <c r="Q2" s="92"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="87"/>
+      <c r="P2" s="87"/>
+      <c r="Q2" s="87"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="I3" s="93" t="s">
+      <c r="I3" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="94" t="s">
+      <c r="J3" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="93" t="s">
+      <c r="K3" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="93" t="s">
+      <c r="L3" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="93" t="s">
+      <c r="M3" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="93" t="s">
+      <c r="N3" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="O3" s="93" t="s">
+      <c r="O3" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="93" t="s">
+      <c r="P3" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="Q3" s="93" t="s">
+      <c r="Q3" s="88" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="2:17" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C4" s="1"/>
-      <c r="I4" s="95" t="s">
+      <c r="I4" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="95" t="s">
+      <c r="J4" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="95" t="s">
+      <c r="K4" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="95" t="s">
+      <c r="L4" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="95" t="s">
+      <c r="M4" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="95" t="s">
+      <c r="N4" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="O4" s="95" t="s">
+      <c r="O4" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="P4" s="95" t="s">
+      <c r="P4" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="Q4" s="95" t="s">
+      <c r="Q4" s="90" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="I5" s="92" t="s">
+      <c r="I5" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="96"/>
-      <c r="K5" s="92" t="str">
+      <c r="J5" s="91"/>
+      <c r="K5" s="87" t="str">
         <f>C2</f>
         <v>COA</v>
       </c>
-      <c r="L5" s="92" t="str">
+      <c r="L5" s="87" t="str">
         <f>D2</f>
         <v>Solid Fuels</v>
       </c>
-      <c r="M5" s="92" t="str">
+      <c r="M5" s="87" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="N5" s="92"/>
-      <c r="O5" s="92"/>
-      <c r="P5" s="92"/>
-      <c r="Q5" s="92"/>
+      <c r="N5" s="87"/>
+      <c r="O5" s="87"/>
+      <c r="P5" s="87"/>
+      <c r="Q5" s="87"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.2">
       <c r="D7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="4"/>
-      <c r="I7" s="91" t="s">
+      <c r="I7" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="91"/>
-      <c r="K7" s="96"/>
-      <c r="L7" s="96"/>
-      <c r="M7" s="96"/>
-      <c r="N7" s="96"/>
-      <c r="O7" s="96"/>
-      <c r="P7" s="96"/>
-      <c r="Q7" s="96"/>
+      <c r="J7" s="86"/>
+      <c r="K7" s="91"/>
+      <c r="L7" s="91"/>
+      <c r="M7" s="91"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="91"/>
+      <c r="P7" s="91"/>
+      <c r="Q7" s="91"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
@@ -14917,31 +14238,31 @@
       <c r="G8" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="I8" s="93" t="s">
+      <c r="I8" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="J8" s="94" t="s">
+      <c r="J8" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="K8" s="93" t="s">
+      <c r="K8" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="L8" s="93" t="s">
+      <c r="L8" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="M8" s="93" t="s">
+      <c r="M8" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="93" t="s">
+      <c r="N8" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="O8" s="93" t="s">
+      <c r="O8" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="P8" s="93" t="s">
+      <c r="P8" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="Q8" s="93" t="s">
+      <c r="Q8" s="88" t="s">
         <v>20</v>
       </c>
     </row>
@@ -14964,31 +14285,31 @@
       <c r="G9" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I9" s="95" t="s">
+      <c r="I9" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="J9" s="95" t="s">
+      <c r="J9" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="K9" s="95" t="s">
+      <c r="K9" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="95" t="s">
+      <c r="L9" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="M9" s="95" t="s">
+      <c r="M9" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="N9" s="95" t="s">
+      <c r="N9" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="O9" s="95" t="s">
+      <c r="O9" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="P9" s="95" t="s">
+      <c r="P9" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="Q9" s="95" t="s">
+      <c r="Q9" s="90" t="s">
         <v>25</v>
       </c>
     </row>
@@ -15010,17 +14331,17 @@
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="I10" s="95" t="s">
+      <c r="I10" s="90" t="s">
         <v>73</v>
       </c>
-      <c r="J10" s="97"/>
-      <c r="K10" s="97"/>
-      <c r="L10" s="97"/>
-      <c r="M10" s="97"/>
-      <c r="N10" s="97"/>
-      <c r="O10" s="97"/>
-      <c r="P10" s="97"/>
-      <c r="Q10" s="97"/>
+      <c r="J10" s="92"/>
+      <c r="K10" s="92"/>
+      <c r="L10" s="92"/>
+      <c r="M10" s="92"/>
+      <c r="N10" s="92"/>
+      <c r="O10" s="92"/>
+      <c r="P10" s="92"/>
+      <c r="Q10" s="92"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="str">
@@ -15035,30 +14356,30 @@
       <c r="E11" s="1"/>
       <c r="F11" s="50"/>
       <c r="G11" s="5"/>
-      <c r="I11" s="96" t="str">
+      <c r="I11" s="91" t="str">
         <f>'EB1'!$B$6</f>
         <v>IMP</v>
       </c>
-      <c r="J11" s="96"/>
-      <c r="K11" s="96" t="str">
+      <c r="J11" s="91"/>
+      <c r="K11" s="91" t="str">
         <f>$I$11&amp;$C$2&amp;1</f>
         <v>IMPCOA1</v>
       </c>
-      <c r="L11" s="98" t="str">
+      <c r="L11" s="93" t="str">
         <f>"Import of "&amp;$D$2&amp; " Step "&amp;RIGHT(K11,1)</f>
         <v>Import of Solid Fuels Step 1</v>
       </c>
-      <c r="M11" s="96" t="str">
+      <c r="M11" s="91" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="N11" s="96" t="str">
+      <c r="N11" s="91" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="O11" s="96"/>
-      <c r="P11" s="96"/>
-      <c r="Q11" s="96"/>
+      <c r="O11" s="91"/>
+      <c r="P11" s="91"/>
+      <c r="Q11" s="91"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="str">
@@ -15072,30 +14393,30 @@
       <c r="D12" s="1"/>
       <c r="F12" s="50"/>
       <c r="G12" s="45"/>
-      <c r="I12" s="96" t="str">
+      <c r="I12" s="91" t="str">
         <f>'EB1'!B7</f>
         <v>EXP</v>
       </c>
-      <c r="J12" s="96"/>
-      <c r="K12" s="96" t="str">
+      <c r="J12" s="91"/>
+      <c r="K12" s="91" t="str">
         <f>$I$12&amp;$C$2&amp;1</f>
         <v>EXPCOA1</v>
       </c>
-      <c r="L12" s="98" t="str">
+      <c r="L12" s="93" t="str">
         <f>"Export of "&amp;$D$2&amp; " Step "&amp;RIGHT(K12,1)</f>
         <v>Export of Solid Fuels Step 1</v>
       </c>
-      <c r="M12" s="96" t="str">
+      <c r="M12" s="91" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="N12" s="96" t="str">
+      <c r="N12" s="91" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="O12" s="96"/>
-      <c r="P12" s="96"/>
-      <c r="Q12" s="96"/>
+      <c r="O12" s="91"/>
+      <c r="P12" s="91"/>
+      <c r="Q12" s="91"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B13" s="1"/>
@@ -15196,10 +14517,10 @@
     <row r="2" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="9"/>
       <c r="C2" s="9" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E2" s="9" t="str">
         <f>'EB1'!Z2</f>
@@ -15209,107 +14530,107 @@
         <f>'EB1'!Y2</f>
         <v>M€2025</v>
       </c>
-      <c r="I2" s="91" t="s">
+      <c r="I2" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="91"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
-      <c r="P2" s="92"/>
-      <c r="Q2" s="92"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="87"/>
+      <c r="P2" s="87"/>
+      <c r="Q2" s="87"/>
     </row>
     <row r="3" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="I3" s="93" t="s">
+      <c r="I3" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="94" t="s">
+      <c r="J3" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="93" t="s">
+      <c r="K3" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="93" t="s">
+      <c r="L3" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="93" t="s">
+      <c r="M3" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="93" t="s">
+      <c r="N3" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="O3" s="93" t="s">
+      <c r="O3" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="93" t="s">
+      <c r="P3" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="Q3" s="93" t="s">
+      <c r="Q3" s="88" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="2:26" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C4">
         <v>4.1868000000000002E-2</v>
       </c>
-      <c r="I4" s="95" t="s">
+      <c r="I4" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="95" t="s">
+      <c r="J4" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="95" t="s">
+      <c r="K4" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="95" t="s">
+      <c r="L4" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="95" t="s">
+      <c r="M4" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="95" t="s">
+      <c r="N4" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="O4" s="95" t="s">
+      <c r="O4" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="P4" s="95" t="s">
+      <c r="P4" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="Q4" s="95" t="s">
+      <c r="Q4" s="90" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="I5" s="92" t="s">
+      <c r="I5" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="96"/>
-      <c r="K5" s="92" t="str">
+      <c r="J5" s="91"/>
+      <c r="K5" s="87" t="str">
         <f>C2</f>
         <v>SHL</v>
       </c>
-      <c r="L5" s="92" t="str">
+      <c r="L5" s="87" t="str">
         <f>D2</f>
         <v>Oil shale</v>
       </c>
-      <c r="M5" s="92" t="str">
+      <c r="M5" s="87" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="N5" s="92"/>
-      <c r="O5" s="92"/>
-      <c r="P5" s="92"/>
-      <c r="Q5" s="92"/>
+      <c r="N5" s="87"/>
+      <c r="O5" s="87"/>
+      <c r="P5" s="87"/>
+      <c r="Q5" s="87"/>
     </row>
     <row r="6" spans="2:26" x14ac:dyDescent="0.2">
       <c r="V6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="W6">
         <v>9.5</v>
@@ -15320,19 +14641,19 @@
         <v>13</v>
       </c>
       <c r="F7" s="4"/>
-      <c r="I7" s="91" t="s">
+      <c r="I7" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="91"/>
-      <c r="K7" s="96"/>
-      <c r="L7" s="96"/>
-      <c r="M7" s="96"/>
-      <c r="N7" s="96"/>
-      <c r="O7" s="96"/>
-      <c r="P7" s="96"/>
-      <c r="Q7" s="96"/>
+      <c r="J7" s="86"/>
+      <c r="K7" s="91"/>
+      <c r="L7" s="91"/>
+      <c r="M7" s="91"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="91"/>
+      <c r="P7" s="91"/>
+      <c r="Q7" s="91"/>
       <c r="V7" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="W7">
         <f>1000000000/(W6*1000)</f>
@@ -15358,31 +14679,31 @@
       <c r="G8" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="I8" s="93" t="s">
+      <c r="I8" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="J8" s="94" t="s">
+      <c r="J8" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="K8" s="93" t="s">
+      <c r="K8" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="L8" s="93" t="s">
+      <c r="L8" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="M8" s="93" t="s">
+      <c r="M8" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="93" t="s">
+      <c r="N8" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="O8" s="93" t="s">
+      <c r="O8" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="P8" s="93" t="s">
+      <c r="P8" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="Q8" s="93" t="s">
+      <c r="Q8" s="88" t="s">
         <v>20</v>
       </c>
     </row>
@@ -15405,44 +14726,44 @@
       <c r="G9" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I9" s="95" t="s">
+      <c r="I9" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="J9" s="95" t="s">
+      <c r="J9" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="K9" s="95" t="s">
+      <c r="K9" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="95" t="s">
+      <c r="L9" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="M9" s="95" t="s">
+      <c r="M9" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="N9" s="95" t="s">
+      <c r="N9" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="O9" s="95" t="s">
+      <c r="O9" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="P9" s="95" t="s">
+      <c r="P9" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="Q9" s="95" t="s">
+      <c r="Q9" s="90" t="s">
         <v>25</v>
       </c>
       <c r="W9" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="X9" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="Y9" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="Z9" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="2:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -15463,17 +14784,17 @@
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="I10" s="95" t="s">
+      <c r="I10" s="90" t="s">
         <v>73</v>
       </c>
-      <c r="J10" s="97"/>
-      <c r="K10" s="97"/>
-      <c r="L10" s="97"/>
-      <c r="M10" s="97"/>
-      <c r="N10" s="97"/>
-      <c r="O10" s="97"/>
-      <c r="P10" s="97"/>
-      <c r="Q10" s="97"/>
+      <c r="J10" s="92"/>
+      <c r="K10" s="92"/>
+      <c r="L10" s="92"/>
+      <c r="M10" s="92"/>
+      <c r="N10" s="92"/>
+      <c r="O10" s="92"/>
+      <c r="P10" s="92"/>
+      <c r="Q10" s="92"/>
       <c r="V10">
         <v>2025</v>
       </c>
@@ -15493,7 +14814,7 @@
       </c>
     </row>
     <row r="11" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="B11" s="92" t="str">
+      <c r="B11" s="87" t="str">
         <f>K11</f>
         <v>MINSHL1</v>
       </c>
@@ -15511,30 +14832,30 @@
         <f>X10</f>
         <v>76.200525999999996</v>
       </c>
-      <c r="I11" s="92" t="str">
+      <c r="I11" s="87" t="str">
         <f>'EB1'!$B$5</f>
         <v>MIN</v>
       </c>
-      <c r="J11" s="96"/>
-      <c r="K11" s="96" t="str">
+      <c r="J11" s="91"/>
+      <c r="K11" s="91" t="str">
         <f>$I$11&amp;$C$2&amp;1</f>
         <v>MINSHL1</v>
       </c>
-      <c r="L11" s="98" t="str">
+      <c r="L11" s="93" t="str">
         <f>"Domestic Supply of "&amp;$D$2&amp; " Step "&amp;RIGHT(K11,1)</f>
         <v>Domestic Supply of Oil shale Step 1</v>
       </c>
-      <c r="M11" s="96" t="str">
+      <c r="M11" s="91" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="N11" s="96" t="str">
+      <c r="N11" s="91" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="O11" s="96"/>
-      <c r="P11" s="96"/>
-      <c r="Q11" s="96"/>
+      <c r="O11" s="91"/>
+      <c r="P11" s="91"/>
+      <c r="Q11" s="91"/>
     </row>
     <row r="12" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B12" s="1"/>
@@ -15543,15 +14864,15 @@
       <c r="E12" s="48"/>
       <c r="F12" s="50"/>
       <c r="G12" s="44"/>
-      <c r="I12" s="96"/>
-      <c r="J12" s="96"/>
-      <c r="K12" s="96"/>
-      <c r="L12" s="98"/>
-      <c r="M12" s="96"/>
-      <c r="N12" s="96"/>
-      <c r="O12" s="96"/>
-      <c r="P12" s="96"/>
-      <c r="Q12" s="96"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="91"/>
+      <c r="K12" s="91"/>
+      <c r="L12" s="93"/>
+      <c r="M12" s="91"/>
+      <c r="N12" s="91"/>
+      <c r="O12" s="91"/>
+      <c r="P12" s="91"/>
+      <c r="Q12" s="91"/>
     </row>
     <row r="13" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B13" s="1"/>
@@ -15560,15 +14881,15 @@
       <c r="E13" s="48"/>
       <c r="F13" s="50"/>
       <c r="G13" s="10"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="96"/>
-      <c r="K13" s="96"/>
-      <c r="L13" s="98"/>
-      <c r="M13" s="96"/>
-      <c r="N13" s="96"/>
-      <c r="O13" s="96"/>
-      <c r="P13" s="96"/>
-      <c r="Q13" s="96"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="91"/>
+      <c r="K13" s="91"/>
+      <c r="L13" s="93"/>
+      <c r="M13" s="91"/>
+      <c r="N13" s="91"/>
+      <c r="O13" s="91"/>
+      <c r="P13" s="91"/>
+      <c r="Q13" s="91"/>
     </row>
     <row r="14" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B14" s="1"/>
@@ -15577,15 +14898,15 @@
       <c r="E14" s="1"/>
       <c r="F14" s="50"/>
       <c r="G14" s="5"/>
-      <c r="I14" s="96"/>
-      <c r="J14" s="96"/>
-      <c r="K14" s="96"/>
-      <c r="L14" s="98"/>
-      <c r="M14" s="96"/>
-      <c r="N14" s="96"/>
-      <c r="O14" s="96"/>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="96"/>
+      <c r="I14" s="91"/>
+      <c r="J14" s="91"/>
+      <c r="K14" s="91"/>
+      <c r="L14" s="93"/>
+      <c r="M14" s="91"/>
+      <c r="N14" s="91"/>
+      <c r="O14" s="91"/>
+      <c r="P14" s="91"/>
+      <c r="Q14" s="91"/>
     </row>
     <row r="15" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B15" s="1"/>
@@ -15593,15 +14914,15 @@
       <c r="D15" s="1"/>
       <c r="F15" s="50"/>
       <c r="G15" s="45"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="96"/>
-      <c r="K15" s="96"/>
-      <c r="L15" s="98"/>
-      <c r="M15" s="96"/>
-      <c r="N15" s="96"/>
-      <c r="O15" s="96"/>
-      <c r="P15" s="96"/>
-      <c r="Q15" s="96"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="91"/>
+      <c r="K15" s="91"/>
+      <c r="L15" s="93"/>
+      <c r="M15" s="91"/>
+      <c r="N15" s="91"/>
+      <c r="O15" s="91"/>
+      <c r="P15" s="91"/>
+      <c r="Q15" s="91"/>
     </row>
     <row r="16" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B16" s="1"/>
@@ -15712,126 +15033,126 @@
         <f>'EB1'!Y2</f>
         <v>M€2025</v>
       </c>
-      <c r="L2" s="91" t="s">
+      <c r="L2" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="91"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
-      <c r="P2" s="92"/>
-      <c r="Q2" s="92"/>
-      <c r="R2" s="92"/>
-      <c r="S2" s="92"/>
-      <c r="T2" s="92"/>
+      <c r="M2" s="86"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="87"/>
+      <c r="P2" s="87"/>
+      <c r="Q2" s="87"/>
+      <c r="R2" s="87"/>
+      <c r="S2" s="87"/>
+      <c r="T2" s="87"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="L3" s="93" t="s">
+      <c r="L3" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="M3" s="94" t="s">
+      <c r="M3" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="93" t="s">
+      <c r="N3" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="O3" s="93" t="s">
+      <c r="O3" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="P3" s="93" t="s">
+      <c r="P3" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="Q3" s="93" t="s">
+      <c r="Q3" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="R3" s="93" t="s">
+      <c r="R3" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="S3" s="93" t="s">
+      <c r="S3" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="T3" s="93" t="s">
+      <c r="T3" s="88" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="2:20" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C4">
         <v>4.1868000000000002E-2</v>
       </c>
-      <c r="L4" s="95" t="s">
+      <c r="L4" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="95" t="s">
+      <c r="M4" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="95" t="s">
+      <c r="N4" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="95" t="s">
+      <c r="O4" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="P4" s="95" t="s">
+      <c r="P4" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="Q4" s="95" t="s">
+      <c r="Q4" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="R4" s="95" t="s">
+      <c r="R4" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="S4" s="95" t="s">
+      <c r="S4" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="T4" s="95" t="s">
+      <c r="T4" s="90" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C5">
         <v>3.5999999999999998E-6</v>
       </c>
-      <c r="L5" s="92" t="s">
+      <c r="L5" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="M5" s="96"/>
-      <c r="N5" s="92" t="str">
+      <c r="M5" s="91"/>
+      <c r="N5" s="87" t="str">
         <f>C2</f>
         <v>GAS</v>
       </c>
-      <c r="O5" s="92" t="str">
+      <c r="O5" s="87" t="str">
         <f>D2</f>
         <v>Natural Gas</v>
       </c>
-      <c r="P5" s="92" t="str">
+      <c r="P5" s="87" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="Q5" s="92"/>
-      <c r="R5" s="92"/>
-      <c r="S5" s="92"/>
-      <c r="T5" s="92"/>
+      <c r="Q5" s="87"/>
+      <c r="R5" s="87"/>
+      <c r="S5" s="87"/>
+      <c r="T5" s="87"/>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.2">
       <c r="D7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="4"/>
-      <c r="L7" s="91" t="s">
+      <c r="L7" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="M7" s="91"/>
-      <c r="N7" s="96"/>
-      <c r="O7" s="96"/>
-      <c r="P7" s="96"/>
-      <c r="Q7" s="96"/>
-      <c r="R7" s="96"/>
-      <c r="S7" s="96"/>
-      <c r="T7" s="96"/>
+      <c r="M7" s="86"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="91"/>
+      <c r="P7" s="91"/>
+      <c r="Q7" s="91"/>
+      <c r="R7" s="91"/>
+      <c r="S7" s="91"/>
+      <c r="T7" s="91"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
@@ -15850,42 +15171,42 @@
         <v>35</v>
       </c>
       <c r="G8" s="53" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="H8" s="53" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="I8" s="53" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="J8" s="53" t="s">
-        <v>175</v>
-      </c>
-      <c r="L8" s="93" t="s">
+        <v>165</v>
+      </c>
+      <c r="L8" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="M8" s="94" t="s">
+      <c r="M8" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="N8" s="93" t="s">
+      <c r="N8" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="O8" s="93" t="s">
+      <c r="O8" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="P8" s="93" t="s">
+      <c r="P8" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="Q8" s="93" t="s">
+      <c r="Q8" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="R8" s="93" t="s">
+      <c r="R8" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="S8" s="93" t="s">
+      <c r="S8" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="T8" s="93" t="s">
+      <c r="T8" s="88" t="s">
         <v>20</v>
       </c>
     </row>
@@ -15917,31 +15238,31 @@
       <c r="J9" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="L9" s="95" t="s">
+      <c r="L9" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="M9" s="95" t="s">
+      <c r="M9" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="N9" s="95" t="s">
+      <c r="N9" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="O9" s="95" t="s">
+      <c r="O9" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="P9" s="95" t="s">
+      <c r="P9" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="Q9" s="95" t="s">
+      <c r="Q9" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="R9" s="95" t="s">
+      <c r="R9" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="S9" s="95" t="s">
+      <c r="S9" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="95" t="s">
+      <c r="T9" s="90" t="s">
         <v>25</v>
       </c>
     </row>
@@ -15975,17 +15296,17 @@
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="L10" s="95" t="s">
+      <c r="L10" s="90" t="s">
         <v>73</v>
       </c>
-      <c r="M10" s="97"/>
-      <c r="N10" s="97"/>
-      <c r="O10" s="97"/>
-      <c r="P10" s="97"/>
-      <c r="Q10" s="97"/>
-      <c r="R10" s="97"/>
-      <c r="S10" s="97"/>
-      <c r="T10" s="97"/>
+      <c r="M10" s="92"/>
+      <c r="N10" s="92"/>
+      <c r="O10" s="92"/>
+      <c r="P10" s="92"/>
+      <c r="Q10" s="92"/>
+      <c r="R10" s="92"/>
+      <c r="S10" s="92"/>
+      <c r="T10" s="92"/>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="str">
@@ -16014,30 +15335,30 @@
         <f>'JRC-IDEES2023'!G5</f>
         <v>269.10361134995702</v>
       </c>
-      <c r="L11" s="96" t="str">
+      <c r="L11" s="91" t="str">
         <f>'EB1'!$B$6</f>
         <v>IMP</v>
       </c>
-      <c r="M11" s="96"/>
-      <c r="N11" s="96" t="str">
+      <c r="M11" s="91"/>
+      <c r="N11" s="91" t="str">
         <f>$L$11&amp;$C$2&amp;1</f>
         <v>IMPGAS1</v>
       </c>
-      <c r="O11" s="98" t="str">
+      <c r="O11" s="93" t="str">
         <f>"Import of "&amp;$D$2&amp; " Step "&amp;RIGHT(N11,1)</f>
         <v>Import of Natural Gas Step 1</v>
       </c>
-      <c r="P11" s="96" t="str">
+      <c r="P11" s="91" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="Q11" s="96" t="str">
+      <c r="Q11" s="91" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="R11" s="96"/>
-      <c r="S11" s="96"/>
-      <c r="T11" s="96"/>
+      <c r="R11" s="91"/>
+      <c r="S11" s="91"/>
+      <c r="T11" s="91"/>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="str">
@@ -16053,30 +15374,30 @@
       <c r="H12" s="45"/>
       <c r="I12" s="45"/>
       <c r="J12" s="45"/>
-      <c r="L12" s="96" t="str">
+      <c r="L12" s="91" t="str">
         <f>'EB1'!B7</f>
         <v>EXP</v>
       </c>
-      <c r="M12" s="96"/>
-      <c r="N12" s="96" t="str">
+      <c r="M12" s="91"/>
+      <c r="N12" s="91" t="str">
         <f>$L$12&amp;$C$2&amp;1</f>
         <v>EXPGAS1</v>
       </c>
-      <c r="O12" s="98" t="str">
+      <c r="O12" s="93" t="str">
         <f>"Export of "&amp;$D$2&amp; " Step "&amp;RIGHT(N12,1)</f>
         <v>Export of Natural Gas Step 1</v>
       </c>
-      <c r="P12" s="96" t="str">
+      <c r="P12" s="91" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="Q12" s="96" t="str">
+      <c r="Q12" s="91" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="R12" s="96"/>
-      <c r="S12" s="96"/>
-      <c r="T12" s="96"/>
+      <c r="R12" s="91"/>
+      <c r="S12" s="91"/>
+      <c r="T12" s="91"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B13" s="1"/>
@@ -16184,115 +15505,115 @@
         <f>'EB1'!Y2</f>
         <v>M€2025</v>
       </c>
-      <c r="I2" s="91" t="s">
+      <c r="I2" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="91"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
-      <c r="P2" s="92"/>
-      <c r="Q2" s="92"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="87"/>
+      <c r="P2" s="87"/>
+      <c r="Q2" s="87"/>
     </row>
     <row r="3" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="I3" s="93" t="s">
+      <c r="I3" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="94" t="s">
+      <c r="J3" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="93" t="s">
+      <c r="K3" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="93" t="s">
+      <c r="L3" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="93" t="s">
+      <c r="M3" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="93" t="s">
+      <c r="N3" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="O3" s="93" t="s">
+      <c r="O3" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="93" t="s">
+      <c r="P3" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="Q3" s="93" t="s">
+      <c r="Q3" s="88" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="2:23" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C4" s="1"/>
-      <c r="I4" s="95" t="s">
+      <c r="I4" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="95" t="s">
+      <c r="J4" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="95" t="s">
+      <c r="K4" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="95" t="s">
+      <c r="L4" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="95" t="s">
+      <c r="M4" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="95" t="s">
+      <c r="N4" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="O4" s="95" t="s">
+      <c r="O4" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="P4" s="95" t="s">
+      <c r="P4" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="Q4" s="95" t="s">
+      <c r="Q4" s="90" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="I5" s="92" t="s">
+      <c r="I5" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="96"/>
-      <c r="K5" s="92" t="str">
+      <c r="J5" s="91"/>
+      <c r="K5" s="87" t="str">
         <f>C2</f>
         <v>OIL</v>
       </c>
-      <c r="L5" s="92" t="str">
+      <c r="L5" s="87" t="str">
         <f>D2</f>
         <v>Crude Oil</v>
       </c>
-      <c r="M5" s="92" t="str">
+      <c r="M5" s="87" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="N5" s="92"/>
-      <c r="O5" s="92"/>
-      <c r="P5" s="92"/>
-      <c r="Q5" s="92"/>
+      <c r="N5" s="87"/>
+      <c r="O5" s="87"/>
+      <c r="P5" s="87"/>
+      <c r="Q5" s="87"/>
     </row>
     <row r="7" spans="2:23" x14ac:dyDescent="0.2">
       <c r="D7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="4"/>
-      <c r="I7" s="91" t="s">
+      <c r="I7" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="91"/>
-      <c r="K7" s="96"/>
-      <c r="L7" s="96"/>
-      <c r="M7" s="96"/>
-      <c r="N7" s="96"/>
-      <c r="O7" s="96"/>
-      <c r="P7" s="96"/>
-      <c r="Q7" s="96"/>
+      <c r="J7" s="86"/>
+      <c r="K7" s="91"/>
+      <c r="L7" s="91"/>
+      <c r="M7" s="91"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="91"/>
+      <c r="P7" s="91"/>
+      <c r="Q7" s="91"/>
     </row>
     <row r="8" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
@@ -16313,31 +15634,31 @@
       <c r="G8" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="I8" s="93" t="s">
+      <c r="I8" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="J8" s="94" t="s">
+      <c r="J8" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="K8" s="93" t="s">
+      <c r="K8" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="L8" s="93" t="s">
+      <c r="L8" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="M8" s="93" t="s">
+      <c r="M8" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="93" t="s">
+      <c r="N8" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="O8" s="93" t="s">
+      <c r="O8" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="P8" s="93" t="s">
+      <c r="P8" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="Q8" s="93" t="s">
+      <c r="Q8" s="88" t="s">
         <v>20</v>
       </c>
     </row>
@@ -16360,31 +15681,31 @@
       <c r="G9" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I9" s="95" t="s">
+      <c r="I9" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="J9" s="95" t="s">
+      <c r="J9" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="K9" s="95" t="s">
+      <c r="K9" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="95" t="s">
+      <c r="L9" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="M9" s="95" t="s">
+      <c r="M9" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="N9" s="95" t="s">
+      <c r="N9" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="O9" s="95" t="s">
+      <c r="O9" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="P9" s="95" t="s">
+      <c r="P9" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="Q9" s="95" t="s">
+      <c r="Q9" s="90" t="s">
         <v>25</v>
       </c>
     </row>
@@ -16406,17 +15727,17 @@
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="I10" s="95" t="s">
+      <c r="I10" s="90" t="s">
         <v>73</v>
       </c>
-      <c r="J10" s="97"/>
-      <c r="K10" s="97"/>
-      <c r="L10" s="97"/>
-      <c r="M10" s="97"/>
-      <c r="N10" s="97"/>
-      <c r="O10" s="97"/>
-      <c r="P10" s="97"/>
-      <c r="Q10" s="97"/>
+      <c r="J10" s="92"/>
+      <c r="K10" s="92"/>
+      <c r="L10" s="92"/>
+      <c r="M10" s="92"/>
+      <c r="N10" s="92"/>
+      <c r="O10" s="92"/>
+      <c r="P10" s="92"/>
+      <c r="Q10" s="92"/>
     </row>
     <row r="11" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="str">
@@ -16433,30 +15754,30 @@
         <v>8</v>
       </c>
       <c r="G11" s="10"/>
-      <c r="I11" s="96" t="str">
+      <c r="I11" s="91" t="str">
         <f>'EB1'!$B$6</f>
         <v>IMP</v>
       </c>
-      <c r="J11" s="96"/>
-      <c r="K11" s="96" t="str">
+      <c r="J11" s="91"/>
+      <c r="K11" s="91" t="str">
         <f>$I$11&amp;$C$2&amp;1</f>
         <v>IMPOIL1</v>
       </c>
-      <c r="L11" s="98" t="str">
+      <c r="L11" s="93" t="str">
         <f>"Import of "&amp;$D$2&amp; " Step "&amp;RIGHT(K11,1)</f>
         <v>Import of Crude Oil Step 1</v>
       </c>
-      <c r="M11" s="96" t="str">
+      <c r="M11" s="91" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="N11" s="96" t="str">
+      <c r="N11" s="91" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="O11" s="96"/>
-      <c r="P11" s="96"/>
-      <c r="Q11" s="96"/>
+      <c r="O11" s="91"/>
+      <c r="P11" s="91"/>
+      <c r="Q11" s="91"/>
     </row>
     <row r="12" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="str">
@@ -16473,30 +15794,30 @@
         <v>8</v>
       </c>
       <c r="G12" s="44"/>
-      <c r="I12" s="96" t="str">
+      <c r="I12" s="91" t="str">
         <f>'EB1'!B7</f>
         <v>EXP</v>
       </c>
-      <c r="J12" s="96"/>
-      <c r="K12" s="96" t="str">
+      <c r="J12" s="91"/>
+      <c r="K12" s="91" t="str">
         <f>$I$12&amp;$C$2&amp;1</f>
         <v>EXPOIL1</v>
       </c>
-      <c r="L12" s="98" t="str">
+      <c r="L12" s="93" t="str">
         <f>"Export of "&amp;$D$2&amp; " Step "&amp;RIGHT(K12,1)</f>
         <v>Export of Crude Oil Step 1</v>
       </c>
-      <c r="M12" s="96" t="str">
+      <c r="M12" s="91" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="N12" s="96" t="str">
+      <c r="N12" s="91" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="O12" s="96"/>
-      <c r="P12" s="96"/>
-      <c r="Q12" s="96"/>
+      <c r="O12" s="91"/>
+      <c r="P12" s="91"/>
+      <c r="Q12" s="91"/>
     </row>
     <row r="13" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B13" s="1"/>
@@ -16597,116 +15918,116 @@
         <f>'EB1'!Y2</f>
         <v>M€2025</v>
       </c>
-      <c r="H2" s="91" t="s">
+      <c r="H2" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="91"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
-      <c r="P2" s="92"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="87"/>
+      <c r="P2" s="87"/>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.2">
       <c r="F3" s="8"/>
-      <c r="H3" s="93" t="s">
+      <c r="H3" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="94" t="s">
+      <c r="I3" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="93" t="s">
+      <c r="J3" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="93" t="s">
+      <c r="K3" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="93" t="s">
+      <c r="L3" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="93" t="s">
+      <c r="M3" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="N3" s="93" t="s">
+      <c r="N3" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="O3" s="93" t="s">
+      <c r="O3" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="93" t="s">
+      <c r="P3" s="88" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="2:16" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1"/>
-      <c r="H4" s="95" t="s">
+      <c r="H4" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="I4" s="95" t="s">
+      <c r="I4" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="95" t="s">
+      <c r="J4" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="95" t="s">
+      <c r="K4" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="L4" s="95" t="s">
+      <c r="L4" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="95" t="s">
+      <c r="M4" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="N4" s="95" t="s">
+      <c r="N4" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="O4" s="95" t="s">
+      <c r="O4" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="P4" s="95" t="s">
+      <c r="P4" s="90" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="H5" s="92" t="s">
+      <c r="H5" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="I5" s="96"/>
-      <c r="J5" s="92" t="str">
+      <c r="I5" s="91"/>
+      <c r="J5" s="87" t="str">
         <f>C2</f>
         <v>NUC</v>
       </c>
-      <c r="K5" s="92" t="str">
+      <c r="K5" s="87" t="str">
         <f>D2</f>
         <v>Nuclear Energy</v>
       </c>
-      <c r="L5" s="92" t="str">
+      <c r="L5" s="87" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="M5" s="92"/>
-      <c r="N5" s="92"/>
-      <c r="O5" s="92"/>
-      <c r="P5" s="92"/>
+      <c r="M5" s="87"/>
+      <c r="N5" s="87"/>
+      <c r="O5" s="87"/>
+      <c r="P5" s="87"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.2">
       <c r="D7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="H7" s="91" t="s">
+      <c r="H7" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="91"/>
-      <c r="J7" s="96"/>
-      <c r="K7" s="96"/>
-      <c r="L7" s="96"/>
-      <c r="M7" s="96"/>
-      <c r="N7" s="96"/>
-      <c r="O7" s="96"/>
-      <c r="P7" s="96"/>
+      <c r="I7" s="86"/>
+      <c r="J7" s="91"/>
+      <c r="K7" s="91"/>
+      <c r="L7" s="91"/>
+      <c r="M7" s="91"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="91"/>
+      <c r="P7" s="91"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
@@ -16724,31 +16045,31 @@
       <c r="F8" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="93" t="s">
+      <c r="H8" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="94" t="s">
+      <c r="I8" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="93" t="s">
+      <c r="J8" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="K8" s="93" t="s">
+      <c r="K8" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="L8" s="93" t="s">
+      <c r="L8" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="M8" s="93" t="s">
+      <c r="M8" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="N8" s="93" t="s">
+      <c r="N8" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="O8" s="93" t="s">
+      <c r="O8" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="P8" s="93" t="s">
+      <c r="P8" s="88" t="s">
         <v>20</v>
       </c>
     </row>
@@ -16768,31 +16089,31 @@
       <c r="F9" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="95" t="s">
+      <c r="H9" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="I9" s="95" t="s">
+      <c r="I9" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="95" t="s">
+      <c r="J9" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="K9" s="95" t="s">
+      <c r="K9" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="L9" s="95" t="s">
+      <c r="L9" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="M9" s="95" t="s">
+      <c r="M9" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="N9" s="95" t="s">
+      <c r="N9" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="O9" s="95" t="s">
+      <c r="O9" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="P9" s="95" t="s">
+      <c r="P9" s="90" t="s">
         <v>25</v>
       </c>
     </row>
@@ -16810,17 +16131,17 @@
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="H10" s="95" t="s">
+      <c r="H10" s="90" t="s">
         <v>73</v>
       </c>
-      <c r="I10" s="97"/>
-      <c r="J10" s="97"/>
-      <c r="K10" s="97"/>
-      <c r="L10" s="97"/>
-      <c r="M10" s="97"/>
-      <c r="N10" s="97"/>
-      <c r="O10" s="97"/>
-      <c r="P10" s="97"/>
+      <c r="I10" s="92"/>
+      <c r="J10" s="92"/>
+      <c r="K10" s="92"/>
+      <c r="L10" s="92"/>
+      <c r="M10" s="92"/>
+      <c r="N10" s="92"/>
+      <c r="O10" s="92"/>
+      <c r="P10" s="92"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="str">
@@ -16836,30 +16157,30 @@
         <v>0.25</v>
       </c>
       <c r="F11" s="55"/>
-      <c r="H11" s="92" t="str">
+      <c r="H11" s="87" t="str">
         <f>'EB1'!$B$5</f>
         <v>MIN</v>
       </c>
-      <c r="I11" s="96"/>
-      <c r="J11" s="96" t="str">
+      <c r="I11" s="91"/>
+      <c r="J11" s="91" t="str">
         <f>$H$11&amp;$C$2&amp;1</f>
         <v>MINNUC1</v>
       </c>
-      <c r="K11" s="98" t="str">
+      <c r="K11" s="93" t="str">
         <f>"Domestic Supply of "&amp;$D$2&amp; " Step "&amp;RIGHT(J11,1)</f>
         <v>Domestic Supply of Nuclear Energy Step 1</v>
       </c>
-      <c r="L11" s="96" t="str">
+      <c r="L11" s="91" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="M11" s="96" t="str">
+      <c r="M11" s="91" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="N11" s="96"/>
-      <c r="O11" s="96"/>
-      <c r="P11" s="96"/>
+      <c r="N11" s="91"/>
+      <c r="O11" s="91"/>
+      <c r="P11" s="91"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B12" s="1"/>
@@ -16979,17 +16300,17 @@
         <f>'EB1'!Y2</f>
         <v>M€2025</v>
       </c>
-      <c r="H2" s="91" t="s">
+      <c r="H2" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="91"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
-      <c r="P2" s="92"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="87"/>
+      <c r="P2" s="87"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C3" s="9" t="str">
@@ -17004,31 +16325,31 @@
         <f>'EB1'!$Z$2</f>
         <v>PJ</v>
       </c>
-      <c r="H3" s="93" t="s">
+      <c r="H3" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="94" t="s">
+      <c r="I3" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="93" t="s">
+      <c r="J3" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="93" t="s">
+      <c r="K3" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="93" t="s">
+      <c r="L3" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="93" t="s">
+      <c r="M3" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="N3" s="93" t="s">
+      <c r="N3" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="O3" s="93" t="s">
+      <c r="O3" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="93" t="s">
+      <c r="P3" s="88" t="s">
         <v>12</v>
       </c>
     </row>
@@ -17046,31 +16367,31 @@
         <f>'EB1'!$Z$2</f>
         <v>PJ</v>
       </c>
-      <c r="H4" s="95" t="s">
+      <c r="H4" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="I4" s="95" t="s">
+      <c r="I4" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="95" t="s">
+      <c r="J4" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="95" t="s">
+      <c r="K4" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="L4" s="95" t="s">
+      <c r="L4" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="95" t="s">
+      <c r="M4" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="N4" s="95" t="s">
+      <c r="N4" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="O4" s="95" t="s">
+      <c r="O4" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="P4" s="95" t="s">
+      <c r="P4" s="90" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17087,107 +16408,107 @@
         <f>'EB1'!$Z$2</f>
         <v>PJ</v>
       </c>
-      <c r="H5" s="92" t="s">
+      <c r="H5" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="I5" s="96"/>
-      <c r="J5" s="92" t="str">
+      <c r="I5" s="91"/>
+      <c r="J5" s="87" t="str">
         <f t="shared" ref="J5:K8" si="0">C2</f>
         <v>BIO</v>
       </c>
-      <c r="K5" s="92" t="str">
+      <c r="K5" s="87" t="str">
         <f t="shared" si="0"/>
         <v>Biomass</v>
       </c>
-      <c r="L5" s="92" t="str">
+      <c r="L5" s="87" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="M5" s="92"/>
-      <c r="N5" s="92"/>
-      <c r="O5" s="92"/>
-      <c r="P5" s="92"/>
+      <c r="M5" s="87"/>
+      <c r="N5" s="87"/>
+      <c r="O5" s="87"/>
+      <c r="P5" s="87"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="H6" s="92"/>
-      <c r="I6" s="96"/>
-      <c r="J6" s="92" t="str">
+      <c r="H6" s="87"/>
+      <c r="I6" s="91"/>
+      <c r="J6" s="87" t="str">
         <f t="shared" si="0"/>
         <v>HYD</v>
       </c>
-      <c r="K6" s="92" t="str">
+      <c r="K6" s="87" t="str">
         <f t="shared" si="0"/>
         <v>Hydro power</v>
       </c>
-      <c r="L6" s="92" t="str">
+      <c r="L6" s="87" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="M6" s="92"/>
-      <c r="N6" s="92"/>
-      <c r="O6" s="92"/>
-      <c r="P6" s="92"/>
+      <c r="M6" s="87"/>
+      <c r="N6" s="87"/>
+      <c r="O6" s="87"/>
+      <c r="P6" s="87"/>
     </row>
     <row r="7" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="92" t="str">
+      <c r="H7" s="87"/>
+      <c r="I7" s="91"/>
+      <c r="J7" s="87" t="str">
         <f t="shared" si="0"/>
         <v>WIN</v>
       </c>
-      <c r="K7" s="92" t="str">
+      <c r="K7" s="87" t="str">
         <f t="shared" si="0"/>
         <v>Wind energy</v>
       </c>
-      <c r="L7" s="92" t="str">
+      <c r="L7" s="87" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="M7" s="92"/>
-      <c r="N7" s="92"/>
-      <c r="O7" s="92"/>
-      <c r="P7" s="92"/>
+      <c r="M7" s="87"/>
+      <c r="N7" s="87"/>
+      <c r="O7" s="87"/>
+      <c r="P7" s="87"/>
     </row>
     <row r="8" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
-      <c r="H8" s="92"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="92" t="str">
+      <c r="H8" s="87"/>
+      <c r="I8" s="91"/>
+      <c r="J8" s="87" t="str">
         <f t="shared" si="0"/>
         <v>SOL</v>
       </c>
-      <c r="K8" s="92" t="str">
+      <c r="K8" s="87" t="str">
         <f t="shared" si="0"/>
         <v>Solar energy</v>
       </c>
-      <c r="L8" s="92" t="str">
+      <c r="L8" s="87" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="M8" s="92"/>
-      <c r="N8" s="92"/>
-      <c r="O8" s="92"/>
-      <c r="P8" s="92"/>
+      <c r="M8" s="87"/>
+      <c r="N8" s="87"/>
+      <c r="O8" s="87"/>
+      <c r="P8" s="87"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.2">
       <c r="D10" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="4"/>
-      <c r="H10" s="91" t="s">
+      <c r="H10" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="91"/>
-      <c r="J10" s="96"/>
-      <c r="K10" s="96"/>
-      <c r="L10" s="96"/>
-      <c r="M10" s="96"/>
-      <c r="N10" s="96"/>
-      <c r="O10" s="96"/>
-      <c r="P10" s="96"/>
+      <c r="I10" s="86"/>
+      <c r="J10" s="91"/>
+      <c r="K10" s="91"/>
+      <c r="L10" s="91"/>
+      <c r="M10" s="91"/>
+      <c r="N10" s="91"/>
+      <c r="O10" s="91"/>
+      <c r="P10" s="91"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
@@ -17205,31 +16526,31 @@
       <c r="F11" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="H11" s="93" t="s">
+      <c r="H11" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="I11" s="94" t="s">
+      <c r="I11" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="J11" s="93" t="s">
+      <c r="J11" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="K11" s="93" t="s">
+      <c r="K11" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="L11" s="93" t="s">
+      <c r="L11" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="M11" s="93" t="s">
+      <c r="M11" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="N11" s="93" t="s">
+      <c r="N11" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="O11" s="93" t="s">
+      <c r="O11" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="P11" s="93" t="s">
+      <c r="P11" s="88" t="s">
         <v>20</v>
       </c>
     </row>
@@ -17249,31 +16570,31 @@
       <c r="F12" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="H12" s="95" t="s">
+      <c r="H12" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="I12" s="95" t="s">
+      <c r="I12" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="J12" s="95" t="s">
+      <c r="J12" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="K12" s="95" t="s">
+      <c r="K12" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="L12" s="95" t="s">
+      <c r="L12" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="M12" s="95" t="s">
+      <c r="M12" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="N12" s="95" t="s">
+      <c r="N12" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="O12" s="95" t="s">
+      <c r="O12" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="P12" s="95" t="s">
+      <c r="P12" s="90" t="s">
         <v>25</v>
       </c>
     </row>
@@ -17291,17 +16612,17 @@
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="H13" s="95" t="s">
+      <c r="H13" s="90" t="s">
         <v>73</v>
       </c>
-      <c r="I13" s="97"/>
-      <c r="J13" s="97"/>
-      <c r="K13" s="97"/>
-      <c r="L13" s="97"/>
-      <c r="M13" s="97"/>
-      <c r="N13" s="97"/>
-      <c r="O13" s="97"/>
-      <c r="P13" s="97"/>
+      <c r="I13" s="92"/>
+      <c r="J13" s="92"/>
+      <c r="K13" s="92"/>
+      <c r="L13" s="92"/>
+      <c r="M13" s="92"/>
+      <c r="N13" s="92"/>
+      <c r="O13" s="92"/>
+      <c r="P13" s="92"/>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="str">
@@ -17317,30 +16638,30 @@
         <v>4.0500000000000007</v>
       </c>
       <c r="F14" s="55"/>
-      <c r="H14" s="92" t="str">
+      <c r="H14" s="87" t="str">
         <f>'EB1'!$B$5</f>
         <v>MIN</v>
       </c>
-      <c r="I14" s="96"/>
-      <c r="J14" s="96" t="str">
+      <c r="I14" s="91"/>
+      <c r="J14" s="91" t="str">
         <f>$H$14&amp;C2&amp;1</f>
         <v>MINBIO1</v>
       </c>
-      <c r="K14" s="98" t="str">
+      <c r="K14" s="93" t="str">
         <f>"Domestic Supply of "&amp;D2&amp; " Step "&amp;RIGHT(J14,1)</f>
         <v>Domestic Supply of Biomass Step 1</v>
       </c>
-      <c r="L14" s="96" t="str">
+      <c r="L14" s="91" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="M14" s="96" t="str">
+      <c r="M14" s="91" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="N14" s="96"/>
-      <c r="O14" s="96"/>
-      <c r="P14" s="96"/>
+      <c r="N14" s="91"/>
+      <c r="O14" s="91"/>
+      <c r="P14" s="91"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="str">
@@ -17354,27 +16675,27 @@
       </c>
       <c r="E15" s="54"/>
       <c r="F15" s="55"/>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="96" t="str">
+      <c r="H15" s="91"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="91" t="str">
         <f>$H$14&amp;C3&amp;1</f>
         <v>MINHYD1</v>
       </c>
-      <c r="K15" s="98" t="str">
+      <c r="K15" s="93" t="str">
         <f>"Domestic Supply of "&amp;D3&amp; " Step "&amp;RIGHT(J15,1)</f>
         <v>Domestic Supply of Hydro power Step 1</v>
       </c>
-      <c r="L15" s="96" t="str">
+      <c r="L15" s="91" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="M15" s="96" t="str">
+      <c r="M15" s="91" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="N15" s="96"/>
-      <c r="O15" s="96"/>
-      <c r="P15" s="96"/>
+      <c r="N15" s="91"/>
+      <c r="O15" s="91"/>
+      <c r="P15" s="91"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="str">
@@ -17388,27 +16709,27 @@
       </c>
       <c r="E16" s="54"/>
       <c r="F16" s="55"/>
-      <c r="H16" s="96"/>
-      <c r="I16" s="96"/>
-      <c r="J16" s="96" t="str">
+      <c r="H16" s="91"/>
+      <c r="I16" s="91"/>
+      <c r="J16" s="91" t="str">
         <f>$H$14&amp;C4&amp;1</f>
         <v>MINWIN1</v>
       </c>
-      <c r="K16" s="98" t="str">
+      <c r="K16" s="93" t="str">
         <f>"Domestic Supply of "&amp;D4&amp; " Step "&amp;RIGHT(J16,1)</f>
         <v>Domestic Supply of Wind energy Step 1</v>
       </c>
-      <c r="L16" s="96" t="str">
+      <c r="L16" s="91" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="M16" s="96" t="str">
+      <c r="M16" s="91" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="N16" s="96"/>
-      <c r="O16" s="96"/>
-      <c r="P16" s="96"/>
+      <c r="N16" s="91"/>
+      <c r="O16" s="91"/>
+      <c r="P16" s="91"/>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="str">
@@ -17421,27 +16742,27 @@
         <v>SOL</v>
       </c>
       <c r="E17" s="25"/>
-      <c r="H17" s="96"/>
-      <c r="I17" s="96"/>
-      <c r="J17" s="96" t="str">
+      <c r="H17" s="91"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="91" t="str">
         <f>$H$14&amp;C5&amp;1</f>
         <v>MINSOL1</v>
       </c>
-      <c r="K17" s="98" t="str">
+      <c r="K17" s="93" t="str">
         <f>"Domestic Supply of "&amp;D5&amp; " Step "&amp;RIGHT(J17,1)</f>
         <v>Domestic Supply of Solar energy Step 1</v>
       </c>
-      <c r="L17" s="96" t="str">
+      <c r="L17" s="91" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="M17" s="96" t="str">
+      <c r="M17" s="91" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="N17" s="96"/>
-      <c r="O17" s="96"/>
-      <c r="P17" s="96"/>
+      <c r="N17" s="91"/>
+      <c r="O17" s="91"/>
+      <c r="P17" s="91"/>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B18" s="1"/>
@@ -17529,10 +16850,10 @@
     <row r="2" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="9"/>
       <c r="C2" s="9" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E2" s="9" t="str">
         <f>'EB1'!$Z$2</f>
@@ -17542,47 +16863,47 @@
         <f>'EB1'!Y2</f>
         <v>M€2025</v>
       </c>
-      <c r="H2" s="91" t="s">
+      <c r="H2" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="91"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
-      <c r="P2" s="92"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="87"/>
+      <c r="P2" s="87"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C3" s="9"/>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
-      <c r="H3" s="93" t="s">
+      <c r="H3" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="94" t="s">
+      <c r="I3" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="93" t="s">
+      <c r="J3" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="93" t="s">
+      <c r="K3" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="93" t="s">
+      <c r="L3" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="93" t="s">
+      <c r="M3" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="N3" s="93" t="s">
+      <c r="N3" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="O3" s="93" t="s">
+      <c r="O3" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="93" t="s">
+      <c r="P3" s="88" t="s">
         <v>12</v>
       </c>
     </row>
@@ -17591,31 +16912,31 @@
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
-      <c r="H4" s="95" t="s">
+      <c r="H4" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="I4" s="95" t="s">
+      <c r="I4" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="95" t="s">
+      <c r="J4" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="95" t="s">
+      <c r="K4" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="L4" s="95" t="s">
+      <c r="L4" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="95" t="s">
+      <c r="M4" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="N4" s="95" t="s">
+      <c r="N4" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="O4" s="95" t="s">
+      <c r="O4" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="P4" s="95" t="s">
+      <c r="P4" s="90" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17623,80 +16944,80 @@
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
-      <c r="H5" s="92" t="s">
+      <c r="H5" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="I5" s="96"/>
-      <c r="J5" s="92" t="str">
+      <c r="I5" s="91"/>
+      <c r="J5" s="87" t="str">
         <f t="shared" ref="J5:K5" si="0">C2</f>
         <v>MSW</v>
       </c>
-      <c r="K5" s="92" t="str">
+      <c r="K5" s="87" t="str">
         <f t="shared" si="0"/>
         <v>Municipal waste</v>
       </c>
-      <c r="L5" s="92" t="str">
+      <c r="L5" s="87" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="M5" s="92"/>
-      <c r="N5" s="92"/>
-      <c r="O5" s="92"/>
-      <c r="P5" s="92"/>
+      <c r="M5" s="87"/>
+      <c r="N5" s="87"/>
+      <c r="O5" s="87"/>
+      <c r="P5" s="87"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="H6" s="92"/>
-      <c r="I6" s="96"/>
-      <c r="J6" s="92"/>
-      <c r="K6" s="92"/>
-      <c r="L6" s="92"/>
-      <c r="M6" s="92"/>
-      <c r="N6" s="92"/>
-      <c r="O6" s="92"/>
-      <c r="P6" s="92"/>
+      <c r="H6" s="87"/>
+      <c r="I6" s="91"/>
+      <c r="J6" s="87"/>
+      <c r="K6" s="87"/>
+      <c r="L6" s="87"/>
+      <c r="M6" s="87"/>
+      <c r="N6" s="87"/>
+      <c r="O6" s="87"/>
+      <c r="P6" s="87"/>
     </row>
     <row r="7" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="92"/>
-      <c r="K7" s="92"/>
-      <c r="L7" s="92"/>
-      <c r="M7" s="92"/>
-      <c r="N7" s="92"/>
-      <c r="O7" s="92"/>
-      <c r="P7" s="92"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="91"/>
+      <c r="J7" s="87"/>
+      <c r="K7" s="87"/>
+      <c r="L7" s="87"/>
+      <c r="M7" s="87"/>
+      <c r="N7" s="87"/>
+      <c r="O7" s="87"/>
+      <c r="P7" s="87"/>
     </row>
     <row r="8" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
-      <c r="H8" s="92"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="92"/>
-      <c r="K8" s="92"/>
-      <c r="L8" s="92"/>
-      <c r="M8" s="92"/>
-      <c r="N8" s="92"/>
-      <c r="O8" s="92"/>
-      <c r="P8" s="92"/>
+      <c r="H8" s="87"/>
+      <c r="I8" s="91"/>
+      <c r="J8" s="87"/>
+      <c r="K8" s="87"/>
+      <c r="L8" s="87"/>
+      <c r="M8" s="87"/>
+      <c r="N8" s="87"/>
+      <c r="O8" s="87"/>
+      <c r="P8" s="87"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.2">
       <c r="D10" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="4"/>
-      <c r="H10" s="91" t="s">
+      <c r="H10" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="91"/>
-      <c r="J10" s="96"/>
-      <c r="K10" s="96"/>
-      <c r="L10" s="96"/>
-      <c r="M10" s="96"/>
-      <c r="N10" s="96"/>
-      <c r="O10" s="96"/>
-      <c r="P10" s="96"/>
+      <c r="I10" s="86"/>
+      <c r="J10" s="91"/>
+      <c r="K10" s="91"/>
+      <c r="L10" s="91"/>
+      <c r="M10" s="91"/>
+      <c r="N10" s="91"/>
+      <c r="O10" s="91"/>
+      <c r="P10" s="91"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
@@ -17714,31 +17035,31 @@
       <c r="F11" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="H11" s="93" t="s">
+      <c r="H11" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="I11" s="94" t="s">
+      <c r="I11" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="J11" s="93" t="s">
+      <c r="J11" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="K11" s="93" t="s">
+      <c r="K11" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="L11" s="93" t="s">
+      <c r="L11" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="M11" s="93" t="s">
+      <c r="M11" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="N11" s="93" t="s">
+      <c r="N11" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="O11" s="93" t="s">
+      <c r="O11" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="P11" s="93" t="s">
+      <c r="P11" s="88" t="s">
         <v>20</v>
       </c>
     </row>
@@ -17758,31 +17079,31 @@
       <c r="F12" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="H12" s="95" t="s">
+      <c r="H12" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="I12" s="95" t="s">
+      <c r="I12" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="J12" s="95" t="s">
+      <c r="J12" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="K12" s="95" t="s">
+      <c r="K12" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="L12" s="95" t="s">
+      <c r="L12" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="M12" s="95" t="s">
+      <c r="M12" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="N12" s="95" t="s">
+      <c r="N12" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="O12" s="95" t="s">
+      <c r="O12" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="P12" s="95" t="s">
+      <c r="P12" s="90" t="s">
         <v>25</v>
       </c>
     </row>
@@ -17800,17 +17121,17 @@
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="H13" s="95" t="s">
+      <c r="H13" s="90" t="s">
         <v>73</v>
       </c>
-      <c r="I13" s="97"/>
-      <c r="J13" s="97"/>
-      <c r="K13" s="97"/>
-      <c r="L13" s="97"/>
-      <c r="M13" s="97"/>
-      <c r="N13" s="97"/>
-      <c r="O13" s="97"/>
-      <c r="P13" s="97"/>
+      <c r="I13" s="92"/>
+      <c r="J13" s="92"/>
+      <c r="K13" s="92"/>
+      <c r="L13" s="92"/>
+      <c r="M13" s="92"/>
+      <c r="N13" s="92"/>
+      <c r="O13" s="92"/>
+      <c r="P13" s="92"/>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="str">
@@ -17826,30 +17147,30 @@
         <v>4.0500000000000007</v>
       </c>
       <c r="F14" s="55"/>
-      <c r="H14" s="92" t="str">
+      <c r="H14" s="87" t="str">
         <f>'EB1'!$B$5</f>
         <v>MIN</v>
       </c>
-      <c r="I14" s="96"/>
-      <c r="J14" s="96" t="str">
+      <c r="I14" s="91"/>
+      <c r="J14" s="91" t="str">
         <f>$H$14&amp;C2&amp;1</f>
         <v>MINMSW1</v>
       </c>
-      <c r="K14" s="98" t="str">
+      <c r="K14" s="93" t="str">
         <f>"Domestic Supply of "&amp;D2&amp; " Step "&amp;RIGHT(J14,1)</f>
         <v>Domestic Supply of Municipal waste Step 1</v>
       </c>
-      <c r="L14" s="96" t="str">
+      <c r="L14" s="91" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="M14" s="96" t="str">
+      <c r="M14" s="91" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="N14" s="96"/>
-      <c r="O14" s="96"/>
-      <c r="P14" s="96"/>
+      <c r="N14" s="91"/>
+      <c r="O14" s="91"/>
+      <c r="P14" s="91"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B15" s="1"/>
@@ -17857,15 +17178,15 @@
       <c r="D15" s="1"/>
       <c r="E15" s="54"/>
       <c r="F15" s="55"/>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="96"/>
-      <c r="K15" s="98"/>
-      <c r="L15" s="96"/>
-      <c r="M15" s="96"/>
-      <c r="N15" s="96"/>
-      <c r="O15" s="96"/>
-      <c r="P15" s="96"/>
+      <c r="H15" s="91"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="91"/>
+      <c r="K15" s="93"/>
+      <c r="L15" s="91"/>
+      <c r="M15" s="91"/>
+      <c r="N15" s="91"/>
+      <c r="O15" s="91"/>
+      <c r="P15" s="91"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B16" s="1"/>
@@ -17873,30 +17194,30 @@
       <c r="D16" s="1"/>
       <c r="E16" s="54"/>
       <c r="F16" s="55"/>
-      <c r="H16" s="96"/>
-      <c r="I16" s="96"/>
-      <c r="J16" s="96"/>
-      <c r="K16" s="98"/>
-      <c r="L16" s="96"/>
-      <c r="M16" s="96"/>
-      <c r="N16" s="96"/>
-      <c r="O16" s="96"/>
-      <c r="P16" s="96"/>
+      <c r="H16" s="91"/>
+      <c r="I16" s="91"/>
+      <c r="J16" s="91"/>
+      <c r="K16" s="93"/>
+      <c r="L16" s="91"/>
+      <c r="M16" s="91"/>
+      <c r="N16" s="91"/>
+      <c r="O16" s="91"/>
+      <c r="P16" s="91"/>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="25"/>
-      <c r="H17" s="96"/>
-      <c r="I17" s="96"/>
-      <c r="J17" s="96"/>
-      <c r="K17" s="98"/>
-      <c r="L17" s="96"/>
-      <c r="M17" s="96"/>
-      <c r="N17" s="96"/>
-      <c r="O17" s="96"/>
-      <c r="P17" s="96"/>
+      <c r="H17" s="91"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="91"/>
+      <c r="K17" s="93"/>
+      <c r="L17" s="91"/>
+      <c r="M17" s="91"/>
+      <c r="N17" s="91"/>
+      <c r="O17" s="91"/>
+      <c r="P17" s="91"/>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B18" s="1"/>
